--- a/vue-pure-admin/public/IP导入模板.xlsx
+++ b/vue-pure-admin/public/IP导入模板.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填写说明" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'IP导入模板'!$A$1:$AF$501</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'IP导入模板'!$A$1:$AO$501</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,7 +19,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="4">
     <font>
       <name val="Calibri"/>
@@ -75,7 +77,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -90,6 +92,12 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -180,6 +188,11 @@
     <comment ref="D1" authorId="0" shapeId="0">
       <text>
         <t>覆盖市场可选多个。每列选择一个市场，最多9列；空白列无需填写。</t>
+      </text>
+    </comment>
+    <comment ref="M1" authorId="0" shapeId="0">
+      <text>
+        <t>渗透率1至9与覆盖市场1至9逐列对应；填0至100的数字，例如25表示25%。可留空。</t>
       </text>
     </comment>
   </commentList>
@@ -475,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF501"/>
+  <dimension ref="A1:AO501"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -490,15 +503,15 @@
     <col width="22" customWidth="1" min="10" max="10"/>
     <col width="22" customWidth="1" min="11" max="11"/>
     <col width="22" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
-    <col width="22" customWidth="1" min="14" max="14"/>
-    <col width="22" customWidth="1" min="15" max="15"/>
-    <col width="30" customWidth="1" min="16" max="16"/>
-    <col width="22" customWidth="1" min="17" max="17"/>
-    <col width="22" customWidth="1" min="18" max="18"/>
-    <col width="22" customWidth="1" min="19" max="19"/>
-    <col width="22" customWidth="1" min="20" max="20"/>
-    <col width="22" customWidth="1" min="21" max="21"/>
+    <col width="19" customWidth="1" min="13" max="13"/>
+    <col width="19" customWidth="1" min="14" max="14"/>
+    <col width="19" customWidth="1" min="15" max="15"/>
+    <col width="19" customWidth="1" min="16" max="16"/>
+    <col width="19" customWidth="1" min="17" max="17"/>
+    <col width="19" customWidth="1" min="18" max="18"/>
+    <col width="19" customWidth="1" min="19" max="19"/>
+    <col width="19" customWidth="1" min="20" max="20"/>
+    <col width="19" customWidth="1" min="21" max="21"/>
     <col width="22" customWidth="1" min="22" max="22"/>
     <col width="22" customWidth="1" min="23" max="23"/>
     <col width="22" customWidth="1" min="24" max="24"/>
@@ -573,102 +586,147 @@
           <t>覆盖市场9</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>渗透率1（%）</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>渗透率2（%）</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>渗透率3（%）</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
+        <is>
+          <t>渗透率4（%）</t>
+        </is>
+      </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>渗透率5（%）</t>
+        </is>
+      </c>
+      <c r="R1" s="2" t="inlineStr">
+        <is>
+          <t>渗透率6（%）</t>
+        </is>
+      </c>
+      <c r="S1" s="2" t="inlineStr">
+        <is>
+          <t>渗透率7（%）</t>
+        </is>
+      </c>
+      <c r="T1" s="2" t="inlineStr">
+        <is>
+          <t>渗透率8（%）</t>
+        </is>
+      </c>
+      <c r="U1" s="2" t="inlineStr">
+        <is>
+          <t>渗透率9（%）</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>版权方</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>联系人</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>目标受众</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>IP简介</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>合作状态</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>币种</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>基础权益价格下限</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>基础权益价格上限</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>授权范围与限制</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>IP形象与风格</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>IP生命周期</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>受众性别占比</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>主要年龄</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>消费力评价</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>注册用户 / 赛事参与</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>历史销售转化力</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>IP展示与合作表现</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>合作建议与提醒</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>历史合作名称</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>历史合作概述</t>
         </is>
@@ -707,6 +765,15 @@
       <c r="AD2" s="3" t="n"/>
       <c r="AE2" s="3" t="n"/>
       <c r="AF2" s="3" t="n"/>
+      <c r="AG2" s="3" t="n"/>
+      <c r="AH2" s="3" t="n"/>
+      <c r="AI2" s="3" t="n"/>
+      <c r="AJ2" s="3" t="n"/>
+      <c r="AK2" s="3" t="n"/>
+      <c r="AL2" s="3" t="n"/>
+      <c r="AM2" s="3" t="n"/>
+      <c r="AN2" s="3" t="n"/>
+      <c r="AO2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n"/>
@@ -741,6 +808,15 @@
       <c r="AD3" s="4" t="n"/>
       <c r="AE3" s="4" t="n"/>
       <c r="AF3" s="4" t="n"/>
+      <c r="AG3" s="4" t="n"/>
+      <c r="AH3" s="4" t="n"/>
+      <c r="AI3" s="4" t="n"/>
+      <c r="AJ3" s="4" t="n"/>
+      <c r="AK3" s="4" t="n"/>
+      <c r="AL3" s="4" t="n"/>
+      <c r="AM3" s="4" t="n"/>
+      <c r="AN3" s="4" t="n"/>
+      <c r="AO3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n"/>
@@ -775,6 +851,15 @@
       <c r="AD4" s="3" t="n"/>
       <c r="AE4" s="3" t="n"/>
       <c r="AF4" s="3" t="n"/>
+      <c r="AG4" s="3" t="n"/>
+      <c r="AH4" s="3" t="n"/>
+      <c r="AI4" s="3" t="n"/>
+      <c r="AJ4" s="3" t="n"/>
+      <c r="AK4" s="3" t="n"/>
+      <c r="AL4" s="3" t="n"/>
+      <c r="AM4" s="3" t="n"/>
+      <c r="AN4" s="3" t="n"/>
+      <c r="AO4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n"/>
@@ -809,6 +894,15 @@
       <c r="AD5" s="4" t="n"/>
       <c r="AE5" s="4" t="n"/>
       <c r="AF5" s="4" t="n"/>
+      <c r="AG5" s="4" t="n"/>
+      <c r="AH5" s="4" t="n"/>
+      <c r="AI5" s="4" t="n"/>
+      <c r="AJ5" s="4" t="n"/>
+      <c r="AK5" s="4" t="n"/>
+      <c r="AL5" s="4" t="n"/>
+      <c r="AM5" s="4" t="n"/>
+      <c r="AN5" s="4" t="n"/>
+      <c r="AO5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n"/>
@@ -843,6 +937,15 @@
       <c r="AD6" s="3" t="n"/>
       <c r="AE6" s="3" t="n"/>
       <c r="AF6" s="3" t="n"/>
+      <c r="AG6" s="3" t="n"/>
+      <c r="AH6" s="3" t="n"/>
+      <c r="AI6" s="3" t="n"/>
+      <c r="AJ6" s="3" t="n"/>
+      <c r="AK6" s="3" t="n"/>
+      <c r="AL6" s="3" t="n"/>
+      <c r="AM6" s="3" t="n"/>
+      <c r="AN6" s="3" t="n"/>
+      <c r="AO6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n"/>
@@ -877,6 +980,15 @@
       <c r="AD7" s="4" t="n"/>
       <c r="AE7" s="4" t="n"/>
       <c r="AF7" s="4" t="n"/>
+      <c r="AG7" s="4" t="n"/>
+      <c r="AH7" s="4" t="n"/>
+      <c r="AI7" s="4" t="n"/>
+      <c r="AJ7" s="4" t="n"/>
+      <c r="AK7" s="4" t="n"/>
+      <c r="AL7" s="4" t="n"/>
+      <c r="AM7" s="4" t="n"/>
+      <c r="AN7" s="4" t="n"/>
+      <c r="AO7" s="4" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n"/>
@@ -911,6 +1023,15 @@
       <c r="AD8" s="3" t="n"/>
       <c r="AE8" s="3" t="n"/>
       <c r="AF8" s="3" t="n"/>
+      <c r="AG8" s="3" t="n"/>
+      <c r="AH8" s="3" t="n"/>
+      <c r="AI8" s="3" t="n"/>
+      <c r="AJ8" s="3" t="n"/>
+      <c r="AK8" s="3" t="n"/>
+      <c r="AL8" s="3" t="n"/>
+      <c r="AM8" s="3" t="n"/>
+      <c r="AN8" s="3" t="n"/>
+      <c r="AO8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n"/>
@@ -945,6 +1066,15 @@
       <c r="AD9" s="4" t="n"/>
       <c r="AE9" s="4" t="n"/>
       <c r="AF9" s="4" t="n"/>
+      <c r="AG9" s="4" t="n"/>
+      <c r="AH9" s="4" t="n"/>
+      <c r="AI9" s="4" t="n"/>
+      <c r="AJ9" s="4" t="n"/>
+      <c r="AK9" s="4" t="n"/>
+      <c r="AL9" s="4" t="n"/>
+      <c r="AM9" s="4" t="n"/>
+      <c r="AN9" s="4" t="n"/>
+      <c r="AO9" s="4" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n"/>
@@ -979,6 +1109,15 @@
       <c r="AD10" s="3" t="n"/>
       <c r="AE10" s="3" t="n"/>
       <c r="AF10" s="3" t="n"/>
+      <c r="AG10" s="3" t="n"/>
+      <c r="AH10" s="3" t="n"/>
+      <c r="AI10" s="3" t="n"/>
+      <c r="AJ10" s="3" t="n"/>
+      <c r="AK10" s="3" t="n"/>
+      <c r="AL10" s="3" t="n"/>
+      <c r="AM10" s="3" t="n"/>
+      <c r="AN10" s="3" t="n"/>
+      <c r="AO10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n"/>
@@ -1013,6 +1152,15 @@
       <c r="AD11" s="4" t="n"/>
       <c r="AE11" s="4" t="n"/>
       <c r="AF11" s="4" t="n"/>
+      <c r="AG11" s="4" t="n"/>
+      <c r="AH11" s="4" t="n"/>
+      <c r="AI11" s="4" t="n"/>
+      <c r="AJ11" s="4" t="n"/>
+      <c r="AK11" s="4" t="n"/>
+      <c r="AL11" s="4" t="n"/>
+      <c r="AM11" s="4" t="n"/>
+      <c r="AN11" s="4" t="n"/>
+      <c r="AO11" s="4" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n"/>
@@ -1047,6 +1195,15 @@
       <c r="AD12" s="3" t="n"/>
       <c r="AE12" s="3" t="n"/>
       <c r="AF12" s="3" t="n"/>
+      <c r="AG12" s="3" t="n"/>
+      <c r="AH12" s="3" t="n"/>
+      <c r="AI12" s="3" t="n"/>
+      <c r="AJ12" s="3" t="n"/>
+      <c r="AK12" s="3" t="n"/>
+      <c r="AL12" s="3" t="n"/>
+      <c r="AM12" s="3" t="n"/>
+      <c r="AN12" s="3" t="n"/>
+      <c r="AO12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n"/>
@@ -1081,6 +1238,15 @@
       <c r="AD13" s="4" t="n"/>
       <c r="AE13" s="4" t="n"/>
       <c r="AF13" s="4" t="n"/>
+      <c r="AG13" s="4" t="n"/>
+      <c r="AH13" s="4" t="n"/>
+      <c r="AI13" s="4" t="n"/>
+      <c r="AJ13" s="4" t="n"/>
+      <c r="AK13" s="4" t="n"/>
+      <c r="AL13" s="4" t="n"/>
+      <c r="AM13" s="4" t="n"/>
+      <c r="AN13" s="4" t="n"/>
+      <c r="AO13" s="4" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n"/>
@@ -1115,6 +1281,15 @@
       <c r="AD14" s="3" t="n"/>
       <c r="AE14" s="3" t="n"/>
       <c r="AF14" s="3" t="n"/>
+      <c r="AG14" s="3" t="n"/>
+      <c r="AH14" s="3" t="n"/>
+      <c r="AI14" s="3" t="n"/>
+      <c r="AJ14" s="3" t="n"/>
+      <c r="AK14" s="3" t="n"/>
+      <c r="AL14" s="3" t="n"/>
+      <c r="AM14" s="3" t="n"/>
+      <c r="AN14" s="3" t="n"/>
+      <c r="AO14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n"/>
@@ -1149,6 +1324,15 @@
       <c r="AD15" s="4" t="n"/>
       <c r="AE15" s="4" t="n"/>
       <c r="AF15" s="4" t="n"/>
+      <c r="AG15" s="4" t="n"/>
+      <c r="AH15" s="4" t="n"/>
+      <c r="AI15" s="4" t="n"/>
+      <c r="AJ15" s="4" t="n"/>
+      <c r="AK15" s="4" t="n"/>
+      <c r="AL15" s="4" t="n"/>
+      <c r="AM15" s="4" t="n"/>
+      <c r="AN15" s="4" t="n"/>
+      <c r="AO15" s="4" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n"/>
@@ -1183,6 +1367,15 @@
       <c r="AD16" s="3" t="n"/>
       <c r="AE16" s="3" t="n"/>
       <c r="AF16" s="3" t="n"/>
+      <c r="AG16" s="3" t="n"/>
+      <c r="AH16" s="3" t="n"/>
+      <c r="AI16" s="3" t="n"/>
+      <c r="AJ16" s="3" t="n"/>
+      <c r="AK16" s="3" t="n"/>
+      <c r="AL16" s="3" t="n"/>
+      <c r="AM16" s="3" t="n"/>
+      <c r="AN16" s="3" t="n"/>
+      <c r="AO16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n"/>
@@ -1217,6 +1410,15 @@
       <c r="AD17" s="4" t="n"/>
       <c r="AE17" s="4" t="n"/>
       <c r="AF17" s="4" t="n"/>
+      <c r="AG17" s="4" t="n"/>
+      <c r="AH17" s="4" t="n"/>
+      <c r="AI17" s="4" t="n"/>
+      <c r="AJ17" s="4" t="n"/>
+      <c r="AK17" s="4" t="n"/>
+      <c r="AL17" s="4" t="n"/>
+      <c r="AM17" s="4" t="n"/>
+      <c r="AN17" s="4" t="n"/>
+      <c r="AO17" s="4" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n"/>
@@ -1251,6 +1453,15 @@
       <c r="AD18" s="3" t="n"/>
       <c r="AE18" s="3" t="n"/>
       <c r="AF18" s="3" t="n"/>
+      <c r="AG18" s="3" t="n"/>
+      <c r="AH18" s="3" t="n"/>
+      <c r="AI18" s="3" t="n"/>
+      <c r="AJ18" s="3" t="n"/>
+      <c r="AK18" s="3" t="n"/>
+      <c r="AL18" s="3" t="n"/>
+      <c r="AM18" s="3" t="n"/>
+      <c r="AN18" s="3" t="n"/>
+      <c r="AO18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n"/>
@@ -1285,6 +1496,15 @@
       <c r="AD19" s="4" t="n"/>
       <c r="AE19" s="4" t="n"/>
       <c r="AF19" s="4" t="n"/>
+      <c r="AG19" s="4" t="n"/>
+      <c r="AH19" s="4" t="n"/>
+      <c r="AI19" s="4" t="n"/>
+      <c r="AJ19" s="4" t="n"/>
+      <c r="AK19" s="4" t="n"/>
+      <c r="AL19" s="4" t="n"/>
+      <c r="AM19" s="4" t="n"/>
+      <c r="AN19" s="4" t="n"/>
+      <c r="AO19" s="4" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n"/>
@@ -1319,6 +1539,15 @@
       <c r="AD20" s="3" t="n"/>
       <c r="AE20" s="3" t="n"/>
       <c r="AF20" s="3" t="n"/>
+      <c r="AG20" s="3" t="n"/>
+      <c r="AH20" s="3" t="n"/>
+      <c r="AI20" s="3" t="n"/>
+      <c r="AJ20" s="3" t="n"/>
+      <c r="AK20" s="3" t="n"/>
+      <c r="AL20" s="3" t="n"/>
+      <c r="AM20" s="3" t="n"/>
+      <c r="AN20" s="3" t="n"/>
+      <c r="AO20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n"/>
@@ -1353,6 +1582,15 @@
       <c r="AD21" s="4" t="n"/>
       <c r="AE21" s="4" t="n"/>
       <c r="AF21" s="4" t="n"/>
+      <c r="AG21" s="4" t="n"/>
+      <c r="AH21" s="4" t="n"/>
+      <c r="AI21" s="4" t="n"/>
+      <c r="AJ21" s="4" t="n"/>
+      <c r="AK21" s="4" t="n"/>
+      <c r="AL21" s="4" t="n"/>
+      <c r="AM21" s="4" t="n"/>
+      <c r="AN21" s="4" t="n"/>
+      <c r="AO21" s="4" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n"/>
@@ -1387,6 +1625,15 @@
       <c r="AD22" s="3" t="n"/>
       <c r="AE22" s="3" t="n"/>
       <c r="AF22" s="3" t="n"/>
+      <c r="AG22" s="3" t="n"/>
+      <c r="AH22" s="3" t="n"/>
+      <c r="AI22" s="3" t="n"/>
+      <c r="AJ22" s="3" t="n"/>
+      <c r="AK22" s="3" t="n"/>
+      <c r="AL22" s="3" t="n"/>
+      <c r="AM22" s="3" t="n"/>
+      <c r="AN22" s="3" t="n"/>
+      <c r="AO22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n"/>
@@ -1421,6 +1668,15 @@
       <c r="AD23" s="4" t="n"/>
       <c r="AE23" s="4" t="n"/>
       <c r="AF23" s="4" t="n"/>
+      <c r="AG23" s="4" t="n"/>
+      <c r="AH23" s="4" t="n"/>
+      <c r="AI23" s="4" t="n"/>
+      <c r="AJ23" s="4" t="n"/>
+      <c r="AK23" s="4" t="n"/>
+      <c r="AL23" s="4" t="n"/>
+      <c r="AM23" s="4" t="n"/>
+      <c r="AN23" s="4" t="n"/>
+      <c r="AO23" s="4" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n"/>
@@ -1455,6 +1711,15 @@
       <c r="AD24" s="3" t="n"/>
       <c r="AE24" s="3" t="n"/>
       <c r="AF24" s="3" t="n"/>
+      <c r="AG24" s="3" t="n"/>
+      <c r="AH24" s="3" t="n"/>
+      <c r="AI24" s="3" t="n"/>
+      <c r="AJ24" s="3" t="n"/>
+      <c r="AK24" s="3" t="n"/>
+      <c r="AL24" s="3" t="n"/>
+      <c r="AM24" s="3" t="n"/>
+      <c r="AN24" s="3" t="n"/>
+      <c r="AO24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n"/>
@@ -1489,6 +1754,15 @@
       <c r="AD25" s="4" t="n"/>
       <c r="AE25" s="4" t="n"/>
       <c r="AF25" s="4" t="n"/>
+      <c r="AG25" s="4" t="n"/>
+      <c r="AH25" s="4" t="n"/>
+      <c r="AI25" s="4" t="n"/>
+      <c r="AJ25" s="4" t="n"/>
+      <c r="AK25" s="4" t="n"/>
+      <c r="AL25" s="4" t="n"/>
+      <c r="AM25" s="4" t="n"/>
+      <c r="AN25" s="4" t="n"/>
+      <c r="AO25" s="4" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n"/>
@@ -1523,6 +1797,15 @@
       <c r="AD26" s="3" t="n"/>
       <c r="AE26" s="3" t="n"/>
       <c r="AF26" s="3" t="n"/>
+      <c r="AG26" s="3" t="n"/>
+      <c r="AH26" s="3" t="n"/>
+      <c r="AI26" s="3" t="n"/>
+      <c r="AJ26" s="3" t="n"/>
+      <c r="AK26" s="3" t="n"/>
+      <c r="AL26" s="3" t="n"/>
+      <c r="AM26" s="3" t="n"/>
+      <c r="AN26" s="3" t="n"/>
+      <c r="AO26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n"/>
@@ -1557,6 +1840,15 @@
       <c r="AD27" s="4" t="n"/>
       <c r="AE27" s="4" t="n"/>
       <c r="AF27" s="4" t="n"/>
+      <c r="AG27" s="4" t="n"/>
+      <c r="AH27" s="4" t="n"/>
+      <c r="AI27" s="4" t="n"/>
+      <c r="AJ27" s="4" t="n"/>
+      <c r="AK27" s="4" t="n"/>
+      <c r="AL27" s="4" t="n"/>
+      <c r="AM27" s="4" t="n"/>
+      <c r="AN27" s="4" t="n"/>
+      <c r="AO27" s="4" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n"/>
@@ -1591,6 +1883,15 @@
       <c r="AD28" s="3" t="n"/>
       <c r="AE28" s="3" t="n"/>
       <c r="AF28" s="3" t="n"/>
+      <c r="AG28" s="3" t="n"/>
+      <c r="AH28" s="3" t="n"/>
+      <c r="AI28" s="3" t="n"/>
+      <c r="AJ28" s="3" t="n"/>
+      <c r="AK28" s="3" t="n"/>
+      <c r="AL28" s="3" t="n"/>
+      <c r="AM28" s="3" t="n"/>
+      <c r="AN28" s="3" t="n"/>
+      <c r="AO28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n"/>
@@ -1625,6 +1926,15 @@
       <c r="AD29" s="4" t="n"/>
       <c r="AE29" s="4" t="n"/>
       <c r="AF29" s="4" t="n"/>
+      <c r="AG29" s="4" t="n"/>
+      <c r="AH29" s="4" t="n"/>
+      <c r="AI29" s="4" t="n"/>
+      <c r="AJ29" s="4" t="n"/>
+      <c r="AK29" s="4" t="n"/>
+      <c r="AL29" s="4" t="n"/>
+      <c r="AM29" s="4" t="n"/>
+      <c r="AN29" s="4" t="n"/>
+      <c r="AO29" s="4" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n"/>
@@ -1659,6 +1969,15 @@
       <c r="AD30" s="3" t="n"/>
       <c r="AE30" s="3" t="n"/>
       <c r="AF30" s="3" t="n"/>
+      <c r="AG30" s="3" t="n"/>
+      <c r="AH30" s="3" t="n"/>
+      <c r="AI30" s="3" t="n"/>
+      <c r="AJ30" s="3" t="n"/>
+      <c r="AK30" s="3" t="n"/>
+      <c r="AL30" s="3" t="n"/>
+      <c r="AM30" s="3" t="n"/>
+      <c r="AN30" s="3" t="n"/>
+      <c r="AO30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n"/>
@@ -1693,6 +2012,15 @@
       <c r="AD31" s="4" t="n"/>
       <c r="AE31" s="4" t="n"/>
       <c r="AF31" s="4" t="n"/>
+      <c r="AG31" s="4" t="n"/>
+      <c r="AH31" s="4" t="n"/>
+      <c r="AI31" s="4" t="n"/>
+      <c r="AJ31" s="4" t="n"/>
+      <c r="AK31" s="4" t="n"/>
+      <c r="AL31" s="4" t="n"/>
+      <c r="AM31" s="4" t="n"/>
+      <c r="AN31" s="4" t="n"/>
+      <c r="AO31" s="4" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n"/>
@@ -1727,6 +2055,15 @@
       <c r="AD32" s="3" t="n"/>
       <c r="AE32" s="3" t="n"/>
       <c r="AF32" s="3" t="n"/>
+      <c r="AG32" s="3" t="n"/>
+      <c r="AH32" s="3" t="n"/>
+      <c r="AI32" s="3" t="n"/>
+      <c r="AJ32" s="3" t="n"/>
+      <c r="AK32" s="3" t="n"/>
+      <c r="AL32" s="3" t="n"/>
+      <c r="AM32" s="3" t="n"/>
+      <c r="AN32" s="3" t="n"/>
+      <c r="AO32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n"/>
@@ -1761,6 +2098,15 @@
       <c r="AD33" s="4" t="n"/>
       <c r="AE33" s="4" t="n"/>
       <c r="AF33" s="4" t="n"/>
+      <c r="AG33" s="4" t="n"/>
+      <c r="AH33" s="4" t="n"/>
+      <c r="AI33" s="4" t="n"/>
+      <c r="AJ33" s="4" t="n"/>
+      <c r="AK33" s="4" t="n"/>
+      <c r="AL33" s="4" t="n"/>
+      <c r="AM33" s="4" t="n"/>
+      <c r="AN33" s="4" t="n"/>
+      <c r="AO33" s="4" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n"/>
@@ -1795,6 +2141,15 @@
       <c r="AD34" s="3" t="n"/>
       <c r="AE34" s="3" t="n"/>
       <c r="AF34" s="3" t="n"/>
+      <c r="AG34" s="3" t="n"/>
+      <c r="AH34" s="3" t="n"/>
+      <c r="AI34" s="3" t="n"/>
+      <c r="AJ34" s="3" t="n"/>
+      <c r="AK34" s="3" t="n"/>
+      <c r="AL34" s="3" t="n"/>
+      <c r="AM34" s="3" t="n"/>
+      <c r="AN34" s="3" t="n"/>
+      <c r="AO34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="n"/>
@@ -1829,6 +2184,15 @@
       <c r="AD35" s="4" t="n"/>
       <c r="AE35" s="4" t="n"/>
       <c r="AF35" s="4" t="n"/>
+      <c r="AG35" s="4" t="n"/>
+      <c r="AH35" s="4" t="n"/>
+      <c r="AI35" s="4" t="n"/>
+      <c r="AJ35" s="4" t="n"/>
+      <c r="AK35" s="4" t="n"/>
+      <c r="AL35" s="4" t="n"/>
+      <c r="AM35" s="4" t="n"/>
+      <c r="AN35" s="4" t="n"/>
+      <c r="AO35" s="4" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n"/>
@@ -1863,6 +2227,15 @@
       <c r="AD36" s="3" t="n"/>
       <c r="AE36" s="3" t="n"/>
       <c r="AF36" s="3" t="n"/>
+      <c r="AG36" s="3" t="n"/>
+      <c r="AH36" s="3" t="n"/>
+      <c r="AI36" s="3" t="n"/>
+      <c r="AJ36" s="3" t="n"/>
+      <c r="AK36" s="3" t="n"/>
+      <c r="AL36" s="3" t="n"/>
+      <c r="AM36" s="3" t="n"/>
+      <c r="AN36" s="3" t="n"/>
+      <c r="AO36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="4" t="n"/>
@@ -1897,6 +2270,15 @@
       <c r="AD37" s="4" t="n"/>
       <c r="AE37" s="4" t="n"/>
       <c r="AF37" s="4" t="n"/>
+      <c r="AG37" s="4" t="n"/>
+      <c r="AH37" s="4" t="n"/>
+      <c r="AI37" s="4" t="n"/>
+      <c r="AJ37" s="4" t="n"/>
+      <c r="AK37" s="4" t="n"/>
+      <c r="AL37" s="4" t="n"/>
+      <c r="AM37" s="4" t="n"/>
+      <c r="AN37" s="4" t="n"/>
+      <c r="AO37" s="4" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n"/>
@@ -1931,6 +2313,15 @@
       <c r="AD38" s="3" t="n"/>
       <c r="AE38" s="3" t="n"/>
       <c r="AF38" s="3" t="n"/>
+      <c r="AG38" s="3" t="n"/>
+      <c r="AH38" s="3" t="n"/>
+      <c r="AI38" s="3" t="n"/>
+      <c r="AJ38" s="3" t="n"/>
+      <c r="AK38" s="3" t="n"/>
+      <c r="AL38" s="3" t="n"/>
+      <c r="AM38" s="3" t="n"/>
+      <c r="AN38" s="3" t="n"/>
+      <c r="AO38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="4" t="n"/>
@@ -1965,6 +2356,15 @@
       <c r="AD39" s="4" t="n"/>
       <c r="AE39" s="4" t="n"/>
       <c r="AF39" s="4" t="n"/>
+      <c r="AG39" s="4" t="n"/>
+      <c r="AH39" s="4" t="n"/>
+      <c r="AI39" s="4" t="n"/>
+      <c r="AJ39" s="4" t="n"/>
+      <c r="AK39" s="4" t="n"/>
+      <c r="AL39" s="4" t="n"/>
+      <c r="AM39" s="4" t="n"/>
+      <c r="AN39" s="4" t="n"/>
+      <c r="AO39" s="4" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n"/>
@@ -1999,6 +2399,15 @@
       <c r="AD40" s="3" t="n"/>
       <c r="AE40" s="3" t="n"/>
       <c r="AF40" s="3" t="n"/>
+      <c r="AG40" s="3" t="n"/>
+      <c r="AH40" s="3" t="n"/>
+      <c r="AI40" s="3" t="n"/>
+      <c r="AJ40" s="3" t="n"/>
+      <c r="AK40" s="3" t="n"/>
+      <c r="AL40" s="3" t="n"/>
+      <c r="AM40" s="3" t="n"/>
+      <c r="AN40" s="3" t="n"/>
+      <c r="AO40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="4" t="n"/>
@@ -2033,6 +2442,15 @@
       <c r="AD41" s="4" t="n"/>
       <c r="AE41" s="4" t="n"/>
       <c r="AF41" s="4" t="n"/>
+      <c r="AG41" s="4" t="n"/>
+      <c r="AH41" s="4" t="n"/>
+      <c r="AI41" s="4" t="n"/>
+      <c r="AJ41" s="4" t="n"/>
+      <c r="AK41" s="4" t="n"/>
+      <c r="AL41" s="4" t="n"/>
+      <c r="AM41" s="4" t="n"/>
+      <c r="AN41" s="4" t="n"/>
+      <c r="AO41" s="4" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n"/>
@@ -2067,6 +2485,15 @@
       <c r="AD42" s="3" t="n"/>
       <c r="AE42" s="3" t="n"/>
       <c r="AF42" s="3" t="n"/>
+      <c r="AG42" s="3" t="n"/>
+      <c r="AH42" s="3" t="n"/>
+      <c r="AI42" s="3" t="n"/>
+      <c r="AJ42" s="3" t="n"/>
+      <c r="AK42" s="3" t="n"/>
+      <c r="AL42" s="3" t="n"/>
+      <c r="AM42" s="3" t="n"/>
+      <c r="AN42" s="3" t="n"/>
+      <c r="AO42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n"/>
@@ -2101,6 +2528,15 @@
       <c r="AD43" s="4" t="n"/>
       <c r="AE43" s="4" t="n"/>
       <c r="AF43" s="4" t="n"/>
+      <c r="AG43" s="4" t="n"/>
+      <c r="AH43" s="4" t="n"/>
+      <c r="AI43" s="4" t="n"/>
+      <c r="AJ43" s="4" t="n"/>
+      <c r="AK43" s="4" t="n"/>
+      <c r="AL43" s="4" t="n"/>
+      <c r="AM43" s="4" t="n"/>
+      <c r="AN43" s="4" t="n"/>
+      <c r="AO43" s="4" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n"/>
@@ -2135,6 +2571,15 @@
       <c r="AD44" s="3" t="n"/>
       <c r="AE44" s="3" t="n"/>
       <c r="AF44" s="3" t="n"/>
+      <c r="AG44" s="3" t="n"/>
+      <c r="AH44" s="3" t="n"/>
+      <c r="AI44" s="3" t="n"/>
+      <c r="AJ44" s="3" t="n"/>
+      <c r="AK44" s="3" t="n"/>
+      <c r="AL44" s="3" t="n"/>
+      <c r="AM44" s="3" t="n"/>
+      <c r="AN44" s="3" t="n"/>
+      <c r="AO44" s="3" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="4" t="n"/>
@@ -2169,6 +2614,15 @@
       <c r="AD45" s="4" t="n"/>
       <c r="AE45" s="4" t="n"/>
       <c r="AF45" s="4" t="n"/>
+      <c r="AG45" s="4" t="n"/>
+      <c r="AH45" s="4" t="n"/>
+      <c r="AI45" s="4" t="n"/>
+      <c r="AJ45" s="4" t="n"/>
+      <c r="AK45" s="4" t="n"/>
+      <c r="AL45" s="4" t="n"/>
+      <c r="AM45" s="4" t="n"/>
+      <c r="AN45" s="4" t="n"/>
+      <c r="AO45" s="4" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n"/>
@@ -2203,6 +2657,15 @@
       <c r="AD46" s="3" t="n"/>
       <c r="AE46" s="3" t="n"/>
       <c r="AF46" s="3" t="n"/>
+      <c r="AG46" s="3" t="n"/>
+      <c r="AH46" s="3" t="n"/>
+      <c r="AI46" s="3" t="n"/>
+      <c r="AJ46" s="3" t="n"/>
+      <c r="AK46" s="3" t="n"/>
+      <c r="AL46" s="3" t="n"/>
+      <c r="AM46" s="3" t="n"/>
+      <c r="AN46" s="3" t="n"/>
+      <c r="AO46" s="3" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="4" t="n"/>
@@ -2237,6 +2700,15 @@
       <c r="AD47" s="4" t="n"/>
       <c r="AE47" s="4" t="n"/>
       <c r="AF47" s="4" t="n"/>
+      <c r="AG47" s="4" t="n"/>
+      <c r="AH47" s="4" t="n"/>
+      <c r="AI47" s="4" t="n"/>
+      <c r="AJ47" s="4" t="n"/>
+      <c r="AK47" s="4" t="n"/>
+      <c r="AL47" s="4" t="n"/>
+      <c r="AM47" s="4" t="n"/>
+      <c r="AN47" s="4" t="n"/>
+      <c r="AO47" s="4" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n"/>
@@ -2271,6 +2743,15 @@
       <c r="AD48" s="3" t="n"/>
       <c r="AE48" s="3" t="n"/>
       <c r="AF48" s="3" t="n"/>
+      <c r="AG48" s="3" t="n"/>
+      <c r="AH48" s="3" t="n"/>
+      <c r="AI48" s="3" t="n"/>
+      <c r="AJ48" s="3" t="n"/>
+      <c r="AK48" s="3" t="n"/>
+      <c r="AL48" s="3" t="n"/>
+      <c r="AM48" s="3" t="n"/>
+      <c r="AN48" s="3" t="n"/>
+      <c r="AO48" s="3" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="4" t="n"/>
@@ -2305,6 +2786,15 @@
       <c r="AD49" s="4" t="n"/>
       <c r="AE49" s="4" t="n"/>
       <c r="AF49" s="4" t="n"/>
+      <c r="AG49" s="4" t="n"/>
+      <c r="AH49" s="4" t="n"/>
+      <c r="AI49" s="4" t="n"/>
+      <c r="AJ49" s="4" t="n"/>
+      <c r="AK49" s="4" t="n"/>
+      <c r="AL49" s="4" t="n"/>
+      <c r="AM49" s="4" t="n"/>
+      <c r="AN49" s="4" t="n"/>
+      <c r="AO49" s="4" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="3" t="n"/>
@@ -2339,6 +2829,15 @@
       <c r="AD50" s="3" t="n"/>
       <c r="AE50" s="3" t="n"/>
       <c r="AF50" s="3" t="n"/>
+      <c r="AG50" s="3" t="n"/>
+      <c r="AH50" s="3" t="n"/>
+      <c r="AI50" s="3" t="n"/>
+      <c r="AJ50" s="3" t="n"/>
+      <c r="AK50" s="3" t="n"/>
+      <c r="AL50" s="3" t="n"/>
+      <c r="AM50" s="3" t="n"/>
+      <c r="AN50" s="3" t="n"/>
+      <c r="AO50" s="3" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="4" t="n"/>
@@ -2373,6 +2872,15 @@
       <c r="AD51" s="4" t="n"/>
       <c r="AE51" s="4" t="n"/>
       <c r="AF51" s="4" t="n"/>
+      <c r="AG51" s="4" t="n"/>
+      <c r="AH51" s="4" t="n"/>
+      <c r="AI51" s="4" t="n"/>
+      <c r="AJ51" s="4" t="n"/>
+      <c r="AK51" s="4" t="n"/>
+      <c r="AL51" s="4" t="n"/>
+      <c r="AM51" s="4" t="n"/>
+      <c r="AN51" s="4" t="n"/>
+      <c r="AO51" s="4" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="3" t="n"/>
@@ -2407,6 +2915,15 @@
       <c r="AD52" s="3" t="n"/>
       <c r="AE52" s="3" t="n"/>
       <c r="AF52" s="3" t="n"/>
+      <c r="AG52" s="3" t="n"/>
+      <c r="AH52" s="3" t="n"/>
+      <c r="AI52" s="3" t="n"/>
+      <c r="AJ52" s="3" t="n"/>
+      <c r="AK52" s="3" t="n"/>
+      <c r="AL52" s="3" t="n"/>
+      <c r="AM52" s="3" t="n"/>
+      <c r="AN52" s="3" t="n"/>
+      <c r="AO52" s="3" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="4" t="n"/>
@@ -2441,6 +2958,15 @@
       <c r="AD53" s="4" t="n"/>
       <c r="AE53" s="4" t="n"/>
       <c r="AF53" s="4" t="n"/>
+      <c r="AG53" s="4" t="n"/>
+      <c r="AH53" s="4" t="n"/>
+      <c r="AI53" s="4" t="n"/>
+      <c r="AJ53" s="4" t="n"/>
+      <c r="AK53" s="4" t="n"/>
+      <c r="AL53" s="4" t="n"/>
+      <c r="AM53" s="4" t="n"/>
+      <c r="AN53" s="4" t="n"/>
+      <c r="AO53" s="4" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n"/>
@@ -2475,6 +3001,15 @@
       <c r="AD54" s="3" t="n"/>
       <c r="AE54" s="3" t="n"/>
       <c r="AF54" s="3" t="n"/>
+      <c r="AG54" s="3" t="n"/>
+      <c r="AH54" s="3" t="n"/>
+      <c r="AI54" s="3" t="n"/>
+      <c r="AJ54" s="3" t="n"/>
+      <c r="AK54" s="3" t="n"/>
+      <c r="AL54" s="3" t="n"/>
+      <c r="AM54" s="3" t="n"/>
+      <c r="AN54" s="3" t="n"/>
+      <c r="AO54" s="3" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="4" t="n"/>
@@ -2509,6 +3044,15 @@
       <c r="AD55" s="4" t="n"/>
       <c r="AE55" s="4" t="n"/>
       <c r="AF55" s="4" t="n"/>
+      <c r="AG55" s="4" t="n"/>
+      <c r="AH55" s="4" t="n"/>
+      <c r="AI55" s="4" t="n"/>
+      <c r="AJ55" s="4" t="n"/>
+      <c r="AK55" s="4" t="n"/>
+      <c r="AL55" s="4" t="n"/>
+      <c r="AM55" s="4" t="n"/>
+      <c r="AN55" s="4" t="n"/>
+      <c r="AO55" s="4" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="3" t="n"/>
@@ -2543,6 +3087,15 @@
       <c r="AD56" s="3" t="n"/>
       <c r="AE56" s="3" t="n"/>
       <c r="AF56" s="3" t="n"/>
+      <c r="AG56" s="3" t="n"/>
+      <c r="AH56" s="3" t="n"/>
+      <c r="AI56" s="3" t="n"/>
+      <c r="AJ56" s="3" t="n"/>
+      <c r="AK56" s="3" t="n"/>
+      <c r="AL56" s="3" t="n"/>
+      <c r="AM56" s="3" t="n"/>
+      <c r="AN56" s="3" t="n"/>
+      <c r="AO56" s="3" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="4" t="n"/>
@@ -2577,6 +3130,15 @@
       <c r="AD57" s="4" t="n"/>
       <c r="AE57" s="4" t="n"/>
       <c r="AF57" s="4" t="n"/>
+      <c r="AG57" s="4" t="n"/>
+      <c r="AH57" s="4" t="n"/>
+      <c r="AI57" s="4" t="n"/>
+      <c r="AJ57" s="4" t="n"/>
+      <c r="AK57" s="4" t="n"/>
+      <c r="AL57" s="4" t="n"/>
+      <c r="AM57" s="4" t="n"/>
+      <c r="AN57" s="4" t="n"/>
+      <c r="AO57" s="4" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="3" t="n"/>
@@ -2611,6 +3173,15 @@
       <c r="AD58" s="3" t="n"/>
       <c r="AE58" s="3" t="n"/>
       <c r="AF58" s="3" t="n"/>
+      <c r="AG58" s="3" t="n"/>
+      <c r="AH58" s="3" t="n"/>
+      <c r="AI58" s="3" t="n"/>
+      <c r="AJ58" s="3" t="n"/>
+      <c r="AK58" s="3" t="n"/>
+      <c r="AL58" s="3" t="n"/>
+      <c r="AM58" s="3" t="n"/>
+      <c r="AN58" s="3" t="n"/>
+      <c r="AO58" s="3" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="4" t="n"/>
@@ -2645,6 +3216,15 @@
       <c r="AD59" s="4" t="n"/>
       <c r="AE59" s="4" t="n"/>
       <c r="AF59" s="4" t="n"/>
+      <c r="AG59" s="4" t="n"/>
+      <c r="AH59" s="4" t="n"/>
+      <c r="AI59" s="4" t="n"/>
+      <c r="AJ59" s="4" t="n"/>
+      <c r="AK59" s="4" t="n"/>
+      <c r="AL59" s="4" t="n"/>
+      <c r="AM59" s="4" t="n"/>
+      <c r="AN59" s="4" t="n"/>
+      <c r="AO59" s="4" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="3" t="n"/>
@@ -2679,6 +3259,15 @@
       <c r="AD60" s="3" t="n"/>
       <c r="AE60" s="3" t="n"/>
       <c r="AF60" s="3" t="n"/>
+      <c r="AG60" s="3" t="n"/>
+      <c r="AH60" s="3" t="n"/>
+      <c r="AI60" s="3" t="n"/>
+      <c r="AJ60" s="3" t="n"/>
+      <c r="AK60" s="3" t="n"/>
+      <c r="AL60" s="3" t="n"/>
+      <c r="AM60" s="3" t="n"/>
+      <c r="AN60" s="3" t="n"/>
+      <c r="AO60" s="3" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="4" t="n"/>
@@ -2713,6 +3302,15 @@
       <c r="AD61" s="4" t="n"/>
       <c r="AE61" s="4" t="n"/>
       <c r="AF61" s="4" t="n"/>
+      <c r="AG61" s="4" t="n"/>
+      <c r="AH61" s="4" t="n"/>
+      <c r="AI61" s="4" t="n"/>
+      <c r="AJ61" s="4" t="n"/>
+      <c r="AK61" s="4" t="n"/>
+      <c r="AL61" s="4" t="n"/>
+      <c r="AM61" s="4" t="n"/>
+      <c r="AN61" s="4" t="n"/>
+      <c r="AO61" s="4" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="3" t="n"/>
@@ -2747,6 +3345,15 @@
       <c r="AD62" s="3" t="n"/>
       <c r="AE62" s="3" t="n"/>
       <c r="AF62" s="3" t="n"/>
+      <c r="AG62" s="3" t="n"/>
+      <c r="AH62" s="3" t="n"/>
+      <c r="AI62" s="3" t="n"/>
+      <c r="AJ62" s="3" t="n"/>
+      <c r="AK62" s="3" t="n"/>
+      <c r="AL62" s="3" t="n"/>
+      <c r="AM62" s="3" t="n"/>
+      <c r="AN62" s="3" t="n"/>
+      <c r="AO62" s="3" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="4" t="n"/>
@@ -2781,6 +3388,15 @@
       <c r="AD63" s="4" t="n"/>
       <c r="AE63" s="4" t="n"/>
       <c r="AF63" s="4" t="n"/>
+      <c r="AG63" s="4" t="n"/>
+      <c r="AH63" s="4" t="n"/>
+      <c r="AI63" s="4" t="n"/>
+      <c r="AJ63" s="4" t="n"/>
+      <c r="AK63" s="4" t="n"/>
+      <c r="AL63" s="4" t="n"/>
+      <c r="AM63" s="4" t="n"/>
+      <c r="AN63" s="4" t="n"/>
+      <c r="AO63" s="4" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="3" t="n"/>
@@ -2815,6 +3431,15 @@
       <c r="AD64" s="3" t="n"/>
       <c r="AE64" s="3" t="n"/>
       <c r="AF64" s="3" t="n"/>
+      <c r="AG64" s="3" t="n"/>
+      <c r="AH64" s="3" t="n"/>
+      <c r="AI64" s="3" t="n"/>
+      <c r="AJ64" s="3" t="n"/>
+      <c r="AK64" s="3" t="n"/>
+      <c r="AL64" s="3" t="n"/>
+      <c r="AM64" s="3" t="n"/>
+      <c r="AN64" s="3" t="n"/>
+      <c r="AO64" s="3" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="4" t="n"/>
@@ -2849,6 +3474,15 @@
       <c r="AD65" s="4" t="n"/>
       <c r="AE65" s="4" t="n"/>
       <c r="AF65" s="4" t="n"/>
+      <c r="AG65" s="4" t="n"/>
+      <c r="AH65" s="4" t="n"/>
+      <c r="AI65" s="4" t="n"/>
+      <c r="AJ65" s="4" t="n"/>
+      <c r="AK65" s="4" t="n"/>
+      <c r="AL65" s="4" t="n"/>
+      <c r="AM65" s="4" t="n"/>
+      <c r="AN65" s="4" t="n"/>
+      <c r="AO65" s="4" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="3" t="n"/>
@@ -2883,6 +3517,15 @@
       <c r="AD66" s="3" t="n"/>
       <c r="AE66" s="3" t="n"/>
       <c r="AF66" s="3" t="n"/>
+      <c r="AG66" s="3" t="n"/>
+      <c r="AH66" s="3" t="n"/>
+      <c r="AI66" s="3" t="n"/>
+      <c r="AJ66" s="3" t="n"/>
+      <c r="AK66" s="3" t="n"/>
+      <c r="AL66" s="3" t="n"/>
+      <c r="AM66" s="3" t="n"/>
+      <c r="AN66" s="3" t="n"/>
+      <c r="AO66" s="3" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="4" t="n"/>
@@ -2917,6 +3560,15 @@
       <c r="AD67" s="4" t="n"/>
       <c r="AE67" s="4" t="n"/>
       <c r="AF67" s="4" t="n"/>
+      <c r="AG67" s="4" t="n"/>
+      <c r="AH67" s="4" t="n"/>
+      <c r="AI67" s="4" t="n"/>
+      <c r="AJ67" s="4" t="n"/>
+      <c r="AK67" s="4" t="n"/>
+      <c r="AL67" s="4" t="n"/>
+      <c r="AM67" s="4" t="n"/>
+      <c r="AN67" s="4" t="n"/>
+      <c r="AO67" s="4" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="3" t="n"/>
@@ -2951,6 +3603,15 @@
       <c r="AD68" s="3" t="n"/>
       <c r="AE68" s="3" t="n"/>
       <c r="AF68" s="3" t="n"/>
+      <c r="AG68" s="3" t="n"/>
+      <c r="AH68" s="3" t="n"/>
+      <c r="AI68" s="3" t="n"/>
+      <c r="AJ68" s="3" t="n"/>
+      <c r="AK68" s="3" t="n"/>
+      <c r="AL68" s="3" t="n"/>
+      <c r="AM68" s="3" t="n"/>
+      <c r="AN68" s="3" t="n"/>
+      <c r="AO68" s="3" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="4" t="n"/>
@@ -2985,6 +3646,15 @@
       <c r="AD69" s="4" t="n"/>
       <c r="AE69" s="4" t="n"/>
       <c r="AF69" s="4" t="n"/>
+      <c r="AG69" s="4" t="n"/>
+      <c r="AH69" s="4" t="n"/>
+      <c r="AI69" s="4" t="n"/>
+      <c r="AJ69" s="4" t="n"/>
+      <c r="AK69" s="4" t="n"/>
+      <c r="AL69" s="4" t="n"/>
+      <c r="AM69" s="4" t="n"/>
+      <c r="AN69" s="4" t="n"/>
+      <c r="AO69" s="4" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="3" t="n"/>
@@ -3019,6 +3689,15 @@
       <c r="AD70" s="3" t="n"/>
       <c r="AE70" s="3" t="n"/>
       <c r="AF70" s="3" t="n"/>
+      <c r="AG70" s="3" t="n"/>
+      <c r="AH70" s="3" t="n"/>
+      <c r="AI70" s="3" t="n"/>
+      <c r="AJ70" s="3" t="n"/>
+      <c r="AK70" s="3" t="n"/>
+      <c r="AL70" s="3" t="n"/>
+      <c r="AM70" s="3" t="n"/>
+      <c r="AN70" s="3" t="n"/>
+      <c r="AO70" s="3" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="4" t="n"/>
@@ -3053,6 +3732,15 @@
       <c r="AD71" s="4" t="n"/>
       <c r="AE71" s="4" t="n"/>
       <c r="AF71" s="4" t="n"/>
+      <c r="AG71" s="4" t="n"/>
+      <c r="AH71" s="4" t="n"/>
+      <c r="AI71" s="4" t="n"/>
+      <c r="AJ71" s="4" t="n"/>
+      <c r="AK71" s="4" t="n"/>
+      <c r="AL71" s="4" t="n"/>
+      <c r="AM71" s="4" t="n"/>
+      <c r="AN71" s="4" t="n"/>
+      <c r="AO71" s="4" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="3" t="n"/>
@@ -3087,6 +3775,15 @@
       <c r="AD72" s="3" t="n"/>
       <c r="AE72" s="3" t="n"/>
       <c r="AF72" s="3" t="n"/>
+      <c r="AG72" s="3" t="n"/>
+      <c r="AH72" s="3" t="n"/>
+      <c r="AI72" s="3" t="n"/>
+      <c r="AJ72" s="3" t="n"/>
+      <c r="AK72" s="3" t="n"/>
+      <c r="AL72" s="3" t="n"/>
+      <c r="AM72" s="3" t="n"/>
+      <c r="AN72" s="3" t="n"/>
+      <c r="AO72" s="3" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="4" t="n"/>
@@ -3121,6 +3818,15 @@
       <c r="AD73" s="4" t="n"/>
       <c r="AE73" s="4" t="n"/>
       <c r="AF73" s="4" t="n"/>
+      <c r="AG73" s="4" t="n"/>
+      <c r="AH73" s="4" t="n"/>
+      <c r="AI73" s="4" t="n"/>
+      <c r="AJ73" s="4" t="n"/>
+      <c r="AK73" s="4" t="n"/>
+      <c r="AL73" s="4" t="n"/>
+      <c r="AM73" s="4" t="n"/>
+      <c r="AN73" s="4" t="n"/>
+      <c r="AO73" s="4" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="3" t="n"/>
@@ -3155,6 +3861,15 @@
       <c r="AD74" s="3" t="n"/>
       <c r="AE74" s="3" t="n"/>
       <c r="AF74" s="3" t="n"/>
+      <c r="AG74" s="3" t="n"/>
+      <c r="AH74" s="3" t="n"/>
+      <c r="AI74" s="3" t="n"/>
+      <c r="AJ74" s="3" t="n"/>
+      <c r="AK74" s="3" t="n"/>
+      <c r="AL74" s="3" t="n"/>
+      <c r="AM74" s="3" t="n"/>
+      <c r="AN74" s="3" t="n"/>
+      <c r="AO74" s="3" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="4" t="n"/>
@@ -3189,6 +3904,15 @@
       <c r="AD75" s="4" t="n"/>
       <c r="AE75" s="4" t="n"/>
       <c r="AF75" s="4" t="n"/>
+      <c r="AG75" s="4" t="n"/>
+      <c r="AH75" s="4" t="n"/>
+      <c r="AI75" s="4" t="n"/>
+      <c r="AJ75" s="4" t="n"/>
+      <c r="AK75" s="4" t="n"/>
+      <c r="AL75" s="4" t="n"/>
+      <c r="AM75" s="4" t="n"/>
+      <c r="AN75" s="4" t="n"/>
+      <c r="AO75" s="4" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="3" t="n"/>
@@ -3223,6 +3947,15 @@
       <c r="AD76" s="3" t="n"/>
       <c r="AE76" s="3" t="n"/>
       <c r="AF76" s="3" t="n"/>
+      <c r="AG76" s="3" t="n"/>
+      <c r="AH76" s="3" t="n"/>
+      <c r="AI76" s="3" t="n"/>
+      <c r="AJ76" s="3" t="n"/>
+      <c r="AK76" s="3" t="n"/>
+      <c r="AL76" s="3" t="n"/>
+      <c r="AM76" s="3" t="n"/>
+      <c r="AN76" s="3" t="n"/>
+      <c r="AO76" s="3" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="4" t="n"/>
@@ -3257,6 +3990,15 @@
       <c r="AD77" s="4" t="n"/>
       <c r="AE77" s="4" t="n"/>
       <c r="AF77" s="4" t="n"/>
+      <c r="AG77" s="4" t="n"/>
+      <c r="AH77" s="4" t="n"/>
+      <c r="AI77" s="4" t="n"/>
+      <c r="AJ77" s="4" t="n"/>
+      <c r="AK77" s="4" t="n"/>
+      <c r="AL77" s="4" t="n"/>
+      <c r="AM77" s="4" t="n"/>
+      <c r="AN77" s="4" t="n"/>
+      <c r="AO77" s="4" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="3" t="n"/>
@@ -3291,6 +4033,15 @@
       <c r="AD78" s="3" t="n"/>
       <c r="AE78" s="3" t="n"/>
       <c r="AF78" s="3" t="n"/>
+      <c r="AG78" s="3" t="n"/>
+      <c r="AH78" s="3" t="n"/>
+      <c r="AI78" s="3" t="n"/>
+      <c r="AJ78" s="3" t="n"/>
+      <c r="AK78" s="3" t="n"/>
+      <c r="AL78" s="3" t="n"/>
+      <c r="AM78" s="3" t="n"/>
+      <c r="AN78" s="3" t="n"/>
+      <c r="AO78" s="3" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="4" t="n"/>
@@ -3325,6 +4076,15 @@
       <c r="AD79" s="4" t="n"/>
       <c r="AE79" s="4" t="n"/>
       <c r="AF79" s="4" t="n"/>
+      <c r="AG79" s="4" t="n"/>
+      <c r="AH79" s="4" t="n"/>
+      <c r="AI79" s="4" t="n"/>
+      <c r="AJ79" s="4" t="n"/>
+      <c r="AK79" s="4" t="n"/>
+      <c r="AL79" s="4" t="n"/>
+      <c r="AM79" s="4" t="n"/>
+      <c r="AN79" s="4" t="n"/>
+      <c r="AO79" s="4" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="3" t="n"/>
@@ -3359,6 +4119,15 @@
       <c r="AD80" s="3" t="n"/>
       <c r="AE80" s="3" t="n"/>
       <c r="AF80" s="3" t="n"/>
+      <c r="AG80" s="3" t="n"/>
+      <c r="AH80" s="3" t="n"/>
+      <c r="AI80" s="3" t="n"/>
+      <c r="AJ80" s="3" t="n"/>
+      <c r="AK80" s="3" t="n"/>
+      <c r="AL80" s="3" t="n"/>
+      <c r="AM80" s="3" t="n"/>
+      <c r="AN80" s="3" t="n"/>
+      <c r="AO80" s="3" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="4" t="n"/>
@@ -3393,6 +4162,15 @@
       <c r="AD81" s="4" t="n"/>
       <c r="AE81" s="4" t="n"/>
       <c r="AF81" s="4" t="n"/>
+      <c r="AG81" s="4" t="n"/>
+      <c r="AH81" s="4" t="n"/>
+      <c r="AI81" s="4" t="n"/>
+      <c r="AJ81" s="4" t="n"/>
+      <c r="AK81" s="4" t="n"/>
+      <c r="AL81" s="4" t="n"/>
+      <c r="AM81" s="4" t="n"/>
+      <c r="AN81" s="4" t="n"/>
+      <c r="AO81" s="4" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="3" t="n"/>
@@ -3427,6 +4205,15 @@
       <c r="AD82" s="3" t="n"/>
       <c r="AE82" s="3" t="n"/>
       <c r="AF82" s="3" t="n"/>
+      <c r="AG82" s="3" t="n"/>
+      <c r="AH82" s="3" t="n"/>
+      <c r="AI82" s="3" t="n"/>
+      <c r="AJ82" s="3" t="n"/>
+      <c r="AK82" s="3" t="n"/>
+      <c r="AL82" s="3" t="n"/>
+      <c r="AM82" s="3" t="n"/>
+      <c r="AN82" s="3" t="n"/>
+      <c r="AO82" s="3" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="4" t="n"/>
@@ -3461,6 +4248,15 @@
       <c r="AD83" s="4" t="n"/>
       <c r="AE83" s="4" t="n"/>
       <c r="AF83" s="4" t="n"/>
+      <c r="AG83" s="4" t="n"/>
+      <c r="AH83" s="4" t="n"/>
+      <c r="AI83" s="4" t="n"/>
+      <c r="AJ83" s="4" t="n"/>
+      <c r="AK83" s="4" t="n"/>
+      <c r="AL83" s="4" t="n"/>
+      <c r="AM83" s="4" t="n"/>
+      <c r="AN83" s="4" t="n"/>
+      <c r="AO83" s="4" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="3" t="n"/>
@@ -3495,6 +4291,15 @@
       <c r="AD84" s="3" t="n"/>
       <c r="AE84" s="3" t="n"/>
       <c r="AF84" s="3" t="n"/>
+      <c r="AG84" s="3" t="n"/>
+      <c r="AH84" s="3" t="n"/>
+      <c r="AI84" s="3" t="n"/>
+      <c r="AJ84" s="3" t="n"/>
+      <c r="AK84" s="3" t="n"/>
+      <c r="AL84" s="3" t="n"/>
+      <c r="AM84" s="3" t="n"/>
+      <c r="AN84" s="3" t="n"/>
+      <c r="AO84" s="3" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="4" t="n"/>
@@ -3529,6 +4334,15 @@
       <c r="AD85" s="4" t="n"/>
       <c r="AE85" s="4" t="n"/>
       <c r="AF85" s="4" t="n"/>
+      <c r="AG85" s="4" t="n"/>
+      <c r="AH85" s="4" t="n"/>
+      <c r="AI85" s="4" t="n"/>
+      <c r="AJ85" s="4" t="n"/>
+      <c r="AK85" s="4" t="n"/>
+      <c r="AL85" s="4" t="n"/>
+      <c r="AM85" s="4" t="n"/>
+      <c r="AN85" s="4" t="n"/>
+      <c r="AO85" s="4" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="3" t="n"/>
@@ -3563,6 +4377,15 @@
       <c r="AD86" s="3" t="n"/>
       <c r="AE86" s="3" t="n"/>
       <c r="AF86" s="3" t="n"/>
+      <c r="AG86" s="3" t="n"/>
+      <c r="AH86" s="3" t="n"/>
+      <c r="AI86" s="3" t="n"/>
+      <c r="AJ86" s="3" t="n"/>
+      <c r="AK86" s="3" t="n"/>
+      <c r="AL86" s="3" t="n"/>
+      <c r="AM86" s="3" t="n"/>
+      <c r="AN86" s="3" t="n"/>
+      <c r="AO86" s="3" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="4" t="n"/>
@@ -3597,6 +4420,15 @@
       <c r="AD87" s="4" t="n"/>
       <c r="AE87" s="4" t="n"/>
       <c r="AF87" s="4" t="n"/>
+      <c r="AG87" s="4" t="n"/>
+      <c r="AH87" s="4" t="n"/>
+      <c r="AI87" s="4" t="n"/>
+      <c r="AJ87" s="4" t="n"/>
+      <c r="AK87" s="4" t="n"/>
+      <c r="AL87" s="4" t="n"/>
+      <c r="AM87" s="4" t="n"/>
+      <c r="AN87" s="4" t="n"/>
+      <c r="AO87" s="4" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="3" t="n"/>
@@ -3631,6 +4463,15 @@
       <c r="AD88" s="3" t="n"/>
       <c r="AE88" s="3" t="n"/>
       <c r="AF88" s="3" t="n"/>
+      <c r="AG88" s="3" t="n"/>
+      <c r="AH88" s="3" t="n"/>
+      <c r="AI88" s="3" t="n"/>
+      <c r="AJ88" s="3" t="n"/>
+      <c r="AK88" s="3" t="n"/>
+      <c r="AL88" s="3" t="n"/>
+      <c r="AM88" s="3" t="n"/>
+      <c r="AN88" s="3" t="n"/>
+      <c r="AO88" s="3" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="4" t="n"/>
@@ -3665,6 +4506,15 @@
       <c r="AD89" s="4" t="n"/>
       <c r="AE89" s="4" t="n"/>
       <c r="AF89" s="4" t="n"/>
+      <c r="AG89" s="4" t="n"/>
+      <c r="AH89" s="4" t="n"/>
+      <c r="AI89" s="4" t="n"/>
+      <c r="AJ89" s="4" t="n"/>
+      <c r="AK89" s="4" t="n"/>
+      <c r="AL89" s="4" t="n"/>
+      <c r="AM89" s="4" t="n"/>
+      <c r="AN89" s="4" t="n"/>
+      <c r="AO89" s="4" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="3" t="n"/>
@@ -3699,6 +4549,15 @@
       <c r="AD90" s="3" t="n"/>
       <c r="AE90" s="3" t="n"/>
       <c r="AF90" s="3" t="n"/>
+      <c r="AG90" s="3" t="n"/>
+      <c r="AH90" s="3" t="n"/>
+      <c r="AI90" s="3" t="n"/>
+      <c r="AJ90" s="3" t="n"/>
+      <c r="AK90" s="3" t="n"/>
+      <c r="AL90" s="3" t="n"/>
+      <c r="AM90" s="3" t="n"/>
+      <c r="AN90" s="3" t="n"/>
+      <c r="AO90" s="3" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="4" t="n"/>
@@ -3733,6 +4592,15 @@
       <c r="AD91" s="4" t="n"/>
       <c r="AE91" s="4" t="n"/>
       <c r="AF91" s="4" t="n"/>
+      <c r="AG91" s="4" t="n"/>
+      <c r="AH91" s="4" t="n"/>
+      <c r="AI91" s="4" t="n"/>
+      <c r="AJ91" s="4" t="n"/>
+      <c r="AK91" s="4" t="n"/>
+      <c r="AL91" s="4" t="n"/>
+      <c r="AM91" s="4" t="n"/>
+      <c r="AN91" s="4" t="n"/>
+      <c r="AO91" s="4" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="3" t="n"/>
@@ -3767,6 +4635,15 @@
       <c r="AD92" s="3" t="n"/>
       <c r="AE92" s="3" t="n"/>
       <c r="AF92" s="3" t="n"/>
+      <c r="AG92" s="3" t="n"/>
+      <c r="AH92" s="3" t="n"/>
+      <c r="AI92" s="3" t="n"/>
+      <c r="AJ92" s="3" t="n"/>
+      <c r="AK92" s="3" t="n"/>
+      <c r="AL92" s="3" t="n"/>
+      <c r="AM92" s="3" t="n"/>
+      <c r="AN92" s="3" t="n"/>
+      <c r="AO92" s="3" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="4" t="n"/>
@@ -3801,6 +4678,15 @@
       <c r="AD93" s="4" t="n"/>
       <c r="AE93" s="4" t="n"/>
       <c r="AF93" s="4" t="n"/>
+      <c r="AG93" s="4" t="n"/>
+      <c r="AH93" s="4" t="n"/>
+      <c r="AI93" s="4" t="n"/>
+      <c r="AJ93" s="4" t="n"/>
+      <c r="AK93" s="4" t="n"/>
+      <c r="AL93" s="4" t="n"/>
+      <c r="AM93" s="4" t="n"/>
+      <c r="AN93" s="4" t="n"/>
+      <c r="AO93" s="4" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="3" t="n"/>
@@ -3835,6 +4721,15 @@
       <c r="AD94" s="3" t="n"/>
       <c r="AE94" s="3" t="n"/>
       <c r="AF94" s="3" t="n"/>
+      <c r="AG94" s="3" t="n"/>
+      <c r="AH94" s="3" t="n"/>
+      <c r="AI94" s="3" t="n"/>
+      <c r="AJ94" s="3" t="n"/>
+      <c r="AK94" s="3" t="n"/>
+      <c r="AL94" s="3" t="n"/>
+      <c r="AM94" s="3" t="n"/>
+      <c r="AN94" s="3" t="n"/>
+      <c r="AO94" s="3" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="4" t="n"/>
@@ -3869,6 +4764,15 @@
       <c r="AD95" s="4" t="n"/>
       <c r="AE95" s="4" t="n"/>
       <c r="AF95" s="4" t="n"/>
+      <c r="AG95" s="4" t="n"/>
+      <c r="AH95" s="4" t="n"/>
+      <c r="AI95" s="4" t="n"/>
+      <c r="AJ95" s="4" t="n"/>
+      <c r="AK95" s="4" t="n"/>
+      <c r="AL95" s="4" t="n"/>
+      <c r="AM95" s="4" t="n"/>
+      <c r="AN95" s="4" t="n"/>
+      <c r="AO95" s="4" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="3" t="n"/>
@@ -3903,6 +4807,15 @@
       <c r="AD96" s="3" t="n"/>
       <c r="AE96" s="3" t="n"/>
       <c r="AF96" s="3" t="n"/>
+      <c r="AG96" s="3" t="n"/>
+      <c r="AH96" s="3" t="n"/>
+      <c r="AI96" s="3" t="n"/>
+      <c r="AJ96" s="3" t="n"/>
+      <c r="AK96" s="3" t="n"/>
+      <c r="AL96" s="3" t="n"/>
+      <c r="AM96" s="3" t="n"/>
+      <c r="AN96" s="3" t="n"/>
+      <c r="AO96" s="3" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="4" t="n"/>
@@ -3937,6 +4850,15 @@
       <c r="AD97" s="4" t="n"/>
       <c r="AE97" s="4" t="n"/>
       <c r="AF97" s="4" t="n"/>
+      <c r="AG97" s="4" t="n"/>
+      <c r="AH97" s="4" t="n"/>
+      <c r="AI97" s="4" t="n"/>
+      <c r="AJ97" s="4" t="n"/>
+      <c r="AK97" s="4" t="n"/>
+      <c r="AL97" s="4" t="n"/>
+      <c r="AM97" s="4" t="n"/>
+      <c r="AN97" s="4" t="n"/>
+      <c r="AO97" s="4" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="3" t="n"/>
@@ -3971,6 +4893,15 @@
       <c r="AD98" s="3" t="n"/>
       <c r="AE98" s="3" t="n"/>
       <c r="AF98" s="3" t="n"/>
+      <c r="AG98" s="3" t="n"/>
+      <c r="AH98" s="3" t="n"/>
+      <c r="AI98" s="3" t="n"/>
+      <c r="AJ98" s="3" t="n"/>
+      <c r="AK98" s="3" t="n"/>
+      <c r="AL98" s="3" t="n"/>
+      <c r="AM98" s="3" t="n"/>
+      <c r="AN98" s="3" t="n"/>
+      <c r="AO98" s="3" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="4" t="n"/>
@@ -4005,6 +4936,15 @@
       <c r="AD99" s="4" t="n"/>
       <c r="AE99" s="4" t="n"/>
       <c r="AF99" s="4" t="n"/>
+      <c r="AG99" s="4" t="n"/>
+      <c r="AH99" s="4" t="n"/>
+      <c r="AI99" s="4" t="n"/>
+      <c r="AJ99" s="4" t="n"/>
+      <c r="AK99" s="4" t="n"/>
+      <c r="AL99" s="4" t="n"/>
+      <c r="AM99" s="4" t="n"/>
+      <c r="AN99" s="4" t="n"/>
+      <c r="AO99" s="4" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="3" t="n"/>
@@ -4039,6 +4979,15 @@
       <c r="AD100" s="3" t="n"/>
       <c r="AE100" s="3" t="n"/>
       <c r="AF100" s="3" t="n"/>
+      <c r="AG100" s="3" t="n"/>
+      <c r="AH100" s="3" t="n"/>
+      <c r="AI100" s="3" t="n"/>
+      <c r="AJ100" s="3" t="n"/>
+      <c r="AK100" s="3" t="n"/>
+      <c r="AL100" s="3" t="n"/>
+      <c r="AM100" s="3" t="n"/>
+      <c r="AN100" s="3" t="n"/>
+      <c r="AO100" s="3" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="4" t="n"/>
@@ -4073,6 +5022,15 @@
       <c r="AD101" s="4" t="n"/>
       <c r="AE101" s="4" t="n"/>
       <c r="AF101" s="4" t="n"/>
+      <c r="AG101" s="4" t="n"/>
+      <c r="AH101" s="4" t="n"/>
+      <c r="AI101" s="4" t="n"/>
+      <c r="AJ101" s="4" t="n"/>
+      <c r="AK101" s="4" t="n"/>
+      <c r="AL101" s="4" t="n"/>
+      <c r="AM101" s="4" t="n"/>
+      <c r="AN101" s="4" t="n"/>
+      <c r="AO101" s="4" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="3" t="n"/>
@@ -4107,6 +5065,15 @@
       <c r="AD102" s="3" t="n"/>
       <c r="AE102" s="3" t="n"/>
       <c r="AF102" s="3" t="n"/>
+      <c r="AG102" s="3" t="n"/>
+      <c r="AH102" s="3" t="n"/>
+      <c r="AI102" s="3" t="n"/>
+      <c r="AJ102" s="3" t="n"/>
+      <c r="AK102" s="3" t="n"/>
+      <c r="AL102" s="3" t="n"/>
+      <c r="AM102" s="3" t="n"/>
+      <c r="AN102" s="3" t="n"/>
+      <c r="AO102" s="3" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="4" t="n"/>
@@ -4141,6 +5108,15 @@
       <c r="AD103" s="4" t="n"/>
       <c r="AE103" s="4" t="n"/>
       <c r="AF103" s="4" t="n"/>
+      <c r="AG103" s="4" t="n"/>
+      <c r="AH103" s="4" t="n"/>
+      <c r="AI103" s="4" t="n"/>
+      <c r="AJ103" s="4" t="n"/>
+      <c r="AK103" s="4" t="n"/>
+      <c r="AL103" s="4" t="n"/>
+      <c r="AM103" s="4" t="n"/>
+      <c r="AN103" s="4" t="n"/>
+      <c r="AO103" s="4" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="3" t="n"/>
@@ -4175,6 +5151,15 @@
       <c r="AD104" s="3" t="n"/>
       <c r="AE104" s="3" t="n"/>
       <c r="AF104" s="3" t="n"/>
+      <c r="AG104" s="3" t="n"/>
+      <c r="AH104" s="3" t="n"/>
+      <c r="AI104" s="3" t="n"/>
+      <c r="AJ104" s="3" t="n"/>
+      <c r="AK104" s="3" t="n"/>
+      <c r="AL104" s="3" t="n"/>
+      <c r="AM104" s="3" t="n"/>
+      <c r="AN104" s="3" t="n"/>
+      <c r="AO104" s="3" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="4" t="n"/>
@@ -4209,6 +5194,15 @@
       <c r="AD105" s="4" t="n"/>
       <c r="AE105" s="4" t="n"/>
       <c r="AF105" s="4" t="n"/>
+      <c r="AG105" s="4" t="n"/>
+      <c r="AH105" s="4" t="n"/>
+      <c r="AI105" s="4" t="n"/>
+      <c r="AJ105" s="4" t="n"/>
+      <c r="AK105" s="4" t="n"/>
+      <c r="AL105" s="4" t="n"/>
+      <c r="AM105" s="4" t="n"/>
+      <c r="AN105" s="4" t="n"/>
+      <c r="AO105" s="4" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="3" t="n"/>
@@ -4243,6 +5237,15 @@
       <c r="AD106" s="3" t="n"/>
       <c r="AE106" s="3" t="n"/>
       <c r="AF106" s="3" t="n"/>
+      <c r="AG106" s="3" t="n"/>
+      <c r="AH106" s="3" t="n"/>
+      <c r="AI106" s="3" t="n"/>
+      <c r="AJ106" s="3" t="n"/>
+      <c r="AK106" s="3" t="n"/>
+      <c r="AL106" s="3" t="n"/>
+      <c r="AM106" s="3" t="n"/>
+      <c r="AN106" s="3" t="n"/>
+      <c r="AO106" s="3" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="4" t="n"/>
@@ -4277,6 +5280,15 @@
       <c r="AD107" s="4" t="n"/>
       <c r="AE107" s="4" t="n"/>
       <c r="AF107" s="4" t="n"/>
+      <c r="AG107" s="4" t="n"/>
+      <c r="AH107" s="4" t="n"/>
+      <c r="AI107" s="4" t="n"/>
+      <c r="AJ107" s="4" t="n"/>
+      <c r="AK107" s="4" t="n"/>
+      <c r="AL107" s="4" t="n"/>
+      <c r="AM107" s="4" t="n"/>
+      <c r="AN107" s="4" t="n"/>
+      <c r="AO107" s="4" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="3" t="n"/>
@@ -4311,6 +5323,15 @@
       <c r="AD108" s="3" t="n"/>
       <c r="AE108" s="3" t="n"/>
       <c r="AF108" s="3" t="n"/>
+      <c r="AG108" s="3" t="n"/>
+      <c r="AH108" s="3" t="n"/>
+      <c r="AI108" s="3" t="n"/>
+      <c r="AJ108" s="3" t="n"/>
+      <c r="AK108" s="3" t="n"/>
+      <c r="AL108" s="3" t="n"/>
+      <c r="AM108" s="3" t="n"/>
+      <c r="AN108" s="3" t="n"/>
+      <c r="AO108" s="3" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="4" t="n"/>
@@ -4345,6 +5366,15 @@
       <c r="AD109" s="4" t="n"/>
       <c r="AE109" s="4" t="n"/>
       <c r="AF109" s="4" t="n"/>
+      <c r="AG109" s="4" t="n"/>
+      <c r="AH109" s="4" t="n"/>
+      <c r="AI109" s="4" t="n"/>
+      <c r="AJ109" s="4" t="n"/>
+      <c r="AK109" s="4" t="n"/>
+      <c r="AL109" s="4" t="n"/>
+      <c r="AM109" s="4" t="n"/>
+      <c r="AN109" s="4" t="n"/>
+      <c r="AO109" s="4" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="3" t="n"/>
@@ -4379,6 +5409,15 @@
       <c r="AD110" s="3" t="n"/>
       <c r="AE110" s="3" t="n"/>
       <c r="AF110" s="3" t="n"/>
+      <c r="AG110" s="3" t="n"/>
+      <c r="AH110" s="3" t="n"/>
+      <c r="AI110" s="3" t="n"/>
+      <c r="AJ110" s="3" t="n"/>
+      <c r="AK110" s="3" t="n"/>
+      <c r="AL110" s="3" t="n"/>
+      <c r="AM110" s="3" t="n"/>
+      <c r="AN110" s="3" t="n"/>
+      <c r="AO110" s="3" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="4" t="n"/>
@@ -4413,6 +5452,15 @@
       <c r="AD111" s="4" t="n"/>
       <c r="AE111" s="4" t="n"/>
       <c r="AF111" s="4" t="n"/>
+      <c r="AG111" s="4" t="n"/>
+      <c r="AH111" s="4" t="n"/>
+      <c r="AI111" s="4" t="n"/>
+      <c r="AJ111" s="4" t="n"/>
+      <c r="AK111" s="4" t="n"/>
+      <c r="AL111" s="4" t="n"/>
+      <c r="AM111" s="4" t="n"/>
+      <c r="AN111" s="4" t="n"/>
+      <c r="AO111" s="4" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="3" t="n"/>
@@ -4447,6 +5495,15 @@
       <c r="AD112" s="3" t="n"/>
       <c r="AE112" s="3" t="n"/>
       <c r="AF112" s="3" t="n"/>
+      <c r="AG112" s="3" t="n"/>
+      <c r="AH112" s="3" t="n"/>
+      <c r="AI112" s="3" t="n"/>
+      <c r="AJ112" s="3" t="n"/>
+      <c r="AK112" s="3" t="n"/>
+      <c r="AL112" s="3" t="n"/>
+      <c r="AM112" s="3" t="n"/>
+      <c r="AN112" s="3" t="n"/>
+      <c r="AO112" s="3" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="4" t="n"/>
@@ -4481,6 +5538,15 @@
       <c r="AD113" s="4" t="n"/>
       <c r="AE113" s="4" t="n"/>
       <c r="AF113" s="4" t="n"/>
+      <c r="AG113" s="4" t="n"/>
+      <c r="AH113" s="4" t="n"/>
+      <c r="AI113" s="4" t="n"/>
+      <c r="AJ113" s="4" t="n"/>
+      <c r="AK113" s="4" t="n"/>
+      <c r="AL113" s="4" t="n"/>
+      <c r="AM113" s="4" t="n"/>
+      <c r="AN113" s="4" t="n"/>
+      <c r="AO113" s="4" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="3" t="n"/>
@@ -4515,6 +5581,15 @@
       <c r="AD114" s="3" t="n"/>
       <c r="AE114" s="3" t="n"/>
       <c r="AF114" s="3" t="n"/>
+      <c r="AG114" s="3" t="n"/>
+      <c r="AH114" s="3" t="n"/>
+      <c r="AI114" s="3" t="n"/>
+      <c r="AJ114" s="3" t="n"/>
+      <c r="AK114" s="3" t="n"/>
+      <c r="AL114" s="3" t="n"/>
+      <c r="AM114" s="3" t="n"/>
+      <c r="AN114" s="3" t="n"/>
+      <c r="AO114" s="3" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="4" t="n"/>
@@ -4549,6 +5624,15 @@
       <c r="AD115" s="4" t="n"/>
       <c r="AE115" s="4" t="n"/>
       <c r="AF115" s="4" t="n"/>
+      <c r="AG115" s="4" t="n"/>
+      <c r="AH115" s="4" t="n"/>
+      <c r="AI115" s="4" t="n"/>
+      <c r="AJ115" s="4" t="n"/>
+      <c r="AK115" s="4" t="n"/>
+      <c r="AL115" s="4" t="n"/>
+      <c r="AM115" s="4" t="n"/>
+      <c r="AN115" s="4" t="n"/>
+      <c r="AO115" s="4" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="3" t="n"/>
@@ -4583,6 +5667,15 @@
       <c r="AD116" s="3" t="n"/>
       <c r="AE116" s="3" t="n"/>
       <c r="AF116" s="3" t="n"/>
+      <c r="AG116" s="3" t="n"/>
+      <c r="AH116" s="3" t="n"/>
+      <c r="AI116" s="3" t="n"/>
+      <c r="AJ116" s="3" t="n"/>
+      <c r="AK116" s="3" t="n"/>
+      <c r="AL116" s="3" t="n"/>
+      <c r="AM116" s="3" t="n"/>
+      <c r="AN116" s="3" t="n"/>
+      <c r="AO116" s="3" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="4" t="n"/>
@@ -4617,6 +5710,15 @@
       <c r="AD117" s="4" t="n"/>
       <c r="AE117" s="4" t="n"/>
       <c r="AF117" s="4" t="n"/>
+      <c r="AG117" s="4" t="n"/>
+      <c r="AH117" s="4" t="n"/>
+      <c r="AI117" s="4" t="n"/>
+      <c r="AJ117" s="4" t="n"/>
+      <c r="AK117" s="4" t="n"/>
+      <c r="AL117" s="4" t="n"/>
+      <c r="AM117" s="4" t="n"/>
+      <c r="AN117" s="4" t="n"/>
+      <c r="AO117" s="4" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="3" t="n"/>
@@ -4651,6 +5753,15 @@
       <c r="AD118" s="3" t="n"/>
       <c r="AE118" s="3" t="n"/>
       <c r="AF118" s="3" t="n"/>
+      <c r="AG118" s="3" t="n"/>
+      <c r="AH118" s="3" t="n"/>
+      <c r="AI118" s="3" t="n"/>
+      <c r="AJ118" s="3" t="n"/>
+      <c r="AK118" s="3" t="n"/>
+      <c r="AL118" s="3" t="n"/>
+      <c r="AM118" s="3" t="n"/>
+      <c r="AN118" s="3" t="n"/>
+      <c r="AO118" s="3" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="4" t="n"/>
@@ -4685,6 +5796,15 @@
       <c r="AD119" s="4" t="n"/>
       <c r="AE119" s="4" t="n"/>
       <c r="AF119" s="4" t="n"/>
+      <c r="AG119" s="4" t="n"/>
+      <c r="AH119" s="4" t="n"/>
+      <c r="AI119" s="4" t="n"/>
+      <c r="AJ119" s="4" t="n"/>
+      <c r="AK119" s="4" t="n"/>
+      <c r="AL119" s="4" t="n"/>
+      <c r="AM119" s="4" t="n"/>
+      <c r="AN119" s="4" t="n"/>
+      <c r="AO119" s="4" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="3" t="n"/>
@@ -4719,6 +5839,15 @@
       <c r="AD120" s="3" t="n"/>
       <c r="AE120" s="3" t="n"/>
       <c r="AF120" s="3" t="n"/>
+      <c r="AG120" s="3" t="n"/>
+      <c r="AH120" s="3" t="n"/>
+      <c r="AI120" s="3" t="n"/>
+      <c r="AJ120" s="3" t="n"/>
+      <c r="AK120" s="3" t="n"/>
+      <c r="AL120" s="3" t="n"/>
+      <c r="AM120" s="3" t="n"/>
+      <c r="AN120" s="3" t="n"/>
+      <c r="AO120" s="3" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="4" t="n"/>
@@ -4753,6 +5882,15 @@
       <c r="AD121" s="4" t="n"/>
       <c r="AE121" s="4" t="n"/>
       <c r="AF121" s="4" t="n"/>
+      <c r="AG121" s="4" t="n"/>
+      <c r="AH121" s="4" t="n"/>
+      <c r="AI121" s="4" t="n"/>
+      <c r="AJ121" s="4" t="n"/>
+      <c r="AK121" s="4" t="n"/>
+      <c r="AL121" s="4" t="n"/>
+      <c r="AM121" s="4" t="n"/>
+      <c r="AN121" s="4" t="n"/>
+      <c r="AO121" s="4" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="3" t="n"/>
@@ -4787,6 +5925,15 @@
       <c r="AD122" s="3" t="n"/>
       <c r="AE122" s="3" t="n"/>
       <c r="AF122" s="3" t="n"/>
+      <c r="AG122" s="3" t="n"/>
+      <c r="AH122" s="3" t="n"/>
+      <c r="AI122" s="3" t="n"/>
+      <c r="AJ122" s="3" t="n"/>
+      <c r="AK122" s="3" t="n"/>
+      <c r="AL122" s="3" t="n"/>
+      <c r="AM122" s="3" t="n"/>
+      <c r="AN122" s="3" t="n"/>
+      <c r="AO122" s="3" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="4" t="n"/>
@@ -4821,6 +5968,15 @@
       <c r="AD123" s="4" t="n"/>
       <c r="AE123" s="4" t="n"/>
       <c r="AF123" s="4" t="n"/>
+      <c r="AG123" s="4" t="n"/>
+      <c r="AH123" s="4" t="n"/>
+      <c r="AI123" s="4" t="n"/>
+      <c r="AJ123" s="4" t="n"/>
+      <c r="AK123" s="4" t="n"/>
+      <c r="AL123" s="4" t="n"/>
+      <c r="AM123" s="4" t="n"/>
+      <c r="AN123" s="4" t="n"/>
+      <c r="AO123" s="4" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="3" t="n"/>
@@ -4855,6 +6011,15 @@
       <c r="AD124" s="3" t="n"/>
       <c r="AE124" s="3" t="n"/>
       <c r="AF124" s="3" t="n"/>
+      <c r="AG124" s="3" t="n"/>
+      <c r="AH124" s="3" t="n"/>
+      <c r="AI124" s="3" t="n"/>
+      <c r="AJ124" s="3" t="n"/>
+      <c r="AK124" s="3" t="n"/>
+      <c r="AL124" s="3" t="n"/>
+      <c r="AM124" s="3" t="n"/>
+      <c r="AN124" s="3" t="n"/>
+      <c r="AO124" s="3" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="4" t="n"/>
@@ -4889,6 +6054,15 @@
       <c r="AD125" s="4" t="n"/>
       <c r="AE125" s="4" t="n"/>
       <c r="AF125" s="4" t="n"/>
+      <c r="AG125" s="4" t="n"/>
+      <c r="AH125" s="4" t="n"/>
+      <c r="AI125" s="4" t="n"/>
+      <c r="AJ125" s="4" t="n"/>
+      <c r="AK125" s="4" t="n"/>
+      <c r="AL125" s="4" t="n"/>
+      <c r="AM125" s="4" t="n"/>
+      <c r="AN125" s="4" t="n"/>
+      <c r="AO125" s="4" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="3" t="n"/>
@@ -4923,6 +6097,15 @@
       <c r="AD126" s="3" t="n"/>
       <c r="AE126" s="3" t="n"/>
       <c r="AF126" s="3" t="n"/>
+      <c r="AG126" s="3" t="n"/>
+      <c r="AH126" s="3" t="n"/>
+      <c r="AI126" s="3" t="n"/>
+      <c r="AJ126" s="3" t="n"/>
+      <c r="AK126" s="3" t="n"/>
+      <c r="AL126" s="3" t="n"/>
+      <c r="AM126" s="3" t="n"/>
+      <c r="AN126" s="3" t="n"/>
+      <c r="AO126" s="3" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="4" t="n"/>
@@ -4957,6 +6140,15 @@
       <c r="AD127" s="4" t="n"/>
       <c r="AE127" s="4" t="n"/>
       <c r="AF127" s="4" t="n"/>
+      <c r="AG127" s="4" t="n"/>
+      <c r="AH127" s="4" t="n"/>
+      <c r="AI127" s="4" t="n"/>
+      <c r="AJ127" s="4" t="n"/>
+      <c r="AK127" s="4" t="n"/>
+      <c r="AL127" s="4" t="n"/>
+      <c r="AM127" s="4" t="n"/>
+      <c r="AN127" s="4" t="n"/>
+      <c r="AO127" s="4" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="3" t="n"/>
@@ -4991,6 +6183,15 @@
       <c r="AD128" s="3" t="n"/>
       <c r="AE128" s="3" t="n"/>
       <c r="AF128" s="3" t="n"/>
+      <c r="AG128" s="3" t="n"/>
+      <c r="AH128" s="3" t="n"/>
+      <c r="AI128" s="3" t="n"/>
+      <c r="AJ128" s="3" t="n"/>
+      <c r="AK128" s="3" t="n"/>
+      <c r="AL128" s="3" t="n"/>
+      <c r="AM128" s="3" t="n"/>
+      <c r="AN128" s="3" t="n"/>
+      <c r="AO128" s="3" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="4" t="n"/>
@@ -5025,6 +6226,15 @@
       <c r="AD129" s="4" t="n"/>
       <c r="AE129" s="4" t="n"/>
       <c r="AF129" s="4" t="n"/>
+      <c r="AG129" s="4" t="n"/>
+      <c r="AH129" s="4" t="n"/>
+      <c r="AI129" s="4" t="n"/>
+      <c r="AJ129" s="4" t="n"/>
+      <c r="AK129" s="4" t="n"/>
+      <c r="AL129" s="4" t="n"/>
+      <c r="AM129" s="4" t="n"/>
+      <c r="AN129" s="4" t="n"/>
+      <c r="AO129" s="4" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="3" t="n"/>
@@ -5059,6 +6269,15 @@
       <c r="AD130" s="3" t="n"/>
       <c r="AE130" s="3" t="n"/>
       <c r="AF130" s="3" t="n"/>
+      <c r="AG130" s="3" t="n"/>
+      <c r="AH130" s="3" t="n"/>
+      <c r="AI130" s="3" t="n"/>
+      <c r="AJ130" s="3" t="n"/>
+      <c r="AK130" s="3" t="n"/>
+      <c r="AL130" s="3" t="n"/>
+      <c r="AM130" s="3" t="n"/>
+      <c r="AN130" s="3" t="n"/>
+      <c r="AO130" s="3" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="4" t="n"/>
@@ -5093,6 +6312,15 @@
       <c r="AD131" s="4" t="n"/>
       <c r="AE131" s="4" t="n"/>
       <c r="AF131" s="4" t="n"/>
+      <c r="AG131" s="4" t="n"/>
+      <c r="AH131" s="4" t="n"/>
+      <c r="AI131" s="4" t="n"/>
+      <c r="AJ131" s="4" t="n"/>
+      <c r="AK131" s="4" t="n"/>
+      <c r="AL131" s="4" t="n"/>
+      <c r="AM131" s="4" t="n"/>
+      <c r="AN131" s="4" t="n"/>
+      <c r="AO131" s="4" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="3" t="n"/>
@@ -5127,6 +6355,15 @@
       <c r="AD132" s="3" t="n"/>
       <c r="AE132" s="3" t="n"/>
       <c r="AF132" s="3" t="n"/>
+      <c r="AG132" s="3" t="n"/>
+      <c r="AH132" s="3" t="n"/>
+      <c r="AI132" s="3" t="n"/>
+      <c r="AJ132" s="3" t="n"/>
+      <c r="AK132" s="3" t="n"/>
+      <c r="AL132" s="3" t="n"/>
+      <c r="AM132" s="3" t="n"/>
+      <c r="AN132" s="3" t="n"/>
+      <c r="AO132" s="3" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="4" t="n"/>
@@ -5161,6 +6398,15 @@
       <c r="AD133" s="4" t="n"/>
       <c r="AE133" s="4" t="n"/>
       <c r="AF133" s="4" t="n"/>
+      <c r="AG133" s="4" t="n"/>
+      <c r="AH133" s="4" t="n"/>
+      <c r="AI133" s="4" t="n"/>
+      <c r="AJ133" s="4" t="n"/>
+      <c r="AK133" s="4" t="n"/>
+      <c r="AL133" s="4" t="n"/>
+      <c r="AM133" s="4" t="n"/>
+      <c r="AN133" s="4" t="n"/>
+      <c r="AO133" s="4" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="3" t="n"/>
@@ -5195,6 +6441,15 @@
       <c r="AD134" s="3" t="n"/>
       <c r="AE134" s="3" t="n"/>
       <c r="AF134" s="3" t="n"/>
+      <c r="AG134" s="3" t="n"/>
+      <c r="AH134" s="3" t="n"/>
+      <c r="AI134" s="3" t="n"/>
+      <c r="AJ134" s="3" t="n"/>
+      <c r="AK134" s="3" t="n"/>
+      <c r="AL134" s="3" t="n"/>
+      <c r="AM134" s="3" t="n"/>
+      <c r="AN134" s="3" t="n"/>
+      <c r="AO134" s="3" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="4" t="n"/>
@@ -5229,6 +6484,15 @@
       <c r="AD135" s="4" t="n"/>
       <c r="AE135" s="4" t="n"/>
       <c r="AF135" s="4" t="n"/>
+      <c r="AG135" s="4" t="n"/>
+      <c r="AH135" s="4" t="n"/>
+      <c r="AI135" s="4" t="n"/>
+      <c r="AJ135" s="4" t="n"/>
+      <c r="AK135" s="4" t="n"/>
+      <c r="AL135" s="4" t="n"/>
+      <c r="AM135" s="4" t="n"/>
+      <c r="AN135" s="4" t="n"/>
+      <c r="AO135" s="4" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="3" t="n"/>
@@ -5263,6 +6527,15 @@
       <c r="AD136" s="3" t="n"/>
       <c r="AE136" s="3" t="n"/>
       <c r="AF136" s="3" t="n"/>
+      <c r="AG136" s="3" t="n"/>
+      <c r="AH136" s="3" t="n"/>
+      <c r="AI136" s="3" t="n"/>
+      <c r="AJ136" s="3" t="n"/>
+      <c r="AK136" s="3" t="n"/>
+      <c r="AL136" s="3" t="n"/>
+      <c r="AM136" s="3" t="n"/>
+      <c r="AN136" s="3" t="n"/>
+      <c r="AO136" s="3" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="4" t="n"/>
@@ -5297,6 +6570,15 @@
       <c r="AD137" s="4" t="n"/>
       <c r="AE137" s="4" t="n"/>
       <c r="AF137" s="4" t="n"/>
+      <c r="AG137" s="4" t="n"/>
+      <c r="AH137" s="4" t="n"/>
+      <c r="AI137" s="4" t="n"/>
+      <c r="AJ137" s="4" t="n"/>
+      <c r="AK137" s="4" t="n"/>
+      <c r="AL137" s="4" t="n"/>
+      <c r="AM137" s="4" t="n"/>
+      <c r="AN137" s="4" t="n"/>
+      <c r="AO137" s="4" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="3" t="n"/>
@@ -5331,6 +6613,15 @@
       <c r="AD138" s="3" t="n"/>
       <c r="AE138" s="3" t="n"/>
       <c r="AF138" s="3" t="n"/>
+      <c r="AG138" s="3" t="n"/>
+      <c r="AH138" s="3" t="n"/>
+      <c r="AI138" s="3" t="n"/>
+      <c r="AJ138" s="3" t="n"/>
+      <c r="AK138" s="3" t="n"/>
+      <c r="AL138" s="3" t="n"/>
+      <c r="AM138" s="3" t="n"/>
+      <c r="AN138" s="3" t="n"/>
+      <c r="AO138" s="3" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="4" t="n"/>
@@ -5365,6 +6656,15 @@
       <c r="AD139" s="4" t="n"/>
       <c r="AE139" s="4" t="n"/>
       <c r="AF139" s="4" t="n"/>
+      <c r="AG139" s="4" t="n"/>
+      <c r="AH139" s="4" t="n"/>
+      <c r="AI139" s="4" t="n"/>
+      <c r="AJ139" s="4" t="n"/>
+      <c r="AK139" s="4" t="n"/>
+      <c r="AL139" s="4" t="n"/>
+      <c r="AM139" s="4" t="n"/>
+      <c r="AN139" s="4" t="n"/>
+      <c r="AO139" s="4" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="3" t="n"/>
@@ -5399,6 +6699,15 @@
       <c r="AD140" s="3" t="n"/>
       <c r="AE140" s="3" t="n"/>
       <c r="AF140" s="3" t="n"/>
+      <c r="AG140" s="3" t="n"/>
+      <c r="AH140" s="3" t="n"/>
+      <c r="AI140" s="3" t="n"/>
+      <c r="AJ140" s="3" t="n"/>
+      <c r="AK140" s="3" t="n"/>
+      <c r="AL140" s="3" t="n"/>
+      <c r="AM140" s="3" t="n"/>
+      <c r="AN140" s="3" t="n"/>
+      <c r="AO140" s="3" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="4" t="n"/>
@@ -5433,6 +6742,15 @@
       <c r="AD141" s="4" t="n"/>
       <c r="AE141" s="4" t="n"/>
       <c r="AF141" s="4" t="n"/>
+      <c r="AG141" s="4" t="n"/>
+      <c r="AH141" s="4" t="n"/>
+      <c r="AI141" s="4" t="n"/>
+      <c r="AJ141" s="4" t="n"/>
+      <c r="AK141" s="4" t="n"/>
+      <c r="AL141" s="4" t="n"/>
+      <c r="AM141" s="4" t="n"/>
+      <c r="AN141" s="4" t="n"/>
+      <c r="AO141" s="4" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="3" t="n"/>
@@ -5467,6 +6785,15 @@
       <c r="AD142" s="3" t="n"/>
       <c r="AE142" s="3" t="n"/>
       <c r="AF142" s="3" t="n"/>
+      <c r="AG142" s="3" t="n"/>
+      <c r="AH142" s="3" t="n"/>
+      <c r="AI142" s="3" t="n"/>
+      <c r="AJ142" s="3" t="n"/>
+      <c r="AK142" s="3" t="n"/>
+      <c r="AL142" s="3" t="n"/>
+      <c r="AM142" s="3" t="n"/>
+      <c r="AN142" s="3" t="n"/>
+      <c r="AO142" s="3" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="4" t="n"/>
@@ -5501,6 +6828,15 @@
       <c r="AD143" s="4" t="n"/>
       <c r="AE143" s="4" t="n"/>
       <c r="AF143" s="4" t="n"/>
+      <c r="AG143" s="4" t="n"/>
+      <c r="AH143" s="4" t="n"/>
+      <c r="AI143" s="4" t="n"/>
+      <c r="AJ143" s="4" t="n"/>
+      <c r="AK143" s="4" t="n"/>
+      <c r="AL143" s="4" t="n"/>
+      <c r="AM143" s="4" t="n"/>
+      <c r="AN143" s="4" t="n"/>
+      <c r="AO143" s="4" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="3" t="n"/>
@@ -5535,6 +6871,15 @@
       <c r="AD144" s="3" t="n"/>
       <c r="AE144" s="3" t="n"/>
       <c r="AF144" s="3" t="n"/>
+      <c r="AG144" s="3" t="n"/>
+      <c r="AH144" s="3" t="n"/>
+      <c r="AI144" s="3" t="n"/>
+      <c r="AJ144" s="3" t="n"/>
+      <c r="AK144" s="3" t="n"/>
+      <c r="AL144" s="3" t="n"/>
+      <c r="AM144" s="3" t="n"/>
+      <c r="AN144" s="3" t="n"/>
+      <c r="AO144" s="3" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="4" t="n"/>
@@ -5569,6 +6914,15 @@
       <c r="AD145" s="4" t="n"/>
       <c r="AE145" s="4" t="n"/>
       <c r="AF145" s="4" t="n"/>
+      <c r="AG145" s="4" t="n"/>
+      <c r="AH145" s="4" t="n"/>
+      <c r="AI145" s="4" t="n"/>
+      <c r="AJ145" s="4" t="n"/>
+      <c r="AK145" s="4" t="n"/>
+      <c r="AL145" s="4" t="n"/>
+      <c r="AM145" s="4" t="n"/>
+      <c r="AN145" s="4" t="n"/>
+      <c r="AO145" s="4" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="3" t="n"/>
@@ -5603,6 +6957,15 @@
       <c r="AD146" s="3" t="n"/>
       <c r="AE146" s="3" t="n"/>
       <c r="AF146" s="3" t="n"/>
+      <c r="AG146" s="3" t="n"/>
+      <c r="AH146" s="3" t="n"/>
+      <c r="AI146" s="3" t="n"/>
+      <c r="AJ146" s="3" t="n"/>
+      <c r="AK146" s="3" t="n"/>
+      <c r="AL146" s="3" t="n"/>
+      <c r="AM146" s="3" t="n"/>
+      <c r="AN146" s="3" t="n"/>
+      <c r="AO146" s="3" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="4" t="n"/>
@@ -5637,6 +7000,15 @@
       <c r="AD147" s="4" t="n"/>
       <c r="AE147" s="4" t="n"/>
       <c r="AF147" s="4" t="n"/>
+      <c r="AG147" s="4" t="n"/>
+      <c r="AH147" s="4" t="n"/>
+      <c r="AI147" s="4" t="n"/>
+      <c r="AJ147" s="4" t="n"/>
+      <c r="AK147" s="4" t="n"/>
+      <c r="AL147" s="4" t="n"/>
+      <c r="AM147" s="4" t="n"/>
+      <c r="AN147" s="4" t="n"/>
+      <c r="AO147" s="4" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="3" t="n"/>
@@ -5671,6 +7043,15 @@
       <c r="AD148" s="3" t="n"/>
       <c r="AE148" s="3" t="n"/>
       <c r="AF148" s="3" t="n"/>
+      <c r="AG148" s="3" t="n"/>
+      <c r="AH148" s="3" t="n"/>
+      <c r="AI148" s="3" t="n"/>
+      <c r="AJ148" s="3" t="n"/>
+      <c r="AK148" s="3" t="n"/>
+      <c r="AL148" s="3" t="n"/>
+      <c r="AM148" s="3" t="n"/>
+      <c r="AN148" s="3" t="n"/>
+      <c r="AO148" s="3" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="4" t="n"/>
@@ -5705,6 +7086,15 @@
       <c r="AD149" s="4" t="n"/>
       <c r="AE149" s="4" t="n"/>
       <c r="AF149" s="4" t="n"/>
+      <c r="AG149" s="4" t="n"/>
+      <c r="AH149" s="4" t="n"/>
+      <c r="AI149" s="4" t="n"/>
+      <c r="AJ149" s="4" t="n"/>
+      <c r="AK149" s="4" t="n"/>
+      <c r="AL149" s="4" t="n"/>
+      <c r="AM149" s="4" t="n"/>
+      <c r="AN149" s="4" t="n"/>
+      <c r="AO149" s="4" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="3" t="n"/>
@@ -5739,6 +7129,15 @@
       <c r="AD150" s="3" t="n"/>
       <c r="AE150" s="3" t="n"/>
       <c r="AF150" s="3" t="n"/>
+      <c r="AG150" s="3" t="n"/>
+      <c r="AH150" s="3" t="n"/>
+      <c r="AI150" s="3" t="n"/>
+      <c r="AJ150" s="3" t="n"/>
+      <c r="AK150" s="3" t="n"/>
+      <c r="AL150" s="3" t="n"/>
+      <c r="AM150" s="3" t="n"/>
+      <c r="AN150" s="3" t="n"/>
+      <c r="AO150" s="3" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="4" t="n"/>
@@ -5773,6 +7172,15 @@
       <c r="AD151" s="4" t="n"/>
       <c r="AE151" s="4" t="n"/>
       <c r="AF151" s="4" t="n"/>
+      <c r="AG151" s="4" t="n"/>
+      <c r="AH151" s="4" t="n"/>
+      <c r="AI151" s="4" t="n"/>
+      <c r="AJ151" s="4" t="n"/>
+      <c r="AK151" s="4" t="n"/>
+      <c r="AL151" s="4" t="n"/>
+      <c r="AM151" s="4" t="n"/>
+      <c r="AN151" s="4" t="n"/>
+      <c r="AO151" s="4" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="3" t="n"/>
@@ -5807,6 +7215,15 @@
       <c r="AD152" s="3" t="n"/>
       <c r="AE152" s="3" t="n"/>
       <c r="AF152" s="3" t="n"/>
+      <c r="AG152" s="3" t="n"/>
+      <c r="AH152" s="3" t="n"/>
+      <c r="AI152" s="3" t="n"/>
+      <c r="AJ152" s="3" t="n"/>
+      <c r="AK152" s="3" t="n"/>
+      <c r="AL152" s="3" t="n"/>
+      <c r="AM152" s="3" t="n"/>
+      <c r="AN152" s="3" t="n"/>
+      <c r="AO152" s="3" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="4" t="n"/>
@@ -5841,6 +7258,15 @@
       <c r="AD153" s="4" t="n"/>
       <c r="AE153" s="4" t="n"/>
       <c r="AF153" s="4" t="n"/>
+      <c r="AG153" s="4" t="n"/>
+      <c r="AH153" s="4" t="n"/>
+      <c r="AI153" s="4" t="n"/>
+      <c r="AJ153" s="4" t="n"/>
+      <c r="AK153" s="4" t="n"/>
+      <c r="AL153" s="4" t="n"/>
+      <c r="AM153" s="4" t="n"/>
+      <c r="AN153" s="4" t="n"/>
+      <c r="AO153" s="4" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="3" t="n"/>
@@ -5875,6 +7301,15 @@
       <c r="AD154" s="3" t="n"/>
       <c r="AE154" s="3" t="n"/>
       <c r="AF154" s="3" t="n"/>
+      <c r="AG154" s="3" t="n"/>
+      <c r="AH154" s="3" t="n"/>
+      <c r="AI154" s="3" t="n"/>
+      <c r="AJ154" s="3" t="n"/>
+      <c r="AK154" s="3" t="n"/>
+      <c r="AL154" s="3" t="n"/>
+      <c r="AM154" s="3" t="n"/>
+      <c r="AN154" s="3" t="n"/>
+      <c r="AO154" s="3" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="4" t="n"/>
@@ -5909,6 +7344,15 @@
       <c r="AD155" s="4" t="n"/>
       <c r="AE155" s="4" t="n"/>
       <c r="AF155" s="4" t="n"/>
+      <c r="AG155" s="4" t="n"/>
+      <c r="AH155" s="4" t="n"/>
+      <c r="AI155" s="4" t="n"/>
+      <c r="AJ155" s="4" t="n"/>
+      <c r="AK155" s="4" t="n"/>
+      <c r="AL155" s="4" t="n"/>
+      <c r="AM155" s="4" t="n"/>
+      <c r="AN155" s="4" t="n"/>
+      <c r="AO155" s="4" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="3" t="n"/>
@@ -5943,6 +7387,15 @@
       <c r="AD156" s="3" t="n"/>
       <c r="AE156" s="3" t="n"/>
       <c r="AF156" s="3" t="n"/>
+      <c r="AG156" s="3" t="n"/>
+      <c r="AH156" s="3" t="n"/>
+      <c r="AI156" s="3" t="n"/>
+      <c r="AJ156" s="3" t="n"/>
+      <c r="AK156" s="3" t="n"/>
+      <c r="AL156" s="3" t="n"/>
+      <c r="AM156" s="3" t="n"/>
+      <c r="AN156" s="3" t="n"/>
+      <c r="AO156" s="3" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="4" t="n"/>
@@ -5977,6 +7430,15 @@
       <c r="AD157" s="4" t="n"/>
       <c r="AE157" s="4" t="n"/>
       <c r="AF157" s="4" t="n"/>
+      <c r="AG157" s="4" t="n"/>
+      <c r="AH157" s="4" t="n"/>
+      <c r="AI157" s="4" t="n"/>
+      <c r="AJ157" s="4" t="n"/>
+      <c r="AK157" s="4" t="n"/>
+      <c r="AL157" s="4" t="n"/>
+      <c r="AM157" s="4" t="n"/>
+      <c r="AN157" s="4" t="n"/>
+      <c r="AO157" s="4" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="3" t="n"/>
@@ -6011,6 +7473,15 @@
       <c r="AD158" s="3" t="n"/>
       <c r="AE158" s="3" t="n"/>
       <c r="AF158" s="3" t="n"/>
+      <c r="AG158" s="3" t="n"/>
+      <c r="AH158" s="3" t="n"/>
+      <c r="AI158" s="3" t="n"/>
+      <c r="AJ158" s="3" t="n"/>
+      <c r="AK158" s="3" t="n"/>
+      <c r="AL158" s="3" t="n"/>
+      <c r="AM158" s="3" t="n"/>
+      <c r="AN158" s="3" t="n"/>
+      <c r="AO158" s="3" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="4" t="n"/>
@@ -6045,6 +7516,15 @@
       <c r="AD159" s="4" t="n"/>
       <c r="AE159" s="4" t="n"/>
       <c r="AF159" s="4" t="n"/>
+      <c r="AG159" s="4" t="n"/>
+      <c r="AH159" s="4" t="n"/>
+      <c r="AI159" s="4" t="n"/>
+      <c r="AJ159" s="4" t="n"/>
+      <c r="AK159" s="4" t="n"/>
+      <c r="AL159" s="4" t="n"/>
+      <c r="AM159" s="4" t="n"/>
+      <c r="AN159" s="4" t="n"/>
+      <c r="AO159" s="4" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="3" t="n"/>
@@ -6079,6 +7559,15 @@
       <c r="AD160" s="3" t="n"/>
       <c r="AE160" s="3" t="n"/>
       <c r="AF160" s="3" t="n"/>
+      <c r="AG160" s="3" t="n"/>
+      <c r="AH160" s="3" t="n"/>
+      <c r="AI160" s="3" t="n"/>
+      <c r="AJ160" s="3" t="n"/>
+      <c r="AK160" s="3" t="n"/>
+      <c r="AL160" s="3" t="n"/>
+      <c r="AM160" s="3" t="n"/>
+      <c r="AN160" s="3" t="n"/>
+      <c r="AO160" s="3" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="4" t="n"/>
@@ -6113,6 +7602,15 @@
       <c r="AD161" s="4" t="n"/>
       <c r="AE161" s="4" t="n"/>
       <c r="AF161" s="4" t="n"/>
+      <c r="AG161" s="4" t="n"/>
+      <c r="AH161" s="4" t="n"/>
+      <c r="AI161" s="4" t="n"/>
+      <c r="AJ161" s="4" t="n"/>
+      <c r="AK161" s="4" t="n"/>
+      <c r="AL161" s="4" t="n"/>
+      <c r="AM161" s="4" t="n"/>
+      <c r="AN161" s="4" t="n"/>
+      <c r="AO161" s="4" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="3" t="n"/>
@@ -6147,6 +7645,15 @@
       <c r="AD162" s="3" t="n"/>
       <c r="AE162" s="3" t="n"/>
       <c r="AF162" s="3" t="n"/>
+      <c r="AG162" s="3" t="n"/>
+      <c r="AH162" s="3" t="n"/>
+      <c r="AI162" s="3" t="n"/>
+      <c r="AJ162" s="3" t="n"/>
+      <c r="AK162" s="3" t="n"/>
+      <c r="AL162" s="3" t="n"/>
+      <c r="AM162" s="3" t="n"/>
+      <c r="AN162" s="3" t="n"/>
+      <c r="AO162" s="3" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="4" t="n"/>
@@ -6181,6 +7688,15 @@
       <c r="AD163" s="4" t="n"/>
       <c r="AE163" s="4" t="n"/>
       <c r="AF163" s="4" t="n"/>
+      <c r="AG163" s="4" t="n"/>
+      <c r="AH163" s="4" t="n"/>
+      <c r="AI163" s="4" t="n"/>
+      <c r="AJ163" s="4" t="n"/>
+      <c r="AK163" s="4" t="n"/>
+      <c r="AL163" s="4" t="n"/>
+      <c r="AM163" s="4" t="n"/>
+      <c r="AN163" s="4" t="n"/>
+      <c r="AO163" s="4" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="3" t="n"/>
@@ -6215,6 +7731,15 @@
       <c r="AD164" s="3" t="n"/>
       <c r="AE164" s="3" t="n"/>
       <c r="AF164" s="3" t="n"/>
+      <c r="AG164" s="3" t="n"/>
+      <c r="AH164" s="3" t="n"/>
+      <c r="AI164" s="3" t="n"/>
+      <c r="AJ164" s="3" t="n"/>
+      <c r="AK164" s="3" t="n"/>
+      <c r="AL164" s="3" t="n"/>
+      <c r="AM164" s="3" t="n"/>
+      <c r="AN164" s="3" t="n"/>
+      <c r="AO164" s="3" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="4" t="n"/>
@@ -6249,6 +7774,15 @@
       <c r="AD165" s="4" t="n"/>
       <c r="AE165" s="4" t="n"/>
       <c r="AF165" s="4" t="n"/>
+      <c r="AG165" s="4" t="n"/>
+      <c r="AH165" s="4" t="n"/>
+      <c r="AI165" s="4" t="n"/>
+      <c r="AJ165" s="4" t="n"/>
+      <c r="AK165" s="4" t="n"/>
+      <c r="AL165" s="4" t="n"/>
+      <c r="AM165" s="4" t="n"/>
+      <c r="AN165" s="4" t="n"/>
+      <c r="AO165" s="4" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="3" t="n"/>
@@ -6283,6 +7817,15 @@
       <c r="AD166" s="3" t="n"/>
       <c r="AE166" s="3" t="n"/>
       <c r="AF166" s="3" t="n"/>
+      <c r="AG166" s="3" t="n"/>
+      <c r="AH166" s="3" t="n"/>
+      <c r="AI166" s="3" t="n"/>
+      <c r="AJ166" s="3" t="n"/>
+      <c r="AK166" s="3" t="n"/>
+      <c r="AL166" s="3" t="n"/>
+      <c r="AM166" s="3" t="n"/>
+      <c r="AN166" s="3" t="n"/>
+      <c r="AO166" s="3" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="4" t="n"/>
@@ -6317,6 +7860,15 @@
       <c r="AD167" s="4" t="n"/>
       <c r="AE167" s="4" t="n"/>
       <c r="AF167" s="4" t="n"/>
+      <c r="AG167" s="4" t="n"/>
+      <c r="AH167" s="4" t="n"/>
+      <c r="AI167" s="4" t="n"/>
+      <c r="AJ167" s="4" t="n"/>
+      <c r="AK167" s="4" t="n"/>
+      <c r="AL167" s="4" t="n"/>
+      <c r="AM167" s="4" t="n"/>
+      <c r="AN167" s="4" t="n"/>
+      <c r="AO167" s="4" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="3" t="n"/>
@@ -6351,6 +7903,15 @@
       <c r="AD168" s="3" t="n"/>
       <c r="AE168" s="3" t="n"/>
       <c r="AF168" s="3" t="n"/>
+      <c r="AG168" s="3" t="n"/>
+      <c r="AH168" s="3" t="n"/>
+      <c r="AI168" s="3" t="n"/>
+      <c r="AJ168" s="3" t="n"/>
+      <c r="AK168" s="3" t="n"/>
+      <c r="AL168" s="3" t="n"/>
+      <c r="AM168" s="3" t="n"/>
+      <c r="AN168" s="3" t="n"/>
+      <c r="AO168" s="3" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="4" t="n"/>
@@ -6385,6 +7946,15 @@
       <c r="AD169" s="4" t="n"/>
       <c r="AE169" s="4" t="n"/>
       <c r="AF169" s="4" t="n"/>
+      <c r="AG169" s="4" t="n"/>
+      <c r="AH169" s="4" t="n"/>
+      <c r="AI169" s="4" t="n"/>
+      <c r="AJ169" s="4" t="n"/>
+      <c r="AK169" s="4" t="n"/>
+      <c r="AL169" s="4" t="n"/>
+      <c r="AM169" s="4" t="n"/>
+      <c r="AN169" s="4" t="n"/>
+      <c r="AO169" s="4" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="3" t="n"/>
@@ -6419,6 +7989,15 @@
       <c r="AD170" s="3" t="n"/>
       <c r="AE170" s="3" t="n"/>
       <c r="AF170" s="3" t="n"/>
+      <c r="AG170" s="3" t="n"/>
+      <c r="AH170" s="3" t="n"/>
+      <c r="AI170" s="3" t="n"/>
+      <c r="AJ170" s="3" t="n"/>
+      <c r="AK170" s="3" t="n"/>
+      <c r="AL170" s="3" t="n"/>
+      <c r="AM170" s="3" t="n"/>
+      <c r="AN170" s="3" t="n"/>
+      <c r="AO170" s="3" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="4" t="n"/>
@@ -6453,6 +8032,15 @@
       <c r="AD171" s="4" t="n"/>
       <c r="AE171" s="4" t="n"/>
       <c r="AF171" s="4" t="n"/>
+      <c r="AG171" s="4" t="n"/>
+      <c r="AH171" s="4" t="n"/>
+      <c r="AI171" s="4" t="n"/>
+      <c r="AJ171" s="4" t="n"/>
+      <c r="AK171" s="4" t="n"/>
+      <c r="AL171" s="4" t="n"/>
+      <c r="AM171" s="4" t="n"/>
+      <c r="AN171" s="4" t="n"/>
+      <c r="AO171" s="4" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="3" t="n"/>
@@ -6487,6 +8075,15 @@
       <c r="AD172" s="3" t="n"/>
       <c r="AE172" s="3" t="n"/>
       <c r="AF172" s="3" t="n"/>
+      <c r="AG172" s="3" t="n"/>
+      <c r="AH172" s="3" t="n"/>
+      <c r="AI172" s="3" t="n"/>
+      <c r="AJ172" s="3" t="n"/>
+      <c r="AK172" s="3" t="n"/>
+      <c r="AL172" s="3" t="n"/>
+      <c r="AM172" s="3" t="n"/>
+      <c r="AN172" s="3" t="n"/>
+      <c r="AO172" s="3" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="4" t="n"/>
@@ -6521,6 +8118,15 @@
       <c r="AD173" s="4" t="n"/>
       <c r="AE173" s="4" t="n"/>
       <c r="AF173" s="4" t="n"/>
+      <c r="AG173" s="4" t="n"/>
+      <c r="AH173" s="4" t="n"/>
+      <c r="AI173" s="4" t="n"/>
+      <c r="AJ173" s="4" t="n"/>
+      <c r="AK173" s="4" t="n"/>
+      <c r="AL173" s="4" t="n"/>
+      <c r="AM173" s="4" t="n"/>
+      <c r="AN173" s="4" t="n"/>
+      <c r="AO173" s="4" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="3" t="n"/>
@@ -6555,6 +8161,15 @@
       <c r="AD174" s="3" t="n"/>
       <c r="AE174" s="3" t="n"/>
       <c r="AF174" s="3" t="n"/>
+      <c r="AG174" s="3" t="n"/>
+      <c r="AH174" s="3" t="n"/>
+      <c r="AI174" s="3" t="n"/>
+      <c r="AJ174" s="3" t="n"/>
+      <c r="AK174" s="3" t="n"/>
+      <c r="AL174" s="3" t="n"/>
+      <c r="AM174" s="3" t="n"/>
+      <c r="AN174" s="3" t="n"/>
+      <c r="AO174" s="3" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="4" t="n"/>
@@ -6589,6 +8204,15 @@
       <c r="AD175" s="4" t="n"/>
       <c r="AE175" s="4" t="n"/>
       <c r="AF175" s="4" t="n"/>
+      <c r="AG175" s="4" t="n"/>
+      <c r="AH175" s="4" t="n"/>
+      <c r="AI175" s="4" t="n"/>
+      <c r="AJ175" s="4" t="n"/>
+      <c r="AK175" s="4" t="n"/>
+      <c r="AL175" s="4" t="n"/>
+      <c r="AM175" s="4" t="n"/>
+      <c r="AN175" s="4" t="n"/>
+      <c r="AO175" s="4" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="3" t="n"/>
@@ -6623,6 +8247,15 @@
       <c r="AD176" s="3" t="n"/>
       <c r="AE176" s="3" t="n"/>
       <c r="AF176" s="3" t="n"/>
+      <c r="AG176" s="3" t="n"/>
+      <c r="AH176" s="3" t="n"/>
+      <c r="AI176" s="3" t="n"/>
+      <c r="AJ176" s="3" t="n"/>
+      <c r="AK176" s="3" t="n"/>
+      <c r="AL176" s="3" t="n"/>
+      <c r="AM176" s="3" t="n"/>
+      <c r="AN176" s="3" t="n"/>
+      <c r="AO176" s="3" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="4" t="n"/>
@@ -6657,6 +8290,15 @@
       <c r="AD177" s="4" t="n"/>
       <c r="AE177" s="4" t="n"/>
       <c r="AF177" s="4" t="n"/>
+      <c r="AG177" s="4" t="n"/>
+      <c r="AH177" s="4" t="n"/>
+      <c r="AI177" s="4" t="n"/>
+      <c r="AJ177" s="4" t="n"/>
+      <c r="AK177" s="4" t="n"/>
+      <c r="AL177" s="4" t="n"/>
+      <c r="AM177" s="4" t="n"/>
+      <c r="AN177" s="4" t="n"/>
+      <c r="AO177" s="4" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="3" t="n"/>
@@ -6691,6 +8333,15 @@
       <c r="AD178" s="3" t="n"/>
       <c r="AE178" s="3" t="n"/>
       <c r="AF178" s="3" t="n"/>
+      <c r="AG178" s="3" t="n"/>
+      <c r="AH178" s="3" t="n"/>
+      <c r="AI178" s="3" t="n"/>
+      <c r="AJ178" s="3" t="n"/>
+      <c r="AK178" s="3" t="n"/>
+      <c r="AL178" s="3" t="n"/>
+      <c r="AM178" s="3" t="n"/>
+      <c r="AN178" s="3" t="n"/>
+      <c r="AO178" s="3" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="4" t="n"/>
@@ -6725,6 +8376,15 @@
       <c r="AD179" s="4" t="n"/>
       <c r="AE179" s="4" t="n"/>
       <c r="AF179" s="4" t="n"/>
+      <c r="AG179" s="4" t="n"/>
+      <c r="AH179" s="4" t="n"/>
+      <c r="AI179" s="4" t="n"/>
+      <c r="AJ179" s="4" t="n"/>
+      <c r="AK179" s="4" t="n"/>
+      <c r="AL179" s="4" t="n"/>
+      <c r="AM179" s="4" t="n"/>
+      <c r="AN179" s="4" t="n"/>
+      <c r="AO179" s="4" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="3" t="n"/>
@@ -6759,6 +8419,15 @@
       <c r="AD180" s="3" t="n"/>
       <c r="AE180" s="3" t="n"/>
       <c r="AF180" s="3" t="n"/>
+      <c r="AG180" s="3" t="n"/>
+      <c r="AH180" s="3" t="n"/>
+      <c r="AI180" s="3" t="n"/>
+      <c r="AJ180" s="3" t="n"/>
+      <c r="AK180" s="3" t="n"/>
+      <c r="AL180" s="3" t="n"/>
+      <c r="AM180" s="3" t="n"/>
+      <c r="AN180" s="3" t="n"/>
+      <c r="AO180" s="3" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="4" t="n"/>
@@ -6793,6 +8462,15 @@
       <c r="AD181" s="4" t="n"/>
       <c r="AE181" s="4" t="n"/>
       <c r="AF181" s="4" t="n"/>
+      <c r="AG181" s="4" t="n"/>
+      <c r="AH181" s="4" t="n"/>
+      <c r="AI181" s="4" t="n"/>
+      <c r="AJ181" s="4" t="n"/>
+      <c r="AK181" s="4" t="n"/>
+      <c r="AL181" s="4" t="n"/>
+      <c r="AM181" s="4" t="n"/>
+      <c r="AN181" s="4" t="n"/>
+      <c r="AO181" s="4" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="3" t="n"/>
@@ -6827,6 +8505,15 @@
       <c r="AD182" s="3" t="n"/>
       <c r="AE182" s="3" t="n"/>
       <c r="AF182" s="3" t="n"/>
+      <c r="AG182" s="3" t="n"/>
+      <c r="AH182" s="3" t="n"/>
+      <c r="AI182" s="3" t="n"/>
+      <c r="AJ182" s="3" t="n"/>
+      <c r="AK182" s="3" t="n"/>
+      <c r="AL182" s="3" t="n"/>
+      <c r="AM182" s="3" t="n"/>
+      <c r="AN182" s="3" t="n"/>
+      <c r="AO182" s="3" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="4" t="n"/>
@@ -6861,6 +8548,15 @@
       <c r="AD183" s="4" t="n"/>
       <c r="AE183" s="4" t="n"/>
       <c r="AF183" s="4" t="n"/>
+      <c r="AG183" s="4" t="n"/>
+      <c r="AH183" s="4" t="n"/>
+      <c r="AI183" s="4" t="n"/>
+      <c r="AJ183" s="4" t="n"/>
+      <c r="AK183" s="4" t="n"/>
+      <c r="AL183" s="4" t="n"/>
+      <c r="AM183" s="4" t="n"/>
+      <c r="AN183" s="4" t="n"/>
+      <c r="AO183" s="4" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="3" t="n"/>
@@ -6895,6 +8591,15 @@
       <c r="AD184" s="3" t="n"/>
       <c r="AE184" s="3" t="n"/>
       <c r="AF184" s="3" t="n"/>
+      <c r="AG184" s="3" t="n"/>
+      <c r="AH184" s="3" t="n"/>
+      <c r="AI184" s="3" t="n"/>
+      <c r="AJ184" s="3" t="n"/>
+      <c r="AK184" s="3" t="n"/>
+      <c r="AL184" s="3" t="n"/>
+      <c r="AM184" s="3" t="n"/>
+      <c r="AN184" s="3" t="n"/>
+      <c r="AO184" s="3" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="4" t="n"/>
@@ -6929,6 +8634,15 @@
       <c r="AD185" s="4" t="n"/>
       <c r="AE185" s="4" t="n"/>
       <c r="AF185" s="4" t="n"/>
+      <c r="AG185" s="4" t="n"/>
+      <c r="AH185" s="4" t="n"/>
+      <c r="AI185" s="4" t="n"/>
+      <c r="AJ185" s="4" t="n"/>
+      <c r="AK185" s="4" t="n"/>
+      <c r="AL185" s="4" t="n"/>
+      <c r="AM185" s="4" t="n"/>
+      <c r="AN185" s="4" t="n"/>
+      <c r="AO185" s="4" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="3" t="n"/>
@@ -6963,6 +8677,15 @@
       <c r="AD186" s="3" t="n"/>
       <c r="AE186" s="3" t="n"/>
       <c r="AF186" s="3" t="n"/>
+      <c r="AG186" s="3" t="n"/>
+      <c r="AH186" s="3" t="n"/>
+      <c r="AI186" s="3" t="n"/>
+      <c r="AJ186" s="3" t="n"/>
+      <c r="AK186" s="3" t="n"/>
+      <c r="AL186" s="3" t="n"/>
+      <c r="AM186" s="3" t="n"/>
+      <c r="AN186" s="3" t="n"/>
+      <c r="AO186" s="3" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="4" t="n"/>
@@ -6997,6 +8720,15 @@
       <c r="AD187" s="4" t="n"/>
       <c r="AE187" s="4" t="n"/>
       <c r="AF187" s="4" t="n"/>
+      <c r="AG187" s="4" t="n"/>
+      <c r="AH187" s="4" t="n"/>
+      <c r="AI187" s="4" t="n"/>
+      <c r="AJ187" s="4" t="n"/>
+      <c r="AK187" s="4" t="n"/>
+      <c r="AL187" s="4" t="n"/>
+      <c r="AM187" s="4" t="n"/>
+      <c r="AN187" s="4" t="n"/>
+      <c r="AO187" s="4" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="3" t="n"/>
@@ -7031,6 +8763,15 @@
       <c r="AD188" s="3" t="n"/>
       <c r="AE188" s="3" t="n"/>
       <c r="AF188" s="3" t="n"/>
+      <c r="AG188" s="3" t="n"/>
+      <c r="AH188" s="3" t="n"/>
+      <c r="AI188" s="3" t="n"/>
+      <c r="AJ188" s="3" t="n"/>
+      <c r="AK188" s="3" t="n"/>
+      <c r="AL188" s="3" t="n"/>
+      <c r="AM188" s="3" t="n"/>
+      <c r="AN188" s="3" t="n"/>
+      <c r="AO188" s="3" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="4" t="n"/>
@@ -7065,6 +8806,15 @@
       <c r="AD189" s="4" t="n"/>
       <c r="AE189" s="4" t="n"/>
       <c r="AF189" s="4" t="n"/>
+      <c r="AG189" s="4" t="n"/>
+      <c r="AH189" s="4" t="n"/>
+      <c r="AI189" s="4" t="n"/>
+      <c r="AJ189" s="4" t="n"/>
+      <c r="AK189" s="4" t="n"/>
+      <c r="AL189" s="4" t="n"/>
+      <c r="AM189" s="4" t="n"/>
+      <c r="AN189" s="4" t="n"/>
+      <c r="AO189" s="4" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="3" t="n"/>
@@ -7099,6 +8849,15 @@
       <c r="AD190" s="3" t="n"/>
       <c r="AE190" s="3" t="n"/>
       <c r="AF190" s="3" t="n"/>
+      <c r="AG190" s="3" t="n"/>
+      <c r="AH190" s="3" t="n"/>
+      <c r="AI190" s="3" t="n"/>
+      <c r="AJ190" s="3" t="n"/>
+      <c r="AK190" s="3" t="n"/>
+      <c r="AL190" s="3" t="n"/>
+      <c r="AM190" s="3" t="n"/>
+      <c r="AN190" s="3" t="n"/>
+      <c r="AO190" s="3" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="4" t="n"/>
@@ -7133,6 +8892,15 @@
       <c r="AD191" s="4" t="n"/>
       <c r="AE191" s="4" t="n"/>
       <c r="AF191" s="4" t="n"/>
+      <c r="AG191" s="4" t="n"/>
+      <c r="AH191" s="4" t="n"/>
+      <c r="AI191" s="4" t="n"/>
+      <c r="AJ191" s="4" t="n"/>
+      <c r="AK191" s="4" t="n"/>
+      <c r="AL191" s="4" t="n"/>
+      <c r="AM191" s="4" t="n"/>
+      <c r="AN191" s="4" t="n"/>
+      <c r="AO191" s="4" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="3" t="n"/>
@@ -7167,6 +8935,15 @@
       <c r="AD192" s="3" t="n"/>
       <c r="AE192" s="3" t="n"/>
       <c r="AF192" s="3" t="n"/>
+      <c r="AG192" s="3" t="n"/>
+      <c r="AH192" s="3" t="n"/>
+      <c r="AI192" s="3" t="n"/>
+      <c r="AJ192" s="3" t="n"/>
+      <c r="AK192" s="3" t="n"/>
+      <c r="AL192" s="3" t="n"/>
+      <c r="AM192" s="3" t="n"/>
+      <c r="AN192" s="3" t="n"/>
+      <c r="AO192" s="3" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="4" t="n"/>
@@ -7201,6 +8978,15 @@
       <c r="AD193" s="4" t="n"/>
       <c r="AE193" s="4" t="n"/>
       <c r="AF193" s="4" t="n"/>
+      <c r="AG193" s="4" t="n"/>
+      <c r="AH193" s="4" t="n"/>
+      <c r="AI193" s="4" t="n"/>
+      <c r="AJ193" s="4" t="n"/>
+      <c r="AK193" s="4" t="n"/>
+      <c r="AL193" s="4" t="n"/>
+      <c r="AM193" s="4" t="n"/>
+      <c r="AN193" s="4" t="n"/>
+      <c r="AO193" s="4" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="3" t="n"/>
@@ -7235,6 +9021,15 @@
       <c r="AD194" s="3" t="n"/>
       <c r="AE194" s="3" t="n"/>
       <c r="AF194" s="3" t="n"/>
+      <c r="AG194" s="3" t="n"/>
+      <c r="AH194" s="3" t="n"/>
+      <c r="AI194" s="3" t="n"/>
+      <c r="AJ194" s="3" t="n"/>
+      <c r="AK194" s="3" t="n"/>
+      <c r="AL194" s="3" t="n"/>
+      <c r="AM194" s="3" t="n"/>
+      <c r="AN194" s="3" t="n"/>
+      <c r="AO194" s="3" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="4" t="n"/>
@@ -7269,6 +9064,15 @@
       <c r="AD195" s="4" t="n"/>
       <c r="AE195" s="4" t="n"/>
       <c r="AF195" s="4" t="n"/>
+      <c r="AG195" s="4" t="n"/>
+      <c r="AH195" s="4" t="n"/>
+      <c r="AI195" s="4" t="n"/>
+      <c r="AJ195" s="4" t="n"/>
+      <c r="AK195" s="4" t="n"/>
+      <c r="AL195" s="4" t="n"/>
+      <c r="AM195" s="4" t="n"/>
+      <c r="AN195" s="4" t="n"/>
+      <c r="AO195" s="4" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="3" t="n"/>
@@ -7303,6 +9107,15 @@
       <c r="AD196" s="3" t="n"/>
       <c r="AE196" s="3" t="n"/>
       <c r="AF196" s="3" t="n"/>
+      <c r="AG196" s="3" t="n"/>
+      <c r="AH196" s="3" t="n"/>
+      <c r="AI196" s="3" t="n"/>
+      <c r="AJ196" s="3" t="n"/>
+      <c r="AK196" s="3" t="n"/>
+      <c r="AL196" s="3" t="n"/>
+      <c r="AM196" s="3" t="n"/>
+      <c r="AN196" s="3" t="n"/>
+      <c r="AO196" s="3" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="4" t="n"/>
@@ -7337,6 +9150,15 @@
       <c r="AD197" s="4" t="n"/>
       <c r="AE197" s="4" t="n"/>
       <c r="AF197" s="4" t="n"/>
+      <c r="AG197" s="4" t="n"/>
+      <c r="AH197" s="4" t="n"/>
+      <c r="AI197" s="4" t="n"/>
+      <c r="AJ197" s="4" t="n"/>
+      <c r="AK197" s="4" t="n"/>
+      <c r="AL197" s="4" t="n"/>
+      <c r="AM197" s="4" t="n"/>
+      <c r="AN197" s="4" t="n"/>
+      <c r="AO197" s="4" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="3" t="n"/>
@@ -7371,6 +9193,15 @@
       <c r="AD198" s="3" t="n"/>
       <c r="AE198" s="3" t="n"/>
       <c r="AF198" s="3" t="n"/>
+      <c r="AG198" s="3" t="n"/>
+      <c r="AH198" s="3" t="n"/>
+      <c r="AI198" s="3" t="n"/>
+      <c r="AJ198" s="3" t="n"/>
+      <c r="AK198" s="3" t="n"/>
+      <c r="AL198" s="3" t="n"/>
+      <c r="AM198" s="3" t="n"/>
+      <c r="AN198" s="3" t="n"/>
+      <c r="AO198" s="3" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="4" t="n"/>
@@ -7405,6 +9236,15 @@
       <c r="AD199" s="4" t="n"/>
       <c r="AE199" s="4" t="n"/>
       <c r="AF199" s="4" t="n"/>
+      <c r="AG199" s="4" t="n"/>
+      <c r="AH199" s="4" t="n"/>
+      <c r="AI199" s="4" t="n"/>
+      <c r="AJ199" s="4" t="n"/>
+      <c r="AK199" s="4" t="n"/>
+      <c r="AL199" s="4" t="n"/>
+      <c r="AM199" s="4" t="n"/>
+      <c r="AN199" s="4" t="n"/>
+      <c r="AO199" s="4" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="3" t="n"/>
@@ -7439,6 +9279,15 @@
       <c r="AD200" s="3" t="n"/>
       <c r="AE200" s="3" t="n"/>
       <c r="AF200" s="3" t="n"/>
+      <c r="AG200" s="3" t="n"/>
+      <c r="AH200" s="3" t="n"/>
+      <c r="AI200" s="3" t="n"/>
+      <c r="AJ200" s="3" t="n"/>
+      <c r="AK200" s="3" t="n"/>
+      <c r="AL200" s="3" t="n"/>
+      <c r="AM200" s="3" t="n"/>
+      <c r="AN200" s="3" t="n"/>
+      <c r="AO200" s="3" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="4" t="n"/>
@@ -7473,6 +9322,15 @@
       <c r="AD201" s="4" t="n"/>
       <c r="AE201" s="4" t="n"/>
       <c r="AF201" s="4" t="n"/>
+      <c r="AG201" s="4" t="n"/>
+      <c r="AH201" s="4" t="n"/>
+      <c r="AI201" s="4" t="n"/>
+      <c r="AJ201" s="4" t="n"/>
+      <c r="AK201" s="4" t="n"/>
+      <c r="AL201" s="4" t="n"/>
+      <c r="AM201" s="4" t="n"/>
+      <c r="AN201" s="4" t="n"/>
+      <c r="AO201" s="4" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="3" t="n"/>
@@ -7507,6 +9365,15 @@
       <c r="AD202" s="3" t="n"/>
       <c r="AE202" s="3" t="n"/>
       <c r="AF202" s="3" t="n"/>
+      <c r="AG202" s="3" t="n"/>
+      <c r="AH202" s="3" t="n"/>
+      <c r="AI202" s="3" t="n"/>
+      <c r="AJ202" s="3" t="n"/>
+      <c r="AK202" s="3" t="n"/>
+      <c r="AL202" s="3" t="n"/>
+      <c r="AM202" s="3" t="n"/>
+      <c r="AN202" s="3" t="n"/>
+      <c r="AO202" s="3" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="4" t="n"/>
@@ -7541,6 +9408,15 @@
       <c r="AD203" s="4" t="n"/>
       <c r="AE203" s="4" t="n"/>
       <c r="AF203" s="4" t="n"/>
+      <c r="AG203" s="4" t="n"/>
+      <c r="AH203" s="4" t="n"/>
+      <c r="AI203" s="4" t="n"/>
+      <c r="AJ203" s="4" t="n"/>
+      <c r="AK203" s="4" t="n"/>
+      <c r="AL203" s="4" t="n"/>
+      <c r="AM203" s="4" t="n"/>
+      <c r="AN203" s="4" t="n"/>
+      <c r="AO203" s="4" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="3" t="n"/>
@@ -7575,6 +9451,15 @@
       <c r="AD204" s="3" t="n"/>
       <c r="AE204" s="3" t="n"/>
       <c r="AF204" s="3" t="n"/>
+      <c r="AG204" s="3" t="n"/>
+      <c r="AH204" s="3" t="n"/>
+      <c r="AI204" s="3" t="n"/>
+      <c r="AJ204" s="3" t="n"/>
+      <c r="AK204" s="3" t="n"/>
+      <c r="AL204" s="3" t="n"/>
+      <c r="AM204" s="3" t="n"/>
+      <c r="AN204" s="3" t="n"/>
+      <c r="AO204" s="3" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="4" t="n"/>
@@ -7609,6 +9494,15 @@
       <c r="AD205" s="4" t="n"/>
       <c r="AE205" s="4" t="n"/>
       <c r="AF205" s="4" t="n"/>
+      <c r="AG205" s="4" t="n"/>
+      <c r="AH205" s="4" t="n"/>
+      <c r="AI205" s="4" t="n"/>
+      <c r="AJ205" s="4" t="n"/>
+      <c r="AK205" s="4" t="n"/>
+      <c r="AL205" s="4" t="n"/>
+      <c r="AM205" s="4" t="n"/>
+      <c r="AN205" s="4" t="n"/>
+      <c r="AO205" s="4" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="3" t="n"/>
@@ -7643,6 +9537,15 @@
       <c r="AD206" s="3" t="n"/>
       <c r="AE206" s="3" t="n"/>
       <c r="AF206" s="3" t="n"/>
+      <c r="AG206" s="3" t="n"/>
+      <c r="AH206" s="3" t="n"/>
+      <c r="AI206" s="3" t="n"/>
+      <c r="AJ206" s="3" t="n"/>
+      <c r="AK206" s="3" t="n"/>
+      <c r="AL206" s="3" t="n"/>
+      <c r="AM206" s="3" t="n"/>
+      <c r="AN206" s="3" t="n"/>
+      <c r="AO206" s="3" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="4" t="n"/>
@@ -7677,6 +9580,15 @@
       <c r="AD207" s="4" t="n"/>
       <c r="AE207" s="4" t="n"/>
       <c r="AF207" s="4" t="n"/>
+      <c r="AG207" s="4" t="n"/>
+      <c r="AH207" s="4" t="n"/>
+      <c r="AI207" s="4" t="n"/>
+      <c r="AJ207" s="4" t="n"/>
+      <c r="AK207" s="4" t="n"/>
+      <c r="AL207" s="4" t="n"/>
+      <c r="AM207" s="4" t="n"/>
+      <c r="AN207" s="4" t="n"/>
+      <c r="AO207" s="4" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="3" t="n"/>
@@ -7711,6 +9623,15 @@
       <c r="AD208" s="3" t="n"/>
       <c r="AE208" s="3" t="n"/>
       <c r="AF208" s="3" t="n"/>
+      <c r="AG208" s="3" t="n"/>
+      <c r="AH208" s="3" t="n"/>
+      <c r="AI208" s="3" t="n"/>
+      <c r="AJ208" s="3" t="n"/>
+      <c r="AK208" s="3" t="n"/>
+      <c r="AL208" s="3" t="n"/>
+      <c r="AM208" s="3" t="n"/>
+      <c r="AN208" s="3" t="n"/>
+      <c r="AO208" s="3" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="4" t="n"/>
@@ -7745,6 +9666,15 @@
       <c r="AD209" s="4" t="n"/>
       <c r="AE209" s="4" t="n"/>
       <c r="AF209" s="4" t="n"/>
+      <c r="AG209" s="4" t="n"/>
+      <c r="AH209" s="4" t="n"/>
+      <c r="AI209" s="4" t="n"/>
+      <c r="AJ209" s="4" t="n"/>
+      <c r="AK209" s="4" t="n"/>
+      <c r="AL209" s="4" t="n"/>
+      <c r="AM209" s="4" t="n"/>
+      <c r="AN209" s="4" t="n"/>
+      <c r="AO209" s="4" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="3" t="n"/>
@@ -7779,6 +9709,15 @@
       <c r="AD210" s="3" t="n"/>
       <c r="AE210" s="3" t="n"/>
       <c r="AF210" s="3" t="n"/>
+      <c r="AG210" s="3" t="n"/>
+      <c r="AH210" s="3" t="n"/>
+      <c r="AI210" s="3" t="n"/>
+      <c r="AJ210" s="3" t="n"/>
+      <c r="AK210" s="3" t="n"/>
+      <c r="AL210" s="3" t="n"/>
+      <c r="AM210" s="3" t="n"/>
+      <c r="AN210" s="3" t="n"/>
+      <c r="AO210" s="3" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="4" t="n"/>
@@ -7813,6 +9752,15 @@
       <c r="AD211" s="4" t="n"/>
       <c r="AE211" s="4" t="n"/>
       <c r="AF211" s="4" t="n"/>
+      <c r="AG211" s="4" t="n"/>
+      <c r="AH211" s="4" t="n"/>
+      <c r="AI211" s="4" t="n"/>
+      <c r="AJ211" s="4" t="n"/>
+      <c r="AK211" s="4" t="n"/>
+      <c r="AL211" s="4" t="n"/>
+      <c r="AM211" s="4" t="n"/>
+      <c r="AN211" s="4" t="n"/>
+      <c r="AO211" s="4" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="3" t="n"/>
@@ -7847,6 +9795,15 @@
       <c r="AD212" s="3" t="n"/>
       <c r="AE212" s="3" t="n"/>
       <c r="AF212" s="3" t="n"/>
+      <c r="AG212" s="3" t="n"/>
+      <c r="AH212" s="3" t="n"/>
+      <c r="AI212" s="3" t="n"/>
+      <c r="AJ212" s="3" t="n"/>
+      <c r="AK212" s="3" t="n"/>
+      <c r="AL212" s="3" t="n"/>
+      <c r="AM212" s="3" t="n"/>
+      <c r="AN212" s="3" t="n"/>
+      <c r="AO212" s="3" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="4" t="n"/>
@@ -7881,6 +9838,15 @@
       <c r="AD213" s="4" t="n"/>
       <c r="AE213" s="4" t="n"/>
       <c r="AF213" s="4" t="n"/>
+      <c r="AG213" s="4" t="n"/>
+      <c r="AH213" s="4" t="n"/>
+      <c r="AI213" s="4" t="n"/>
+      <c r="AJ213" s="4" t="n"/>
+      <c r="AK213" s="4" t="n"/>
+      <c r="AL213" s="4" t="n"/>
+      <c r="AM213" s="4" t="n"/>
+      <c r="AN213" s="4" t="n"/>
+      <c r="AO213" s="4" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="3" t="n"/>
@@ -7915,6 +9881,15 @@
       <c r="AD214" s="3" t="n"/>
       <c r="AE214" s="3" t="n"/>
       <c r="AF214" s="3" t="n"/>
+      <c r="AG214" s="3" t="n"/>
+      <c r="AH214" s="3" t="n"/>
+      <c r="AI214" s="3" t="n"/>
+      <c r="AJ214" s="3" t="n"/>
+      <c r="AK214" s="3" t="n"/>
+      <c r="AL214" s="3" t="n"/>
+      <c r="AM214" s="3" t="n"/>
+      <c r="AN214" s="3" t="n"/>
+      <c r="AO214" s="3" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="4" t="n"/>
@@ -7949,6 +9924,15 @@
       <c r="AD215" s="4" t="n"/>
       <c r="AE215" s="4" t="n"/>
       <c r="AF215" s="4" t="n"/>
+      <c r="AG215" s="4" t="n"/>
+      <c r="AH215" s="4" t="n"/>
+      <c r="AI215" s="4" t="n"/>
+      <c r="AJ215" s="4" t="n"/>
+      <c r="AK215" s="4" t="n"/>
+      <c r="AL215" s="4" t="n"/>
+      <c r="AM215" s="4" t="n"/>
+      <c r="AN215" s="4" t="n"/>
+      <c r="AO215" s="4" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="3" t="n"/>
@@ -7983,6 +9967,15 @@
       <c r="AD216" s="3" t="n"/>
       <c r="AE216" s="3" t="n"/>
       <c r="AF216" s="3" t="n"/>
+      <c r="AG216" s="3" t="n"/>
+      <c r="AH216" s="3" t="n"/>
+      <c r="AI216" s="3" t="n"/>
+      <c r="AJ216" s="3" t="n"/>
+      <c r="AK216" s="3" t="n"/>
+      <c r="AL216" s="3" t="n"/>
+      <c r="AM216" s="3" t="n"/>
+      <c r="AN216" s="3" t="n"/>
+      <c r="AO216" s="3" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="4" t="n"/>
@@ -8017,6 +10010,15 @@
       <c r="AD217" s="4" t="n"/>
       <c r="AE217" s="4" t="n"/>
       <c r="AF217" s="4" t="n"/>
+      <c r="AG217" s="4" t="n"/>
+      <c r="AH217" s="4" t="n"/>
+      <c r="AI217" s="4" t="n"/>
+      <c r="AJ217" s="4" t="n"/>
+      <c r="AK217" s="4" t="n"/>
+      <c r="AL217" s="4" t="n"/>
+      <c r="AM217" s="4" t="n"/>
+      <c r="AN217" s="4" t="n"/>
+      <c r="AO217" s="4" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="3" t="n"/>
@@ -8051,6 +10053,15 @@
       <c r="AD218" s="3" t="n"/>
       <c r="AE218" s="3" t="n"/>
       <c r="AF218" s="3" t="n"/>
+      <c r="AG218" s="3" t="n"/>
+      <c r="AH218" s="3" t="n"/>
+      <c r="AI218" s="3" t="n"/>
+      <c r="AJ218" s="3" t="n"/>
+      <c r="AK218" s="3" t="n"/>
+      <c r="AL218" s="3" t="n"/>
+      <c r="AM218" s="3" t="n"/>
+      <c r="AN218" s="3" t="n"/>
+      <c r="AO218" s="3" t="n"/>
     </row>
     <row r="219">
       <c r="A219" s="4" t="n"/>
@@ -8085,6 +10096,15 @@
       <c r="AD219" s="4" t="n"/>
       <c r="AE219" s="4" t="n"/>
       <c r="AF219" s="4" t="n"/>
+      <c r="AG219" s="4" t="n"/>
+      <c r="AH219" s="4" t="n"/>
+      <c r="AI219" s="4" t="n"/>
+      <c r="AJ219" s="4" t="n"/>
+      <c r="AK219" s="4" t="n"/>
+      <c r="AL219" s="4" t="n"/>
+      <c r="AM219" s="4" t="n"/>
+      <c r="AN219" s="4" t="n"/>
+      <c r="AO219" s="4" t="n"/>
     </row>
     <row r="220">
       <c r="A220" s="3" t="n"/>
@@ -8119,6 +10139,15 @@
       <c r="AD220" s="3" t="n"/>
       <c r="AE220" s="3" t="n"/>
       <c r="AF220" s="3" t="n"/>
+      <c r="AG220" s="3" t="n"/>
+      <c r="AH220" s="3" t="n"/>
+      <c r="AI220" s="3" t="n"/>
+      <c r="AJ220" s="3" t="n"/>
+      <c r="AK220" s="3" t="n"/>
+      <c r="AL220" s="3" t="n"/>
+      <c r="AM220" s="3" t="n"/>
+      <c r="AN220" s="3" t="n"/>
+      <c r="AO220" s="3" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="4" t="n"/>
@@ -8153,6 +10182,15 @@
       <c r="AD221" s="4" t="n"/>
       <c r="AE221" s="4" t="n"/>
       <c r="AF221" s="4" t="n"/>
+      <c r="AG221" s="4" t="n"/>
+      <c r="AH221" s="4" t="n"/>
+      <c r="AI221" s="4" t="n"/>
+      <c r="AJ221" s="4" t="n"/>
+      <c r="AK221" s="4" t="n"/>
+      <c r="AL221" s="4" t="n"/>
+      <c r="AM221" s="4" t="n"/>
+      <c r="AN221" s="4" t="n"/>
+      <c r="AO221" s="4" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="3" t="n"/>
@@ -8187,6 +10225,15 @@
       <c r="AD222" s="3" t="n"/>
       <c r="AE222" s="3" t="n"/>
       <c r="AF222" s="3" t="n"/>
+      <c r="AG222" s="3" t="n"/>
+      <c r="AH222" s="3" t="n"/>
+      <c r="AI222" s="3" t="n"/>
+      <c r="AJ222" s="3" t="n"/>
+      <c r="AK222" s="3" t="n"/>
+      <c r="AL222" s="3" t="n"/>
+      <c r="AM222" s="3" t="n"/>
+      <c r="AN222" s="3" t="n"/>
+      <c r="AO222" s="3" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="4" t="n"/>
@@ -8221,6 +10268,15 @@
       <c r="AD223" s="4" t="n"/>
       <c r="AE223" s="4" t="n"/>
       <c r="AF223" s="4" t="n"/>
+      <c r="AG223" s="4" t="n"/>
+      <c r="AH223" s="4" t="n"/>
+      <c r="AI223" s="4" t="n"/>
+      <c r="AJ223" s="4" t="n"/>
+      <c r="AK223" s="4" t="n"/>
+      <c r="AL223" s="4" t="n"/>
+      <c r="AM223" s="4" t="n"/>
+      <c r="AN223" s="4" t="n"/>
+      <c r="AO223" s="4" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="3" t="n"/>
@@ -8255,6 +10311,15 @@
       <c r="AD224" s="3" t="n"/>
       <c r="AE224" s="3" t="n"/>
       <c r="AF224" s="3" t="n"/>
+      <c r="AG224" s="3" t="n"/>
+      <c r="AH224" s="3" t="n"/>
+      <c r="AI224" s="3" t="n"/>
+      <c r="AJ224" s="3" t="n"/>
+      <c r="AK224" s="3" t="n"/>
+      <c r="AL224" s="3" t="n"/>
+      <c r="AM224" s="3" t="n"/>
+      <c r="AN224" s="3" t="n"/>
+      <c r="AO224" s="3" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="4" t="n"/>
@@ -8289,6 +10354,15 @@
       <c r="AD225" s="4" t="n"/>
       <c r="AE225" s="4" t="n"/>
       <c r="AF225" s="4" t="n"/>
+      <c r="AG225" s="4" t="n"/>
+      <c r="AH225" s="4" t="n"/>
+      <c r="AI225" s="4" t="n"/>
+      <c r="AJ225" s="4" t="n"/>
+      <c r="AK225" s="4" t="n"/>
+      <c r="AL225" s="4" t="n"/>
+      <c r="AM225" s="4" t="n"/>
+      <c r="AN225" s="4" t="n"/>
+      <c r="AO225" s="4" t="n"/>
     </row>
     <row r="226">
       <c r="A226" s="3" t="n"/>
@@ -8323,6 +10397,15 @@
       <c r="AD226" s="3" t="n"/>
       <c r="AE226" s="3" t="n"/>
       <c r="AF226" s="3" t="n"/>
+      <c r="AG226" s="3" t="n"/>
+      <c r="AH226" s="3" t="n"/>
+      <c r="AI226" s="3" t="n"/>
+      <c r="AJ226" s="3" t="n"/>
+      <c r="AK226" s="3" t="n"/>
+      <c r="AL226" s="3" t="n"/>
+      <c r="AM226" s="3" t="n"/>
+      <c r="AN226" s="3" t="n"/>
+      <c r="AO226" s="3" t="n"/>
     </row>
     <row r="227">
       <c r="A227" s="4" t="n"/>
@@ -8357,6 +10440,15 @@
       <c r="AD227" s="4" t="n"/>
       <c r="AE227" s="4" t="n"/>
       <c r="AF227" s="4" t="n"/>
+      <c r="AG227" s="4" t="n"/>
+      <c r="AH227" s="4" t="n"/>
+      <c r="AI227" s="4" t="n"/>
+      <c r="AJ227" s="4" t="n"/>
+      <c r="AK227" s="4" t="n"/>
+      <c r="AL227" s="4" t="n"/>
+      <c r="AM227" s="4" t="n"/>
+      <c r="AN227" s="4" t="n"/>
+      <c r="AO227" s="4" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="3" t="n"/>
@@ -8391,6 +10483,15 @@
       <c r="AD228" s="3" t="n"/>
       <c r="AE228" s="3" t="n"/>
       <c r="AF228" s="3" t="n"/>
+      <c r="AG228" s="3" t="n"/>
+      <c r="AH228" s="3" t="n"/>
+      <c r="AI228" s="3" t="n"/>
+      <c r="AJ228" s="3" t="n"/>
+      <c r="AK228" s="3" t="n"/>
+      <c r="AL228" s="3" t="n"/>
+      <c r="AM228" s="3" t="n"/>
+      <c r="AN228" s="3" t="n"/>
+      <c r="AO228" s="3" t="n"/>
     </row>
     <row r="229">
       <c r="A229" s="4" t="n"/>
@@ -8425,6 +10526,15 @@
       <c r="AD229" s="4" t="n"/>
       <c r="AE229" s="4" t="n"/>
       <c r="AF229" s="4" t="n"/>
+      <c r="AG229" s="4" t="n"/>
+      <c r="AH229" s="4" t="n"/>
+      <c r="AI229" s="4" t="n"/>
+      <c r="AJ229" s="4" t="n"/>
+      <c r="AK229" s="4" t="n"/>
+      <c r="AL229" s="4" t="n"/>
+      <c r="AM229" s="4" t="n"/>
+      <c r="AN229" s="4" t="n"/>
+      <c r="AO229" s="4" t="n"/>
     </row>
     <row r="230">
       <c r="A230" s="3" t="n"/>
@@ -8459,6 +10569,15 @@
       <c r="AD230" s="3" t="n"/>
       <c r="AE230" s="3" t="n"/>
       <c r="AF230" s="3" t="n"/>
+      <c r="AG230" s="3" t="n"/>
+      <c r="AH230" s="3" t="n"/>
+      <c r="AI230" s="3" t="n"/>
+      <c r="AJ230" s="3" t="n"/>
+      <c r="AK230" s="3" t="n"/>
+      <c r="AL230" s="3" t="n"/>
+      <c r="AM230" s="3" t="n"/>
+      <c r="AN230" s="3" t="n"/>
+      <c r="AO230" s="3" t="n"/>
     </row>
     <row r="231">
       <c r="A231" s="4" t="n"/>
@@ -8493,6 +10612,15 @@
       <c r="AD231" s="4" t="n"/>
       <c r="AE231" s="4" t="n"/>
       <c r="AF231" s="4" t="n"/>
+      <c r="AG231" s="4" t="n"/>
+      <c r="AH231" s="4" t="n"/>
+      <c r="AI231" s="4" t="n"/>
+      <c r="AJ231" s="4" t="n"/>
+      <c r="AK231" s="4" t="n"/>
+      <c r="AL231" s="4" t="n"/>
+      <c r="AM231" s="4" t="n"/>
+      <c r="AN231" s="4" t="n"/>
+      <c r="AO231" s="4" t="n"/>
     </row>
     <row r="232">
       <c r="A232" s="3" t="n"/>
@@ -8527,6 +10655,15 @@
       <c r="AD232" s="3" t="n"/>
       <c r="AE232" s="3" t="n"/>
       <c r="AF232" s="3" t="n"/>
+      <c r="AG232" s="3" t="n"/>
+      <c r="AH232" s="3" t="n"/>
+      <c r="AI232" s="3" t="n"/>
+      <c r="AJ232" s="3" t="n"/>
+      <c r="AK232" s="3" t="n"/>
+      <c r="AL232" s="3" t="n"/>
+      <c r="AM232" s="3" t="n"/>
+      <c r="AN232" s="3" t="n"/>
+      <c r="AO232" s="3" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="4" t="n"/>
@@ -8561,6 +10698,15 @@
       <c r="AD233" s="4" t="n"/>
       <c r="AE233" s="4" t="n"/>
       <c r="AF233" s="4" t="n"/>
+      <c r="AG233" s="4" t="n"/>
+      <c r="AH233" s="4" t="n"/>
+      <c r="AI233" s="4" t="n"/>
+      <c r="AJ233" s="4" t="n"/>
+      <c r="AK233" s="4" t="n"/>
+      <c r="AL233" s="4" t="n"/>
+      <c r="AM233" s="4" t="n"/>
+      <c r="AN233" s="4" t="n"/>
+      <c r="AO233" s="4" t="n"/>
     </row>
     <row r="234">
       <c r="A234" s="3" t="n"/>
@@ -8595,6 +10741,15 @@
       <c r="AD234" s="3" t="n"/>
       <c r="AE234" s="3" t="n"/>
       <c r="AF234" s="3" t="n"/>
+      <c r="AG234" s="3" t="n"/>
+      <c r="AH234" s="3" t="n"/>
+      <c r="AI234" s="3" t="n"/>
+      <c r="AJ234" s="3" t="n"/>
+      <c r="AK234" s="3" t="n"/>
+      <c r="AL234" s="3" t="n"/>
+      <c r="AM234" s="3" t="n"/>
+      <c r="AN234" s="3" t="n"/>
+      <c r="AO234" s="3" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="4" t="n"/>
@@ -8629,6 +10784,15 @@
       <c r="AD235" s="4" t="n"/>
       <c r="AE235" s="4" t="n"/>
       <c r="AF235" s="4" t="n"/>
+      <c r="AG235" s="4" t="n"/>
+      <c r="AH235" s="4" t="n"/>
+      <c r="AI235" s="4" t="n"/>
+      <c r="AJ235" s="4" t="n"/>
+      <c r="AK235" s="4" t="n"/>
+      <c r="AL235" s="4" t="n"/>
+      <c r="AM235" s="4" t="n"/>
+      <c r="AN235" s="4" t="n"/>
+      <c r="AO235" s="4" t="n"/>
     </row>
     <row r="236">
       <c r="A236" s="3" t="n"/>
@@ -8663,6 +10827,15 @@
       <c r="AD236" s="3" t="n"/>
       <c r="AE236" s="3" t="n"/>
       <c r="AF236" s="3" t="n"/>
+      <c r="AG236" s="3" t="n"/>
+      <c r="AH236" s="3" t="n"/>
+      <c r="AI236" s="3" t="n"/>
+      <c r="AJ236" s="3" t="n"/>
+      <c r="AK236" s="3" t="n"/>
+      <c r="AL236" s="3" t="n"/>
+      <c r="AM236" s="3" t="n"/>
+      <c r="AN236" s="3" t="n"/>
+      <c r="AO236" s="3" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="4" t="n"/>
@@ -8697,6 +10870,15 @@
       <c r="AD237" s="4" t="n"/>
       <c r="AE237" s="4" t="n"/>
       <c r="AF237" s="4" t="n"/>
+      <c r="AG237" s="4" t="n"/>
+      <c r="AH237" s="4" t="n"/>
+      <c r="AI237" s="4" t="n"/>
+      <c r="AJ237" s="4" t="n"/>
+      <c r="AK237" s="4" t="n"/>
+      <c r="AL237" s="4" t="n"/>
+      <c r="AM237" s="4" t="n"/>
+      <c r="AN237" s="4" t="n"/>
+      <c r="AO237" s="4" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="3" t="n"/>
@@ -8731,6 +10913,15 @@
       <c r="AD238" s="3" t="n"/>
       <c r="AE238" s="3" t="n"/>
       <c r="AF238" s="3" t="n"/>
+      <c r="AG238" s="3" t="n"/>
+      <c r="AH238" s="3" t="n"/>
+      <c r="AI238" s="3" t="n"/>
+      <c r="AJ238" s="3" t="n"/>
+      <c r="AK238" s="3" t="n"/>
+      <c r="AL238" s="3" t="n"/>
+      <c r="AM238" s="3" t="n"/>
+      <c r="AN238" s="3" t="n"/>
+      <c r="AO238" s="3" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="4" t="n"/>
@@ -8765,6 +10956,15 @@
       <c r="AD239" s="4" t="n"/>
       <c r="AE239" s="4" t="n"/>
       <c r="AF239" s="4" t="n"/>
+      <c r="AG239" s="4" t="n"/>
+      <c r="AH239" s="4" t="n"/>
+      <c r="AI239" s="4" t="n"/>
+      <c r="AJ239" s="4" t="n"/>
+      <c r="AK239" s="4" t="n"/>
+      <c r="AL239" s="4" t="n"/>
+      <c r="AM239" s="4" t="n"/>
+      <c r="AN239" s="4" t="n"/>
+      <c r="AO239" s="4" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="3" t="n"/>
@@ -8799,6 +10999,15 @@
       <c r="AD240" s="3" t="n"/>
       <c r="AE240" s="3" t="n"/>
       <c r="AF240" s="3" t="n"/>
+      <c r="AG240" s="3" t="n"/>
+      <c r="AH240" s="3" t="n"/>
+      <c r="AI240" s="3" t="n"/>
+      <c r="AJ240" s="3" t="n"/>
+      <c r="AK240" s="3" t="n"/>
+      <c r="AL240" s="3" t="n"/>
+      <c r="AM240" s="3" t="n"/>
+      <c r="AN240" s="3" t="n"/>
+      <c r="AO240" s="3" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="4" t="n"/>
@@ -8833,6 +11042,15 @@
       <c r="AD241" s="4" t="n"/>
       <c r="AE241" s="4" t="n"/>
       <c r="AF241" s="4" t="n"/>
+      <c r="AG241" s="4" t="n"/>
+      <c r="AH241" s="4" t="n"/>
+      <c r="AI241" s="4" t="n"/>
+      <c r="AJ241" s="4" t="n"/>
+      <c r="AK241" s="4" t="n"/>
+      <c r="AL241" s="4" t="n"/>
+      <c r="AM241" s="4" t="n"/>
+      <c r="AN241" s="4" t="n"/>
+      <c r="AO241" s="4" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="3" t="n"/>
@@ -8867,6 +11085,15 @@
       <c r="AD242" s="3" t="n"/>
       <c r="AE242" s="3" t="n"/>
       <c r="AF242" s="3" t="n"/>
+      <c r="AG242" s="3" t="n"/>
+      <c r="AH242" s="3" t="n"/>
+      <c r="AI242" s="3" t="n"/>
+      <c r="AJ242" s="3" t="n"/>
+      <c r="AK242" s="3" t="n"/>
+      <c r="AL242" s="3" t="n"/>
+      <c r="AM242" s="3" t="n"/>
+      <c r="AN242" s="3" t="n"/>
+      <c r="AO242" s="3" t="n"/>
     </row>
     <row r="243">
       <c r="A243" s="4" t="n"/>
@@ -8901,6 +11128,15 @@
       <c r="AD243" s="4" t="n"/>
       <c r="AE243" s="4" t="n"/>
       <c r="AF243" s="4" t="n"/>
+      <c r="AG243" s="4" t="n"/>
+      <c r="AH243" s="4" t="n"/>
+      <c r="AI243" s="4" t="n"/>
+      <c r="AJ243" s="4" t="n"/>
+      <c r="AK243" s="4" t="n"/>
+      <c r="AL243" s="4" t="n"/>
+      <c r="AM243" s="4" t="n"/>
+      <c r="AN243" s="4" t="n"/>
+      <c r="AO243" s="4" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="3" t="n"/>
@@ -8935,6 +11171,15 @@
       <c r="AD244" s="3" t="n"/>
       <c r="AE244" s="3" t="n"/>
       <c r="AF244" s="3" t="n"/>
+      <c r="AG244" s="3" t="n"/>
+      <c r="AH244" s="3" t="n"/>
+      <c r="AI244" s="3" t="n"/>
+      <c r="AJ244" s="3" t="n"/>
+      <c r="AK244" s="3" t="n"/>
+      <c r="AL244" s="3" t="n"/>
+      <c r="AM244" s="3" t="n"/>
+      <c r="AN244" s="3" t="n"/>
+      <c r="AO244" s="3" t="n"/>
     </row>
     <row r="245">
       <c r="A245" s="4" t="n"/>
@@ -8969,6 +11214,15 @@
       <c r="AD245" s="4" t="n"/>
       <c r="AE245" s="4" t="n"/>
       <c r="AF245" s="4" t="n"/>
+      <c r="AG245" s="4" t="n"/>
+      <c r="AH245" s="4" t="n"/>
+      <c r="AI245" s="4" t="n"/>
+      <c r="AJ245" s="4" t="n"/>
+      <c r="AK245" s="4" t="n"/>
+      <c r="AL245" s="4" t="n"/>
+      <c r="AM245" s="4" t="n"/>
+      <c r="AN245" s="4" t="n"/>
+      <c r="AO245" s="4" t="n"/>
     </row>
     <row r="246">
       <c r="A246" s="3" t="n"/>
@@ -9003,6 +11257,15 @@
       <c r="AD246" s="3" t="n"/>
       <c r="AE246" s="3" t="n"/>
       <c r="AF246" s="3" t="n"/>
+      <c r="AG246" s="3" t="n"/>
+      <c r="AH246" s="3" t="n"/>
+      <c r="AI246" s="3" t="n"/>
+      <c r="AJ246" s="3" t="n"/>
+      <c r="AK246" s="3" t="n"/>
+      <c r="AL246" s="3" t="n"/>
+      <c r="AM246" s="3" t="n"/>
+      <c r="AN246" s="3" t="n"/>
+      <c r="AO246" s="3" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="4" t="n"/>
@@ -9037,6 +11300,15 @@
       <c r="AD247" s="4" t="n"/>
       <c r="AE247" s="4" t="n"/>
       <c r="AF247" s="4" t="n"/>
+      <c r="AG247" s="4" t="n"/>
+      <c r="AH247" s="4" t="n"/>
+      <c r="AI247" s="4" t="n"/>
+      <c r="AJ247" s="4" t="n"/>
+      <c r="AK247" s="4" t="n"/>
+      <c r="AL247" s="4" t="n"/>
+      <c r="AM247" s="4" t="n"/>
+      <c r="AN247" s="4" t="n"/>
+      <c r="AO247" s="4" t="n"/>
     </row>
     <row r="248">
       <c r="A248" s="3" t="n"/>
@@ -9071,6 +11343,15 @@
       <c r="AD248" s="3" t="n"/>
       <c r="AE248" s="3" t="n"/>
       <c r="AF248" s="3" t="n"/>
+      <c r="AG248" s="3" t="n"/>
+      <c r="AH248" s="3" t="n"/>
+      <c r="AI248" s="3" t="n"/>
+      <c r="AJ248" s="3" t="n"/>
+      <c r="AK248" s="3" t="n"/>
+      <c r="AL248" s="3" t="n"/>
+      <c r="AM248" s="3" t="n"/>
+      <c r="AN248" s="3" t="n"/>
+      <c r="AO248" s="3" t="n"/>
     </row>
     <row r="249">
       <c r="A249" s="4" t="n"/>
@@ -9105,6 +11386,15 @@
       <c r="AD249" s="4" t="n"/>
       <c r="AE249" s="4" t="n"/>
       <c r="AF249" s="4" t="n"/>
+      <c r="AG249" s="4" t="n"/>
+      <c r="AH249" s="4" t="n"/>
+      <c r="AI249" s="4" t="n"/>
+      <c r="AJ249" s="4" t="n"/>
+      <c r="AK249" s="4" t="n"/>
+      <c r="AL249" s="4" t="n"/>
+      <c r="AM249" s="4" t="n"/>
+      <c r="AN249" s="4" t="n"/>
+      <c r="AO249" s="4" t="n"/>
     </row>
     <row r="250">
       <c r="A250" s="3" t="n"/>
@@ -9139,6 +11429,15 @@
       <c r="AD250" s="3" t="n"/>
       <c r="AE250" s="3" t="n"/>
       <c r="AF250" s="3" t="n"/>
+      <c r="AG250" s="3" t="n"/>
+      <c r="AH250" s="3" t="n"/>
+      <c r="AI250" s="3" t="n"/>
+      <c r="AJ250" s="3" t="n"/>
+      <c r="AK250" s="3" t="n"/>
+      <c r="AL250" s="3" t="n"/>
+      <c r="AM250" s="3" t="n"/>
+      <c r="AN250" s="3" t="n"/>
+      <c r="AO250" s="3" t="n"/>
     </row>
     <row r="251">
       <c r="A251" s="4" t="n"/>
@@ -9173,6 +11472,15 @@
       <c r="AD251" s="4" t="n"/>
       <c r="AE251" s="4" t="n"/>
       <c r="AF251" s="4" t="n"/>
+      <c r="AG251" s="4" t="n"/>
+      <c r="AH251" s="4" t="n"/>
+      <c r="AI251" s="4" t="n"/>
+      <c r="AJ251" s="4" t="n"/>
+      <c r="AK251" s="4" t="n"/>
+      <c r="AL251" s="4" t="n"/>
+      <c r="AM251" s="4" t="n"/>
+      <c r="AN251" s="4" t="n"/>
+      <c r="AO251" s="4" t="n"/>
     </row>
     <row r="252">
       <c r="A252" s="3" t="n"/>
@@ -9207,6 +11515,15 @@
       <c r="AD252" s="3" t="n"/>
       <c r="AE252" s="3" t="n"/>
       <c r="AF252" s="3" t="n"/>
+      <c r="AG252" s="3" t="n"/>
+      <c r="AH252" s="3" t="n"/>
+      <c r="AI252" s="3" t="n"/>
+      <c r="AJ252" s="3" t="n"/>
+      <c r="AK252" s="3" t="n"/>
+      <c r="AL252" s="3" t="n"/>
+      <c r="AM252" s="3" t="n"/>
+      <c r="AN252" s="3" t="n"/>
+      <c r="AO252" s="3" t="n"/>
     </row>
     <row r="253">
       <c r="A253" s="4" t="n"/>
@@ -9241,6 +11558,15 @@
       <c r="AD253" s="4" t="n"/>
       <c r="AE253" s="4" t="n"/>
       <c r="AF253" s="4" t="n"/>
+      <c r="AG253" s="4" t="n"/>
+      <c r="AH253" s="4" t="n"/>
+      <c r="AI253" s="4" t="n"/>
+      <c r="AJ253" s="4" t="n"/>
+      <c r="AK253" s="4" t="n"/>
+      <c r="AL253" s="4" t="n"/>
+      <c r="AM253" s="4" t="n"/>
+      <c r="AN253" s="4" t="n"/>
+      <c r="AO253" s="4" t="n"/>
     </row>
     <row r="254">
       <c r="A254" s="3" t="n"/>
@@ -9275,6 +11601,15 @@
       <c r="AD254" s="3" t="n"/>
       <c r="AE254" s="3" t="n"/>
       <c r="AF254" s="3" t="n"/>
+      <c r="AG254" s="3" t="n"/>
+      <c r="AH254" s="3" t="n"/>
+      <c r="AI254" s="3" t="n"/>
+      <c r="AJ254" s="3" t="n"/>
+      <c r="AK254" s="3" t="n"/>
+      <c r="AL254" s="3" t="n"/>
+      <c r="AM254" s="3" t="n"/>
+      <c r="AN254" s="3" t="n"/>
+      <c r="AO254" s="3" t="n"/>
     </row>
     <row r="255">
       <c r="A255" s="4" t="n"/>
@@ -9309,6 +11644,15 @@
       <c r="AD255" s="4" t="n"/>
       <c r="AE255" s="4" t="n"/>
       <c r="AF255" s="4" t="n"/>
+      <c r="AG255" s="4" t="n"/>
+      <c r="AH255" s="4" t="n"/>
+      <c r="AI255" s="4" t="n"/>
+      <c r="AJ255" s="4" t="n"/>
+      <c r="AK255" s="4" t="n"/>
+      <c r="AL255" s="4" t="n"/>
+      <c r="AM255" s="4" t="n"/>
+      <c r="AN255" s="4" t="n"/>
+      <c r="AO255" s="4" t="n"/>
     </row>
     <row r="256">
       <c r="A256" s="3" t="n"/>
@@ -9343,6 +11687,15 @@
       <c r="AD256" s="3" t="n"/>
       <c r="AE256" s="3" t="n"/>
       <c r="AF256" s="3" t="n"/>
+      <c r="AG256" s="3" t="n"/>
+      <c r="AH256" s="3" t="n"/>
+      <c r="AI256" s="3" t="n"/>
+      <c r="AJ256" s="3" t="n"/>
+      <c r="AK256" s="3" t="n"/>
+      <c r="AL256" s="3" t="n"/>
+      <c r="AM256" s="3" t="n"/>
+      <c r="AN256" s="3" t="n"/>
+      <c r="AO256" s="3" t="n"/>
     </row>
     <row r="257">
       <c r="A257" s="4" t="n"/>
@@ -9377,6 +11730,15 @@
       <c r="AD257" s="4" t="n"/>
       <c r="AE257" s="4" t="n"/>
       <c r="AF257" s="4" t="n"/>
+      <c r="AG257" s="4" t="n"/>
+      <c r="AH257" s="4" t="n"/>
+      <c r="AI257" s="4" t="n"/>
+      <c r="AJ257" s="4" t="n"/>
+      <c r="AK257" s="4" t="n"/>
+      <c r="AL257" s="4" t="n"/>
+      <c r="AM257" s="4" t="n"/>
+      <c r="AN257" s="4" t="n"/>
+      <c r="AO257" s="4" t="n"/>
     </row>
     <row r="258">
       <c r="A258" s="3" t="n"/>
@@ -9411,6 +11773,15 @@
       <c r="AD258" s="3" t="n"/>
       <c r="AE258" s="3" t="n"/>
       <c r="AF258" s="3" t="n"/>
+      <c r="AG258" s="3" t="n"/>
+      <c r="AH258" s="3" t="n"/>
+      <c r="AI258" s="3" t="n"/>
+      <c r="AJ258" s="3" t="n"/>
+      <c r="AK258" s="3" t="n"/>
+      <c r="AL258" s="3" t="n"/>
+      <c r="AM258" s="3" t="n"/>
+      <c r="AN258" s="3" t="n"/>
+      <c r="AO258" s="3" t="n"/>
     </row>
     <row r="259">
       <c r="A259" s="4" t="n"/>
@@ -9445,6 +11816,15 @@
       <c r="AD259" s="4" t="n"/>
       <c r="AE259" s="4" t="n"/>
       <c r="AF259" s="4" t="n"/>
+      <c r="AG259" s="4" t="n"/>
+      <c r="AH259" s="4" t="n"/>
+      <c r="AI259" s="4" t="n"/>
+      <c r="AJ259" s="4" t="n"/>
+      <c r="AK259" s="4" t="n"/>
+      <c r="AL259" s="4" t="n"/>
+      <c r="AM259" s="4" t="n"/>
+      <c r="AN259" s="4" t="n"/>
+      <c r="AO259" s="4" t="n"/>
     </row>
     <row r="260">
       <c r="A260" s="3" t="n"/>
@@ -9479,6 +11859,15 @@
       <c r="AD260" s="3" t="n"/>
       <c r="AE260" s="3" t="n"/>
       <c r="AF260" s="3" t="n"/>
+      <c r="AG260" s="3" t="n"/>
+      <c r="AH260" s="3" t="n"/>
+      <c r="AI260" s="3" t="n"/>
+      <c r="AJ260" s="3" t="n"/>
+      <c r="AK260" s="3" t="n"/>
+      <c r="AL260" s="3" t="n"/>
+      <c r="AM260" s="3" t="n"/>
+      <c r="AN260" s="3" t="n"/>
+      <c r="AO260" s="3" t="n"/>
     </row>
     <row r="261">
       <c r="A261" s="4" t="n"/>
@@ -9513,6 +11902,15 @@
       <c r="AD261" s="4" t="n"/>
       <c r="AE261" s="4" t="n"/>
       <c r="AF261" s="4" t="n"/>
+      <c r="AG261" s="4" t="n"/>
+      <c r="AH261" s="4" t="n"/>
+      <c r="AI261" s="4" t="n"/>
+      <c r="AJ261" s="4" t="n"/>
+      <c r="AK261" s="4" t="n"/>
+      <c r="AL261" s="4" t="n"/>
+      <c r="AM261" s="4" t="n"/>
+      <c r="AN261" s="4" t="n"/>
+      <c r="AO261" s="4" t="n"/>
     </row>
     <row r="262">
       <c r="A262" s="3" t="n"/>
@@ -9547,6 +11945,15 @@
       <c r="AD262" s="3" t="n"/>
       <c r="AE262" s="3" t="n"/>
       <c r="AF262" s="3" t="n"/>
+      <c r="AG262" s="3" t="n"/>
+      <c r="AH262" s="3" t="n"/>
+      <c r="AI262" s="3" t="n"/>
+      <c r="AJ262" s="3" t="n"/>
+      <c r="AK262" s="3" t="n"/>
+      <c r="AL262" s="3" t="n"/>
+      <c r="AM262" s="3" t="n"/>
+      <c r="AN262" s="3" t="n"/>
+      <c r="AO262" s="3" t="n"/>
     </row>
     <row r="263">
       <c r="A263" s="4" t="n"/>
@@ -9581,6 +11988,15 @@
       <c r="AD263" s="4" t="n"/>
       <c r="AE263" s="4" t="n"/>
       <c r="AF263" s="4" t="n"/>
+      <c r="AG263" s="4" t="n"/>
+      <c r="AH263" s="4" t="n"/>
+      <c r="AI263" s="4" t="n"/>
+      <c r="AJ263" s="4" t="n"/>
+      <c r="AK263" s="4" t="n"/>
+      <c r="AL263" s="4" t="n"/>
+      <c r="AM263" s="4" t="n"/>
+      <c r="AN263" s="4" t="n"/>
+      <c r="AO263" s="4" t="n"/>
     </row>
     <row r="264">
       <c r="A264" s="3" t="n"/>
@@ -9615,6 +12031,15 @@
       <c r="AD264" s="3" t="n"/>
       <c r="AE264" s="3" t="n"/>
       <c r="AF264" s="3" t="n"/>
+      <c r="AG264" s="3" t="n"/>
+      <c r="AH264" s="3" t="n"/>
+      <c r="AI264" s="3" t="n"/>
+      <c r="AJ264" s="3" t="n"/>
+      <c r="AK264" s="3" t="n"/>
+      <c r="AL264" s="3" t="n"/>
+      <c r="AM264" s="3" t="n"/>
+      <c r="AN264" s="3" t="n"/>
+      <c r="AO264" s="3" t="n"/>
     </row>
     <row r="265">
       <c r="A265" s="4" t="n"/>
@@ -9649,6 +12074,15 @@
       <c r="AD265" s="4" t="n"/>
       <c r="AE265" s="4" t="n"/>
       <c r="AF265" s="4" t="n"/>
+      <c r="AG265" s="4" t="n"/>
+      <c r="AH265" s="4" t="n"/>
+      <c r="AI265" s="4" t="n"/>
+      <c r="AJ265" s="4" t="n"/>
+      <c r="AK265" s="4" t="n"/>
+      <c r="AL265" s="4" t="n"/>
+      <c r="AM265" s="4" t="n"/>
+      <c r="AN265" s="4" t="n"/>
+      <c r="AO265" s="4" t="n"/>
     </row>
     <row r="266">
       <c r="A266" s="3" t="n"/>
@@ -9683,6 +12117,15 @@
       <c r="AD266" s="3" t="n"/>
       <c r="AE266" s="3" t="n"/>
       <c r="AF266" s="3" t="n"/>
+      <c r="AG266" s="3" t="n"/>
+      <c r="AH266" s="3" t="n"/>
+      <c r="AI266" s="3" t="n"/>
+      <c r="AJ266" s="3" t="n"/>
+      <c r="AK266" s="3" t="n"/>
+      <c r="AL266" s="3" t="n"/>
+      <c r="AM266" s="3" t="n"/>
+      <c r="AN266" s="3" t="n"/>
+      <c r="AO266" s="3" t="n"/>
     </row>
     <row r="267">
       <c r="A267" s="4" t="n"/>
@@ -9717,6 +12160,15 @@
       <c r="AD267" s="4" t="n"/>
       <c r="AE267" s="4" t="n"/>
       <c r="AF267" s="4" t="n"/>
+      <c r="AG267" s="4" t="n"/>
+      <c r="AH267" s="4" t="n"/>
+      <c r="AI267" s="4" t="n"/>
+      <c r="AJ267" s="4" t="n"/>
+      <c r="AK267" s="4" t="n"/>
+      <c r="AL267" s="4" t="n"/>
+      <c r="AM267" s="4" t="n"/>
+      <c r="AN267" s="4" t="n"/>
+      <c r="AO267" s="4" t="n"/>
     </row>
     <row r="268">
       <c r="A268" s="3" t="n"/>
@@ -9751,6 +12203,15 @@
       <c r="AD268" s="3" t="n"/>
       <c r="AE268" s="3" t="n"/>
       <c r="AF268" s="3" t="n"/>
+      <c r="AG268" s="3" t="n"/>
+      <c r="AH268" s="3" t="n"/>
+      <c r="AI268" s="3" t="n"/>
+      <c r="AJ268" s="3" t="n"/>
+      <c r="AK268" s="3" t="n"/>
+      <c r="AL268" s="3" t="n"/>
+      <c r="AM268" s="3" t="n"/>
+      <c r="AN268" s="3" t="n"/>
+      <c r="AO268" s="3" t="n"/>
     </row>
     <row r="269">
       <c r="A269" s="4" t="n"/>
@@ -9785,6 +12246,15 @@
       <c r="AD269" s="4" t="n"/>
       <c r="AE269" s="4" t="n"/>
       <c r="AF269" s="4" t="n"/>
+      <c r="AG269" s="4" t="n"/>
+      <c r="AH269" s="4" t="n"/>
+      <c r="AI269" s="4" t="n"/>
+      <c r="AJ269" s="4" t="n"/>
+      <c r="AK269" s="4" t="n"/>
+      <c r="AL269" s="4" t="n"/>
+      <c r="AM269" s="4" t="n"/>
+      <c r="AN269" s="4" t="n"/>
+      <c r="AO269" s="4" t="n"/>
     </row>
     <row r="270">
       <c r="A270" s="3" t="n"/>
@@ -9819,6 +12289,15 @@
       <c r="AD270" s="3" t="n"/>
       <c r="AE270" s="3" t="n"/>
       <c r="AF270" s="3" t="n"/>
+      <c r="AG270" s="3" t="n"/>
+      <c r="AH270" s="3" t="n"/>
+      <c r="AI270" s="3" t="n"/>
+      <c r="AJ270" s="3" t="n"/>
+      <c r="AK270" s="3" t="n"/>
+      <c r="AL270" s="3" t="n"/>
+      <c r="AM270" s="3" t="n"/>
+      <c r="AN270" s="3" t="n"/>
+      <c r="AO270" s="3" t="n"/>
     </row>
     <row r="271">
       <c r="A271" s="4" t="n"/>
@@ -9853,6 +12332,15 @@
       <c r="AD271" s="4" t="n"/>
       <c r="AE271" s="4" t="n"/>
       <c r="AF271" s="4" t="n"/>
+      <c r="AG271" s="4" t="n"/>
+      <c r="AH271" s="4" t="n"/>
+      <c r="AI271" s="4" t="n"/>
+      <c r="AJ271" s="4" t="n"/>
+      <c r="AK271" s="4" t="n"/>
+      <c r="AL271" s="4" t="n"/>
+      <c r="AM271" s="4" t="n"/>
+      <c r="AN271" s="4" t="n"/>
+      <c r="AO271" s="4" t="n"/>
     </row>
     <row r="272">
       <c r="A272" s="3" t="n"/>
@@ -9887,6 +12375,15 @@
       <c r="AD272" s="3" t="n"/>
       <c r="AE272" s="3" t="n"/>
       <c r="AF272" s="3" t="n"/>
+      <c r="AG272" s="3" t="n"/>
+      <c r="AH272" s="3" t="n"/>
+      <c r="AI272" s="3" t="n"/>
+      <c r="AJ272" s="3" t="n"/>
+      <c r="AK272" s="3" t="n"/>
+      <c r="AL272" s="3" t="n"/>
+      <c r="AM272" s="3" t="n"/>
+      <c r="AN272" s="3" t="n"/>
+      <c r="AO272" s="3" t="n"/>
     </row>
     <row r="273">
       <c r="A273" s="4" t="n"/>
@@ -9921,6 +12418,15 @@
       <c r="AD273" s="4" t="n"/>
       <c r="AE273" s="4" t="n"/>
       <c r="AF273" s="4" t="n"/>
+      <c r="AG273" s="4" t="n"/>
+      <c r="AH273" s="4" t="n"/>
+      <c r="AI273" s="4" t="n"/>
+      <c r="AJ273" s="4" t="n"/>
+      <c r="AK273" s="4" t="n"/>
+      <c r="AL273" s="4" t="n"/>
+      <c r="AM273" s="4" t="n"/>
+      <c r="AN273" s="4" t="n"/>
+      <c r="AO273" s="4" t="n"/>
     </row>
     <row r="274">
       <c r="A274" s="3" t="n"/>
@@ -9955,6 +12461,15 @@
       <c r="AD274" s="3" t="n"/>
       <c r="AE274" s="3" t="n"/>
       <c r="AF274" s="3" t="n"/>
+      <c r="AG274" s="3" t="n"/>
+      <c r="AH274" s="3" t="n"/>
+      <c r="AI274" s="3" t="n"/>
+      <c r="AJ274" s="3" t="n"/>
+      <c r="AK274" s="3" t="n"/>
+      <c r="AL274" s="3" t="n"/>
+      <c r="AM274" s="3" t="n"/>
+      <c r="AN274" s="3" t="n"/>
+      <c r="AO274" s="3" t="n"/>
     </row>
     <row r="275">
       <c r="A275" s="4" t="n"/>
@@ -9989,6 +12504,15 @@
       <c r="AD275" s="4" t="n"/>
       <c r="AE275" s="4" t="n"/>
       <c r="AF275" s="4" t="n"/>
+      <c r="AG275" s="4" t="n"/>
+      <c r="AH275" s="4" t="n"/>
+      <c r="AI275" s="4" t="n"/>
+      <c r="AJ275" s="4" t="n"/>
+      <c r="AK275" s="4" t="n"/>
+      <c r="AL275" s="4" t="n"/>
+      <c r="AM275" s="4" t="n"/>
+      <c r="AN275" s="4" t="n"/>
+      <c r="AO275" s="4" t="n"/>
     </row>
     <row r="276">
       <c r="A276" s="3" t="n"/>
@@ -10023,6 +12547,15 @@
       <c r="AD276" s="3" t="n"/>
       <c r="AE276" s="3" t="n"/>
       <c r="AF276" s="3" t="n"/>
+      <c r="AG276" s="3" t="n"/>
+      <c r="AH276" s="3" t="n"/>
+      <c r="AI276" s="3" t="n"/>
+      <c r="AJ276" s="3" t="n"/>
+      <c r="AK276" s="3" t="n"/>
+      <c r="AL276" s="3" t="n"/>
+      <c r="AM276" s="3" t="n"/>
+      <c r="AN276" s="3" t="n"/>
+      <c r="AO276" s="3" t="n"/>
     </row>
     <row r="277">
       <c r="A277" s="4" t="n"/>
@@ -10057,6 +12590,15 @@
       <c r="AD277" s="4" t="n"/>
       <c r="AE277" s="4" t="n"/>
       <c r="AF277" s="4" t="n"/>
+      <c r="AG277" s="4" t="n"/>
+      <c r="AH277" s="4" t="n"/>
+      <c r="AI277" s="4" t="n"/>
+      <c r="AJ277" s="4" t="n"/>
+      <c r="AK277" s="4" t="n"/>
+      <c r="AL277" s="4" t="n"/>
+      <c r="AM277" s="4" t="n"/>
+      <c r="AN277" s="4" t="n"/>
+      <c r="AO277" s="4" t="n"/>
     </row>
     <row r="278">
       <c r="A278" s="3" t="n"/>
@@ -10091,6 +12633,15 @@
       <c r="AD278" s="3" t="n"/>
       <c r="AE278" s="3" t="n"/>
       <c r="AF278" s="3" t="n"/>
+      <c r="AG278" s="3" t="n"/>
+      <c r="AH278" s="3" t="n"/>
+      <c r="AI278" s="3" t="n"/>
+      <c r="AJ278" s="3" t="n"/>
+      <c r="AK278" s="3" t="n"/>
+      <c r="AL278" s="3" t="n"/>
+      <c r="AM278" s="3" t="n"/>
+      <c r="AN278" s="3" t="n"/>
+      <c r="AO278" s="3" t="n"/>
     </row>
     <row r="279">
       <c r="A279" s="4" t="n"/>
@@ -10125,6 +12676,15 @@
       <c r="AD279" s="4" t="n"/>
       <c r="AE279" s="4" t="n"/>
       <c r="AF279" s="4" t="n"/>
+      <c r="AG279" s="4" t="n"/>
+      <c r="AH279" s="4" t="n"/>
+      <c r="AI279" s="4" t="n"/>
+      <c r="AJ279" s="4" t="n"/>
+      <c r="AK279" s="4" t="n"/>
+      <c r="AL279" s="4" t="n"/>
+      <c r="AM279" s="4" t="n"/>
+      <c r="AN279" s="4" t="n"/>
+      <c r="AO279" s="4" t="n"/>
     </row>
     <row r="280">
       <c r="A280" s="3" t="n"/>
@@ -10159,6 +12719,15 @@
       <c r="AD280" s="3" t="n"/>
       <c r="AE280" s="3" t="n"/>
       <c r="AF280" s="3" t="n"/>
+      <c r="AG280" s="3" t="n"/>
+      <c r="AH280" s="3" t="n"/>
+      <c r="AI280" s="3" t="n"/>
+      <c r="AJ280" s="3" t="n"/>
+      <c r="AK280" s="3" t="n"/>
+      <c r="AL280" s="3" t="n"/>
+      <c r="AM280" s="3" t="n"/>
+      <c r="AN280" s="3" t="n"/>
+      <c r="AO280" s="3" t="n"/>
     </row>
     <row r="281">
       <c r="A281" s="4" t="n"/>
@@ -10193,6 +12762,15 @@
       <c r="AD281" s="4" t="n"/>
       <c r="AE281" s="4" t="n"/>
       <c r="AF281" s="4" t="n"/>
+      <c r="AG281" s="4" t="n"/>
+      <c r="AH281" s="4" t="n"/>
+      <c r="AI281" s="4" t="n"/>
+      <c r="AJ281" s="4" t="n"/>
+      <c r="AK281" s="4" t="n"/>
+      <c r="AL281" s="4" t="n"/>
+      <c r="AM281" s="4" t="n"/>
+      <c r="AN281" s="4" t="n"/>
+      <c r="AO281" s="4" t="n"/>
     </row>
     <row r="282">
       <c r="A282" s="3" t="n"/>
@@ -10227,6 +12805,15 @@
       <c r="AD282" s="3" t="n"/>
       <c r="AE282" s="3" t="n"/>
       <c r="AF282" s="3" t="n"/>
+      <c r="AG282" s="3" t="n"/>
+      <c r="AH282" s="3" t="n"/>
+      <c r="AI282" s="3" t="n"/>
+      <c r="AJ282" s="3" t="n"/>
+      <c r="AK282" s="3" t="n"/>
+      <c r="AL282" s="3" t="n"/>
+      <c r="AM282" s="3" t="n"/>
+      <c r="AN282" s="3" t="n"/>
+      <c r="AO282" s="3" t="n"/>
     </row>
     <row r="283">
       <c r="A283" s="4" t="n"/>
@@ -10261,6 +12848,15 @@
       <c r="AD283" s="4" t="n"/>
       <c r="AE283" s="4" t="n"/>
       <c r="AF283" s="4" t="n"/>
+      <c r="AG283" s="4" t="n"/>
+      <c r="AH283" s="4" t="n"/>
+      <c r="AI283" s="4" t="n"/>
+      <c r="AJ283" s="4" t="n"/>
+      <c r="AK283" s="4" t="n"/>
+      <c r="AL283" s="4" t="n"/>
+      <c r="AM283" s="4" t="n"/>
+      <c r="AN283" s="4" t="n"/>
+      <c r="AO283" s="4" t="n"/>
     </row>
     <row r="284">
       <c r="A284" s="3" t="n"/>
@@ -10295,6 +12891,15 @@
       <c r="AD284" s="3" t="n"/>
       <c r="AE284" s="3" t="n"/>
       <c r="AF284" s="3" t="n"/>
+      <c r="AG284" s="3" t="n"/>
+      <c r="AH284" s="3" t="n"/>
+      <c r="AI284" s="3" t="n"/>
+      <c r="AJ284" s="3" t="n"/>
+      <c r="AK284" s="3" t="n"/>
+      <c r="AL284" s="3" t="n"/>
+      <c r="AM284" s="3" t="n"/>
+      <c r="AN284" s="3" t="n"/>
+      <c r="AO284" s="3" t="n"/>
     </row>
     <row r="285">
       <c r="A285" s="4" t="n"/>
@@ -10329,6 +12934,15 @@
       <c r="AD285" s="4" t="n"/>
       <c r="AE285" s="4" t="n"/>
       <c r="AF285" s="4" t="n"/>
+      <c r="AG285" s="4" t="n"/>
+      <c r="AH285" s="4" t="n"/>
+      <c r="AI285" s="4" t="n"/>
+      <c r="AJ285" s="4" t="n"/>
+      <c r="AK285" s="4" t="n"/>
+      <c r="AL285" s="4" t="n"/>
+      <c r="AM285" s="4" t="n"/>
+      <c r="AN285" s="4" t="n"/>
+      <c r="AO285" s="4" t="n"/>
     </row>
     <row r="286">
       <c r="A286" s="3" t="n"/>
@@ -10363,6 +12977,15 @@
       <c r="AD286" s="3" t="n"/>
       <c r="AE286" s="3" t="n"/>
       <c r="AF286" s="3" t="n"/>
+      <c r="AG286" s="3" t="n"/>
+      <c r="AH286" s="3" t="n"/>
+      <c r="AI286" s="3" t="n"/>
+      <c r="AJ286" s="3" t="n"/>
+      <c r="AK286" s="3" t="n"/>
+      <c r="AL286" s="3" t="n"/>
+      <c r="AM286" s="3" t="n"/>
+      <c r="AN286" s="3" t="n"/>
+      <c r="AO286" s="3" t="n"/>
     </row>
     <row r="287">
       <c r="A287" s="4" t="n"/>
@@ -10397,6 +13020,15 @@
       <c r="AD287" s="4" t="n"/>
       <c r="AE287" s="4" t="n"/>
       <c r="AF287" s="4" t="n"/>
+      <c r="AG287" s="4" t="n"/>
+      <c r="AH287" s="4" t="n"/>
+      <c r="AI287" s="4" t="n"/>
+      <c r="AJ287" s="4" t="n"/>
+      <c r="AK287" s="4" t="n"/>
+      <c r="AL287" s="4" t="n"/>
+      <c r="AM287" s="4" t="n"/>
+      <c r="AN287" s="4" t="n"/>
+      <c r="AO287" s="4" t="n"/>
     </row>
     <row r="288">
       <c r="A288" s="3" t="n"/>
@@ -10431,6 +13063,15 @@
       <c r="AD288" s="3" t="n"/>
       <c r="AE288" s="3" t="n"/>
       <c r="AF288" s="3" t="n"/>
+      <c r="AG288" s="3" t="n"/>
+      <c r="AH288" s="3" t="n"/>
+      <c r="AI288" s="3" t="n"/>
+      <c r="AJ288" s="3" t="n"/>
+      <c r="AK288" s="3" t="n"/>
+      <c r="AL288" s="3" t="n"/>
+      <c r="AM288" s="3" t="n"/>
+      <c r="AN288" s="3" t="n"/>
+      <c r="AO288" s="3" t="n"/>
     </row>
     <row r="289">
       <c r="A289" s="4" t="n"/>
@@ -10465,6 +13106,15 @@
       <c r="AD289" s="4" t="n"/>
       <c r="AE289" s="4" t="n"/>
       <c r="AF289" s="4" t="n"/>
+      <c r="AG289" s="4" t="n"/>
+      <c r="AH289" s="4" t="n"/>
+      <c r="AI289" s="4" t="n"/>
+      <c r="AJ289" s="4" t="n"/>
+      <c r="AK289" s="4" t="n"/>
+      <c r="AL289" s="4" t="n"/>
+      <c r="AM289" s="4" t="n"/>
+      <c r="AN289" s="4" t="n"/>
+      <c r="AO289" s="4" t="n"/>
     </row>
     <row r="290">
       <c r="A290" s="3" t="n"/>
@@ -10499,6 +13149,15 @@
       <c r="AD290" s="3" t="n"/>
       <c r="AE290" s="3" t="n"/>
       <c r="AF290" s="3" t="n"/>
+      <c r="AG290" s="3" t="n"/>
+      <c r="AH290" s="3" t="n"/>
+      <c r="AI290" s="3" t="n"/>
+      <c r="AJ290" s="3" t="n"/>
+      <c r="AK290" s="3" t="n"/>
+      <c r="AL290" s="3" t="n"/>
+      <c r="AM290" s="3" t="n"/>
+      <c r="AN290" s="3" t="n"/>
+      <c r="AO290" s="3" t="n"/>
     </row>
     <row r="291">
       <c r="A291" s="4" t="n"/>
@@ -10533,6 +13192,15 @@
       <c r="AD291" s="4" t="n"/>
       <c r="AE291" s="4" t="n"/>
       <c r="AF291" s="4" t="n"/>
+      <c r="AG291" s="4" t="n"/>
+      <c r="AH291" s="4" t="n"/>
+      <c r="AI291" s="4" t="n"/>
+      <c r="AJ291" s="4" t="n"/>
+      <c r="AK291" s="4" t="n"/>
+      <c r="AL291" s="4" t="n"/>
+      <c r="AM291" s="4" t="n"/>
+      <c r="AN291" s="4" t="n"/>
+      <c r="AO291" s="4" t="n"/>
     </row>
     <row r="292">
       <c r="A292" s="3" t="n"/>
@@ -10567,6 +13235,15 @@
       <c r="AD292" s="3" t="n"/>
       <c r="AE292" s="3" t="n"/>
       <c r="AF292" s="3" t="n"/>
+      <c r="AG292" s="3" t="n"/>
+      <c r="AH292" s="3" t="n"/>
+      <c r="AI292" s="3" t="n"/>
+      <c r="AJ292" s="3" t="n"/>
+      <c r="AK292" s="3" t="n"/>
+      <c r="AL292" s="3" t="n"/>
+      <c r="AM292" s="3" t="n"/>
+      <c r="AN292" s="3" t="n"/>
+      <c r="AO292" s="3" t="n"/>
     </row>
     <row r="293">
       <c r="A293" s="4" t="n"/>
@@ -10601,6 +13278,15 @@
       <c r="AD293" s="4" t="n"/>
       <c r="AE293" s="4" t="n"/>
       <c r="AF293" s="4" t="n"/>
+      <c r="AG293" s="4" t="n"/>
+      <c r="AH293" s="4" t="n"/>
+      <c r="AI293" s="4" t="n"/>
+      <c r="AJ293" s="4" t="n"/>
+      <c r="AK293" s="4" t="n"/>
+      <c r="AL293" s="4" t="n"/>
+      <c r="AM293" s="4" t="n"/>
+      <c r="AN293" s="4" t="n"/>
+      <c r="AO293" s="4" t="n"/>
     </row>
     <row r="294">
       <c r="A294" s="3" t="n"/>
@@ -10635,6 +13321,15 @@
       <c r="AD294" s="3" t="n"/>
       <c r="AE294" s="3" t="n"/>
       <c r="AF294" s="3" t="n"/>
+      <c r="AG294" s="3" t="n"/>
+      <c r="AH294" s="3" t="n"/>
+      <c r="AI294" s="3" t="n"/>
+      <c r="AJ294" s="3" t="n"/>
+      <c r="AK294" s="3" t="n"/>
+      <c r="AL294" s="3" t="n"/>
+      <c r="AM294" s="3" t="n"/>
+      <c r="AN294" s="3" t="n"/>
+      <c r="AO294" s="3" t="n"/>
     </row>
     <row r="295">
       <c r="A295" s="4" t="n"/>
@@ -10669,6 +13364,15 @@
       <c r="AD295" s="4" t="n"/>
       <c r="AE295" s="4" t="n"/>
       <c r="AF295" s="4" t="n"/>
+      <c r="AG295" s="4" t="n"/>
+      <c r="AH295" s="4" t="n"/>
+      <c r="AI295" s="4" t="n"/>
+      <c r="AJ295" s="4" t="n"/>
+      <c r="AK295" s="4" t="n"/>
+      <c r="AL295" s="4" t="n"/>
+      <c r="AM295" s="4" t="n"/>
+      <c r="AN295" s="4" t="n"/>
+      <c r="AO295" s="4" t="n"/>
     </row>
     <row r="296">
       <c r="A296" s="3" t="n"/>
@@ -10703,6 +13407,15 @@
       <c r="AD296" s="3" t="n"/>
       <c r="AE296" s="3" t="n"/>
       <c r="AF296" s="3" t="n"/>
+      <c r="AG296" s="3" t="n"/>
+      <c r="AH296" s="3" t="n"/>
+      <c r="AI296" s="3" t="n"/>
+      <c r="AJ296" s="3" t="n"/>
+      <c r="AK296" s="3" t="n"/>
+      <c r="AL296" s="3" t="n"/>
+      <c r="AM296" s="3" t="n"/>
+      <c r="AN296" s="3" t="n"/>
+      <c r="AO296" s="3" t="n"/>
     </row>
     <row r="297">
       <c r="A297" s="4" t="n"/>
@@ -10737,6 +13450,15 @@
       <c r="AD297" s="4" t="n"/>
       <c r="AE297" s="4" t="n"/>
       <c r="AF297" s="4" t="n"/>
+      <c r="AG297" s="4" t="n"/>
+      <c r="AH297" s="4" t="n"/>
+      <c r="AI297" s="4" t="n"/>
+      <c r="AJ297" s="4" t="n"/>
+      <c r="AK297" s="4" t="n"/>
+      <c r="AL297" s="4" t="n"/>
+      <c r="AM297" s="4" t="n"/>
+      <c r="AN297" s="4" t="n"/>
+      <c r="AO297" s="4" t="n"/>
     </row>
     <row r="298">
       <c r="A298" s="3" t="n"/>
@@ -10771,6 +13493,15 @@
       <c r="AD298" s="3" t="n"/>
       <c r="AE298" s="3" t="n"/>
       <c r="AF298" s="3" t="n"/>
+      <c r="AG298" s="3" t="n"/>
+      <c r="AH298" s="3" t="n"/>
+      <c r="AI298" s="3" t="n"/>
+      <c r="AJ298" s="3" t="n"/>
+      <c r="AK298" s="3" t="n"/>
+      <c r="AL298" s="3" t="n"/>
+      <c r="AM298" s="3" t="n"/>
+      <c r="AN298" s="3" t="n"/>
+      <c r="AO298" s="3" t="n"/>
     </row>
     <row r="299">
       <c r="A299" s="4" t="n"/>
@@ -10805,6 +13536,15 @@
       <c r="AD299" s="4" t="n"/>
       <c r="AE299" s="4" t="n"/>
       <c r="AF299" s="4" t="n"/>
+      <c r="AG299" s="4" t="n"/>
+      <c r="AH299" s="4" t="n"/>
+      <c r="AI299" s="4" t="n"/>
+      <c r="AJ299" s="4" t="n"/>
+      <c r="AK299" s="4" t="n"/>
+      <c r="AL299" s="4" t="n"/>
+      <c r="AM299" s="4" t="n"/>
+      <c r="AN299" s="4" t="n"/>
+      <c r="AO299" s="4" t="n"/>
     </row>
     <row r="300">
       <c r="A300" s="3" t="n"/>
@@ -10839,6 +13579,15 @@
       <c r="AD300" s="3" t="n"/>
       <c r="AE300" s="3" t="n"/>
       <c r="AF300" s="3" t="n"/>
+      <c r="AG300" s="3" t="n"/>
+      <c r="AH300" s="3" t="n"/>
+      <c r="AI300" s="3" t="n"/>
+      <c r="AJ300" s="3" t="n"/>
+      <c r="AK300" s="3" t="n"/>
+      <c r="AL300" s="3" t="n"/>
+      <c r="AM300" s="3" t="n"/>
+      <c r="AN300" s="3" t="n"/>
+      <c r="AO300" s="3" t="n"/>
     </row>
     <row r="301">
       <c r="A301" s="4" t="n"/>
@@ -10873,6 +13622,15 @@
       <c r="AD301" s="4" t="n"/>
       <c r="AE301" s="4" t="n"/>
       <c r="AF301" s="4" t="n"/>
+      <c r="AG301" s="4" t="n"/>
+      <c r="AH301" s="4" t="n"/>
+      <c r="AI301" s="4" t="n"/>
+      <c r="AJ301" s="4" t="n"/>
+      <c r="AK301" s="4" t="n"/>
+      <c r="AL301" s="4" t="n"/>
+      <c r="AM301" s="4" t="n"/>
+      <c r="AN301" s="4" t="n"/>
+      <c r="AO301" s="4" t="n"/>
     </row>
     <row r="302">
       <c r="A302" s="3" t="n"/>
@@ -10907,6 +13665,15 @@
       <c r="AD302" s="3" t="n"/>
       <c r="AE302" s="3" t="n"/>
       <c r="AF302" s="3" t="n"/>
+      <c r="AG302" s="3" t="n"/>
+      <c r="AH302" s="3" t="n"/>
+      <c r="AI302" s="3" t="n"/>
+      <c r="AJ302" s="3" t="n"/>
+      <c r="AK302" s="3" t="n"/>
+      <c r="AL302" s="3" t="n"/>
+      <c r="AM302" s="3" t="n"/>
+      <c r="AN302" s="3" t="n"/>
+      <c r="AO302" s="3" t="n"/>
     </row>
     <row r="303">
       <c r="A303" s="4" t="n"/>
@@ -10941,6 +13708,15 @@
       <c r="AD303" s="4" t="n"/>
       <c r="AE303" s="4" t="n"/>
       <c r="AF303" s="4" t="n"/>
+      <c r="AG303" s="4" t="n"/>
+      <c r="AH303" s="4" t="n"/>
+      <c r="AI303" s="4" t="n"/>
+      <c r="AJ303" s="4" t="n"/>
+      <c r="AK303" s="4" t="n"/>
+      <c r="AL303" s="4" t="n"/>
+      <c r="AM303" s="4" t="n"/>
+      <c r="AN303" s="4" t="n"/>
+      <c r="AO303" s="4" t="n"/>
     </row>
     <row r="304">
       <c r="A304" s="3" t="n"/>
@@ -10975,6 +13751,15 @@
       <c r="AD304" s="3" t="n"/>
       <c r="AE304" s="3" t="n"/>
       <c r="AF304" s="3" t="n"/>
+      <c r="AG304" s="3" t="n"/>
+      <c r="AH304" s="3" t="n"/>
+      <c r="AI304" s="3" t="n"/>
+      <c r="AJ304" s="3" t="n"/>
+      <c r="AK304" s="3" t="n"/>
+      <c r="AL304" s="3" t="n"/>
+      <c r="AM304" s="3" t="n"/>
+      <c r="AN304" s="3" t="n"/>
+      <c r="AO304" s="3" t="n"/>
     </row>
     <row r="305">
       <c r="A305" s="4" t="n"/>
@@ -11009,6 +13794,15 @@
       <c r="AD305" s="4" t="n"/>
       <c r="AE305" s="4" t="n"/>
       <c r="AF305" s="4" t="n"/>
+      <c r="AG305" s="4" t="n"/>
+      <c r="AH305" s="4" t="n"/>
+      <c r="AI305" s="4" t="n"/>
+      <c r="AJ305" s="4" t="n"/>
+      <c r="AK305" s="4" t="n"/>
+      <c r="AL305" s="4" t="n"/>
+      <c r="AM305" s="4" t="n"/>
+      <c r="AN305" s="4" t="n"/>
+      <c r="AO305" s="4" t="n"/>
     </row>
     <row r="306">
       <c r="A306" s="3" t="n"/>
@@ -11043,6 +13837,15 @@
       <c r="AD306" s="3" t="n"/>
       <c r="AE306" s="3" t="n"/>
       <c r="AF306" s="3" t="n"/>
+      <c r="AG306" s="3" t="n"/>
+      <c r="AH306" s="3" t="n"/>
+      <c r="AI306" s="3" t="n"/>
+      <c r="AJ306" s="3" t="n"/>
+      <c r="AK306" s="3" t="n"/>
+      <c r="AL306" s="3" t="n"/>
+      <c r="AM306" s="3" t="n"/>
+      <c r="AN306" s="3" t="n"/>
+      <c r="AO306" s="3" t="n"/>
     </row>
     <row r="307">
       <c r="A307" s="4" t="n"/>
@@ -11077,6 +13880,15 @@
       <c r="AD307" s="4" t="n"/>
       <c r="AE307" s="4" t="n"/>
       <c r="AF307" s="4" t="n"/>
+      <c r="AG307" s="4" t="n"/>
+      <c r="AH307" s="4" t="n"/>
+      <c r="AI307" s="4" t="n"/>
+      <c r="AJ307" s="4" t="n"/>
+      <c r="AK307" s="4" t="n"/>
+      <c r="AL307" s="4" t="n"/>
+      <c r="AM307" s="4" t="n"/>
+      <c r="AN307" s="4" t="n"/>
+      <c r="AO307" s="4" t="n"/>
     </row>
     <row r="308">
       <c r="A308" s="3" t="n"/>
@@ -11111,6 +13923,15 @@
       <c r="AD308" s="3" t="n"/>
       <c r="AE308" s="3" t="n"/>
       <c r="AF308" s="3" t="n"/>
+      <c r="AG308" s="3" t="n"/>
+      <c r="AH308" s="3" t="n"/>
+      <c r="AI308" s="3" t="n"/>
+      <c r="AJ308" s="3" t="n"/>
+      <c r="AK308" s="3" t="n"/>
+      <c r="AL308" s="3" t="n"/>
+      <c r="AM308" s="3" t="n"/>
+      <c r="AN308" s="3" t="n"/>
+      <c r="AO308" s="3" t="n"/>
     </row>
     <row r="309">
       <c r="A309" s="4" t="n"/>
@@ -11145,6 +13966,15 @@
       <c r="AD309" s="4" t="n"/>
       <c r="AE309" s="4" t="n"/>
       <c r="AF309" s="4" t="n"/>
+      <c r="AG309" s="4" t="n"/>
+      <c r="AH309" s="4" t="n"/>
+      <c r="AI309" s="4" t="n"/>
+      <c r="AJ309" s="4" t="n"/>
+      <c r="AK309" s="4" t="n"/>
+      <c r="AL309" s="4" t="n"/>
+      <c r="AM309" s="4" t="n"/>
+      <c r="AN309" s="4" t="n"/>
+      <c r="AO309" s="4" t="n"/>
     </row>
     <row r="310">
       <c r="A310" s="3" t="n"/>
@@ -11179,6 +14009,15 @@
       <c r="AD310" s="3" t="n"/>
       <c r="AE310" s="3" t="n"/>
       <c r="AF310" s="3" t="n"/>
+      <c r="AG310" s="3" t="n"/>
+      <c r="AH310" s="3" t="n"/>
+      <c r="AI310" s="3" t="n"/>
+      <c r="AJ310" s="3" t="n"/>
+      <c r="AK310" s="3" t="n"/>
+      <c r="AL310" s="3" t="n"/>
+      <c r="AM310" s="3" t="n"/>
+      <c r="AN310" s="3" t="n"/>
+      <c r="AO310" s="3" t="n"/>
     </row>
     <row r="311">
       <c r="A311" s="4" t="n"/>
@@ -11213,6 +14052,15 @@
       <c r="AD311" s="4" t="n"/>
       <c r="AE311" s="4" t="n"/>
       <c r="AF311" s="4" t="n"/>
+      <c r="AG311" s="4" t="n"/>
+      <c r="AH311" s="4" t="n"/>
+      <c r="AI311" s="4" t="n"/>
+      <c r="AJ311" s="4" t="n"/>
+      <c r="AK311" s="4" t="n"/>
+      <c r="AL311" s="4" t="n"/>
+      <c r="AM311" s="4" t="n"/>
+      <c r="AN311" s="4" t="n"/>
+      <c r="AO311" s="4" t="n"/>
     </row>
     <row r="312">
       <c r="A312" s="3" t="n"/>
@@ -11247,6 +14095,15 @@
       <c r="AD312" s="3" t="n"/>
       <c r="AE312" s="3" t="n"/>
       <c r="AF312" s="3" t="n"/>
+      <c r="AG312" s="3" t="n"/>
+      <c r="AH312" s="3" t="n"/>
+      <c r="AI312" s="3" t="n"/>
+      <c r="AJ312" s="3" t="n"/>
+      <c r="AK312" s="3" t="n"/>
+      <c r="AL312" s="3" t="n"/>
+      <c r="AM312" s="3" t="n"/>
+      <c r="AN312" s="3" t="n"/>
+      <c r="AO312" s="3" t="n"/>
     </row>
     <row r="313">
       <c r="A313" s="4" t="n"/>
@@ -11281,6 +14138,15 @@
       <c r="AD313" s="4" t="n"/>
       <c r="AE313" s="4" t="n"/>
       <c r="AF313" s="4" t="n"/>
+      <c r="AG313" s="4" t="n"/>
+      <c r="AH313" s="4" t="n"/>
+      <c r="AI313" s="4" t="n"/>
+      <c r="AJ313" s="4" t="n"/>
+      <c r="AK313" s="4" t="n"/>
+      <c r="AL313" s="4" t="n"/>
+      <c r="AM313" s="4" t="n"/>
+      <c r="AN313" s="4" t="n"/>
+      <c r="AO313" s="4" t="n"/>
     </row>
     <row r="314">
       <c r="A314" s="3" t="n"/>
@@ -11315,6 +14181,15 @@
       <c r="AD314" s="3" t="n"/>
       <c r="AE314" s="3" t="n"/>
       <c r="AF314" s="3" t="n"/>
+      <c r="AG314" s="3" t="n"/>
+      <c r="AH314" s="3" t="n"/>
+      <c r="AI314" s="3" t="n"/>
+      <c r="AJ314" s="3" t="n"/>
+      <c r="AK314" s="3" t="n"/>
+      <c r="AL314" s="3" t="n"/>
+      <c r="AM314" s="3" t="n"/>
+      <c r="AN314" s="3" t="n"/>
+      <c r="AO314" s="3" t="n"/>
     </row>
     <row r="315">
       <c r="A315" s="4" t="n"/>
@@ -11349,6 +14224,15 @@
       <c r="AD315" s="4" t="n"/>
       <c r="AE315" s="4" t="n"/>
       <c r="AF315" s="4" t="n"/>
+      <c r="AG315" s="4" t="n"/>
+      <c r="AH315" s="4" t="n"/>
+      <c r="AI315" s="4" t="n"/>
+      <c r="AJ315" s="4" t="n"/>
+      <c r="AK315" s="4" t="n"/>
+      <c r="AL315" s="4" t="n"/>
+      <c r="AM315" s="4" t="n"/>
+      <c r="AN315" s="4" t="n"/>
+      <c r="AO315" s="4" t="n"/>
     </row>
     <row r="316">
       <c r="A316" s="3" t="n"/>
@@ -11383,6 +14267,15 @@
       <c r="AD316" s="3" t="n"/>
       <c r="AE316" s="3" t="n"/>
       <c r="AF316" s="3" t="n"/>
+      <c r="AG316" s="3" t="n"/>
+      <c r="AH316" s="3" t="n"/>
+      <c r="AI316" s="3" t="n"/>
+      <c r="AJ316" s="3" t="n"/>
+      <c r="AK316" s="3" t="n"/>
+      <c r="AL316" s="3" t="n"/>
+      <c r="AM316" s="3" t="n"/>
+      <c r="AN316" s="3" t="n"/>
+      <c r="AO316" s="3" t="n"/>
     </row>
     <row r="317">
       <c r="A317" s="4" t="n"/>
@@ -11417,6 +14310,15 @@
       <c r="AD317" s="4" t="n"/>
       <c r="AE317" s="4" t="n"/>
       <c r="AF317" s="4" t="n"/>
+      <c r="AG317" s="4" t="n"/>
+      <c r="AH317" s="4" t="n"/>
+      <c r="AI317" s="4" t="n"/>
+      <c r="AJ317" s="4" t="n"/>
+      <c r="AK317" s="4" t="n"/>
+      <c r="AL317" s="4" t="n"/>
+      <c r="AM317" s="4" t="n"/>
+      <c r="AN317" s="4" t="n"/>
+      <c r="AO317" s="4" t="n"/>
     </row>
     <row r="318">
       <c r="A318" s="3" t="n"/>
@@ -11451,6 +14353,15 @@
       <c r="AD318" s="3" t="n"/>
       <c r="AE318" s="3" t="n"/>
       <c r="AF318" s="3" t="n"/>
+      <c r="AG318" s="3" t="n"/>
+      <c r="AH318" s="3" t="n"/>
+      <c r="AI318" s="3" t="n"/>
+      <c r="AJ318" s="3" t="n"/>
+      <c r="AK318" s="3" t="n"/>
+      <c r="AL318" s="3" t="n"/>
+      <c r="AM318" s="3" t="n"/>
+      <c r="AN318" s="3" t="n"/>
+      <c r="AO318" s="3" t="n"/>
     </row>
     <row r="319">
       <c r="A319" s="4" t="n"/>
@@ -11485,6 +14396,15 @@
       <c r="AD319" s="4" t="n"/>
       <c r="AE319" s="4" t="n"/>
       <c r="AF319" s="4" t="n"/>
+      <c r="AG319" s="4" t="n"/>
+      <c r="AH319" s="4" t="n"/>
+      <c r="AI319" s="4" t="n"/>
+      <c r="AJ319" s="4" t="n"/>
+      <c r="AK319" s="4" t="n"/>
+      <c r="AL319" s="4" t="n"/>
+      <c r="AM319" s="4" t="n"/>
+      <c r="AN319" s="4" t="n"/>
+      <c r="AO319" s="4" t="n"/>
     </row>
     <row r="320">
       <c r="A320" s="3" t="n"/>
@@ -11519,6 +14439,15 @@
       <c r="AD320" s="3" t="n"/>
       <c r="AE320" s="3" t="n"/>
       <c r="AF320" s="3" t="n"/>
+      <c r="AG320" s="3" t="n"/>
+      <c r="AH320" s="3" t="n"/>
+      <c r="AI320" s="3" t="n"/>
+      <c r="AJ320" s="3" t="n"/>
+      <c r="AK320" s="3" t="n"/>
+      <c r="AL320" s="3" t="n"/>
+      <c r="AM320" s="3" t="n"/>
+      <c r="AN320" s="3" t="n"/>
+      <c r="AO320" s="3" t="n"/>
     </row>
     <row r="321">
       <c r="A321" s="4" t="n"/>
@@ -11553,6 +14482,15 @@
       <c r="AD321" s="4" t="n"/>
       <c r="AE321" s="4" t="n"/>
       <c r="AF321" s="4" t="n"/>
+      <c r="AG321" s="4" t="n"/>
+      <c r="AH321" s="4" t="n"/>
+      <c r="AI321" s="4" t="n"/>
+      <c r="AJ321" s="4" t="n"/>
+      <c r="AK321" s="4" t="n"/>
+      <c r="AL321" s="4" t="n"/>
+      <c r="AM321" s="4" t="n"/>
+      <c r="AN321" s="4" t="n"/>
+      <c r="AO321" s="4" t="n"/>
     </row>
     <row r="322">
       <c r="A322" s="3" t="n"/>
@@ -11587,6 +14525,15 @@
       <c r="AD322" s="3" t="n"/>
       <c r="AE322" s="3" t="n"/>
       <c r="AF322" s="3" t="n"/>
+      <c r="AG322" s="3" t="n"/>
+      <c r="AH322" s="3" t="n"/>
+      <c r="AI322" s="3" t="n"/>
+      <c r="AJ322" s="3" t="n"/>
+      <c r="AK322" s="3" t="n"/>
+      <c r="AL322" s="3" t="n"/>
+      <c r="AM322" s="3" t="n"/>
+      <c r="AN322" s="3" t="n"/>
+      <c r="AO322" s="3" t="n"/>
     </row>
     <row r="323">
       <c r="A323" s="4" t="n"/>
@@ -11621,6 +14568,15 @@
       <c r="AD323" s="4" t="n"/>
       <c r="AE323" s="4" t="n"/>
       <c r="AF323" s="4" t="n"/>
+      <c r="AG323" s="4" t="n"/>
+      <c r="AH323" s="4" t="n"/>
+      <c r="AI323" s="4" t="n"/>
+      <c r="AJ323" s="4" t="n"/>
+      <c r="AK323" s="4" t="n"/>
+      <c r="AL323" s="4" t="n"/>
+      <c r="AM323" s="4" t="n"/>
+      <c r="AN323" s="4" t="n"/>
+      <c r="AO323" s="4" t="n"/>
     </row>
     <row r="324">
       <c r="A324" s="3" t="n"/>
@@ -11655,6 +14611,15 @@
       <c r="AD324" s="3" t="n"/>
       <c r="AE324" s="3" t="n"/>
       <c r="AF324" s="3" t="n"/>
+      <c r="AG324" s="3" t="n"/>
+      <c r="AH324" s="3" t="n"/>
+      <c r="AI324" s="3" t="n"/>
+      <c r="AJ324" s="3" t="n"/>
+      <c r="AK324" s="3" t="n"/>
+      <c r="AL324" s="3" t="n"/>
+      <c r="AM324" s="3" t="n"/>
+      <c r="AN324" s="3" t="n"/>
+      <c r="AO324" s="3" t="n"/>
     </row>
     <row r="325">
       <c r="A325" s="4" t="n"/>
@@ -11689,6 +14654,15 @@
       <c r="AD325" s="4" t="n"/>
       <c r="AE325" s="4" t="n"/>
       <c r="AF325" s="4" t="n"/>
+      <c r="AG325" s="4" t="n"/>
+      <c r="AH325" s="4" t="n"/>
+      <c r="AI325" s="4" t="n"/>
+      <c r="AJ325" s="4" t="n"/>
+      <c r="AK325" s="4" t="n"/>
+      <c r="AL325" s="4" t="n"/>
+      <c r="AM325" s="4" t="n"/>
+      <c r="AN325" s="4" t="n"/>
+      <c r="AO325" s="4" t="n"/>
     </row>
     <row r="326">
       <c r="A326" s="3" t="n"/>
@@ -11723,6 +14697,15 @@
       <c r="AD326" s="3" t="n"/>
       <c r="AE326" s="3" t="n"/>
       <c r="AF326" s="3" t="n"/>
+      <c r="AG326" s="3" t="n"/>
+      <c r="AH326" s="3" t="n"/>
+      <c r="AI326" s="3" t="n"/>
+      <c r="AJ326" s="3" t="n"/>
+      <c r="AK326" s="3" t="n"/>
+      <c r="AL326" s="3" t="n"/>
+      <c r="AM326" s="3" t="n"/>
+      <c r="AN326" s="3" t="n"/>
+      <c r="AO326" s="3" t="n"/>
     </row>
     <row r="327">
       <c r="A327" s="4" t="n"/>
@@ -11757,6 +14740,15 @@
       <c r="AD327" s="4" t="n"/>
       <c r="AE327" s="4" t="n"/>
       <c r="AF327" s="4" t="n"/>
+      <c r="AG327" s="4" t="n"/>
+      <c r="AH327" s="4" t="n"/>
+      <c r="AI327" s="4" t="n"/>
+      <c r="AJ327" s="4" t="n"/>
+      <c r="AK327" s="4" t="n"/>
+      <c r="AL327" s="4" t="n"/>
+      <c r="AM327" s="4" t="n"/>
+      <c r="AN327" s="4" t="n"/>
+      <c r="AO327" s="4" t="n"/>
     </row>
     <row r="328">
       <c r="A328" s="3" t="n"/>
@@ -11791,6 +14783,15 @@
       <c r="AD328" s="3" t="n"/>
       <c r="AE328" s="3" t="n"/>
       <c r="AF328" s="3" t="n"/>
+      <c r="AG328" s="3" t="n"/>
+      <c r="AH328" s="3" t="n"/>
+      <c r="AI328" s="3" t="n"/>
+      <c r="AJ328" s="3" t="n"/>
+      <c r="AK328" s="3" t="n"/>
+      <c r="AL328" s="3" t="n"/>
+      <c r="AM328" s="3" t="n"/>
+      <c r="AN328" s="3" t="n"/>
+      <c r="AO328" s="3" t="n"/>
     </row>
     <row r="329">
       <c r="A329" s="4" t="n"/>
@@ -11825,6 +14826,15 @@
       <c r="AD329" s="4" t="n"/>
       <c r="AE329" s="4" t="n"/>
       <c r="AF329" s="4" t="n"/>
+      <c r="AG329" s="4" t="n"/>
+      <c r="AH329" s="4" t="n"/>
+      <c r="AI329" s="4" t="n"/>
+      <c r="AJ329" s="4" t="n"/>
+      <c r="AK329" s="4" t="n"/>
+      <c r="AL329" s="4" t="n"/>
+      <c r="AM329" s="4" t="n"/>
+      <c r="AN329" s="4" t="n"/>
+      <c r="AO329" s="4" t="n"/>
     </row>
     <row r="330">
       <c r="A330" s="3" t="n"/>
@@ -11859,6 +14869,15 @@
       <c r="AD330" s="3" t="n"/>
       <c r="AE330" s="3" t="n"/>
       <c r="AF330" s="3" t="n"/>
+      <c r="AG330" s="3" t="n"/>
+      <c r="AH330" s="3" t="n"/>
+      <c r="AI330" s="3" t="n"/>
+      <c r="AJ330" s="3" t="n"/>
+      <c r="AK330" s="3" t="n"/>
+      <c r="AL330" s="3" t="n"/>
+      <c r="AM330" s="3" t="n"/>
+      <c r="AN330" s="3" t="n"/>
+      <c r="AO330" s="3" t="n"/>
     </row>
     <row r="331">
       <c r="A331" s="4" t="n"/>
@@ -11893,6 +14912,15 @@
       <c r="AD331" s="4" t="n"/>
       <c r="AE331" s="4" t="n"/>
       <c r="AF331" s="4" t="n"/>
+      <c r="AG331" s="4" t="n"/>
+      <c r="AH331" s="4" t="n"/>
+      <c r="AI331" s="4" t="n"/>
+      <c r="AJ331" s="4" t="n"/>
+      <c r="AK331" s="4" t="n"/>
+      <c r="AL331" s="4" t="n"/>
+      <c r="AM331" s="4" t="n"/>
+      <c r="AN331" s="4" t="n"/>
+      <c r="AO331" s="4" t="n"/>
     </row>
     <row r="332">
       <c r="A332" s="3" t="n"/>
@@ -11927,6 +14955,15 @@
       <c r="AD332" s="3" t="n"/>
       <c r="AE332" s="3" t="n"/>
       <c r="AF332" s="3" t="n"/>
+      <c r="AG332" s="3" t="n"/>
+      <c r="AH332" s="3" t="n"/>
+      <c r="AI332" s="3" t="n"/>
+      <c r="AJ332" s="3" t="n"/>
+      <c r="AK332" s="3" t="n"/>
+      <c r="AL332" s="3" t="n"/>
+      <c r="AM332" s="3" t="n"/>
+      <c r="AN332" s="3" t="n"/>
+      <c r="AO332" s="3" t="n"/>
     </row>
     <row r="333">
       <c r="A333" s="4" t="n"/>
@@ -11961,6 +14998,15 @@
       <c r="AD333" s="4" t="n"/>
       <c r="AE333" s="4" t="n"/>
       <c r="AF333" s="4" t="n"/>
+      <c r="AG333" s="4" t="n"/>
+      <c r="AH333" s="4" t="n"/>
+      <c r="AI333" s="4" t="n"/>
+      <c r="AJ333" s="4" t="n"/>
+      <c r="AK333" s="4" t="n"/>
+      <c r="AL333" s="4" t="n"/>
+      <c r="AM333" s="4" t="n"/>
+      <c r="AN333" s="4" t="n"/>
+      <c r="AO333" s="4" t="n"/>
     </row>
     <row r="334">
       <c r="A334" s="3" t="n"/>
@@ -11995,6 +15041,15 @@
       <c r="AD334" s="3" t="n"/>
       <c r="AE334" s="3" t="n"/>
       <c r="AF334" s="3" t="n"/>
+      <c r="AG334" s="3" t="n"/>
+      <c r="AH334" s="3" t="n"/>
+      <c r="AI334" s="3" t="n"/>
+      <c r="AJ334" s="3" t="n"/>
+      <c r="AK334" s="3" t="n"/>
+      <c r="AL334" s="3" t="n"/>
+      <c r="AM334" s="3" t="n"/>
+      <c r="AN334" s="3" t="n"/>
+      <c r="AO334" s="3" t="n"/>
     </row>
     <row r="335">
       <c r="A335" s="4" t="n"/>
@@ -12029,6 +15084,15 @@
       <c r="AD335" s="4" t="n"/>
       <c r="AE335" s="4" t="n"/>
       <c r="AF335" s="4" t="n"/>
+      <c r="AG335" s="4" t="n"/>
+      <c r="AH335" s="4" t="n"/>
+      <c r="AI335" s="4" t="n"/>
+      <c r="AJ335" s="4" t="n"/>
+      <c r="AK335" s="4" t="n"/>
+      <c r="AL335" s="4" t="n"/>
+      <c r="AM335" s="4" t="n"/>
+      <c r="AN335" s="4" t="n"/>
+      <c r="AO335" s="4" t="n"/>
     </row>
     <row r="336">
       <c r="A336" s="3" t="n"/>
@@ -12063,6 +15127,15 @@
       <c r="AD336" s="3" t="n"/>
       <c r="AE336" s="3" t="n"/>
       <c r="AF336" s="3" t="n"/>
+      <c r="AG336" s="3" t="n"/>
+      <c r="AH336" s="3" t="n"/>
+      <c r="AI336" s="3" t="n"/>
+      <c r="AJ336" s="3" t="n"/>
+      <c r="AK336" s="3" t="n"/>
+      <c r="AL336" s="3" t="n"/>
+      <c r="AM336" s="3" t="n"/>
+      <c r="AN336" s="3" t="n"/>
+      <c r="AO336" s="3" t="n"/>
     </row>
     <row r="337">
       <c r="A337" s="4" t="n"/>
@@ -12097,6 +15170,15 @@
       <c r="AD337" s="4" t="n"/>
       <c r="AE337" s="4" t="n"/>
       <c r="AF337" s="4" t="n"/>
+      <c r="AG337" s="4" t="n"/>
+      <c r="AH337" s="4" t="n"/>
+      <c r="AI337" s="4" t="n"/>
+      <c r="AJ337" s="4" t="n"/>
+      <c r="AK337" s="4" t="n"/>
+      <c r="AL337" s="4" t="n"/>
+      <c r="AM337" s="4" t="n"/>
+      <c r="AN337" s="4" t="n"/>
+      <c r="AO337" s="4" t="n"/>
     </row>
     <row r="338">
       <c r="A338" s="3" t="n"/>
@@ -12131,6 +15213,15 @@
       <c r="AD338" s="3" t="n"/>
       <c r="AE338" s="3" t="n"/>
       <c r="AF338" s="3" t="n"/>
+      <c r="AG338" s="3" t="n"/>
+      <c r="AH338" s="3" t="n"/>
+      <c r="AI338" s="3" t="n"/>
+      <c r="AJ338" s="3" t="n"/>
+      <c r="AK338" s="3" t="n"/>
+      <c r="AL338" s="3" t="n"/>
+      <c r="AM338" s="3" t="n"/>
+      <c r="AN338" s="3" t="n"/>
+      <c r="AO338" s="3" t="n"/>
     </row>
     <row r="339">
       <c r="A339" s="4" t="n"/>
@@ -12165,6 +15256,15 @@
       <c r="AD339" s="4" t="n"/>
       <c r="AE339" s="4" t="n"/>
       <c r="AF339" s="4" t="n"/>
+      <c r="AG339" s="4" t="n"/>
+      <c r="AH339" s="4" t="n"/>
+      <c r="AI339" s="4" t="n"/>
+      <c r="AJ339" s="4" t="n"/>
+      <c r="AK339" s="4" t="n"/>
+      <c r="AL339" s="4" t="n"/>
+      <c r="AM339" s="4" t="n"/>
+      <c r="AN339" s="4" t="n"/>
+      <c r="AO339" s="4" t="n"/>
     </row>
     <row r="340">
       <c r="A340" s="3" t="n"/>
@@ -12199,6 +15299,15 @@
       <c r="AD340" s="3" t="n"/>
       <c r="AE340" s="3" t="n"/>
       <c r="AF340" s="3" t="n"/>
+      <c r="AG340" s="3" t="n"/>
+      <c r="AH340" s="3" t="n"/>
+      <c r="AI340" s="3" t="n"/>
+      <c r="AJ340" s="3" t="n"/>
+      <c r="AK340" s="3" t="n"/>
+      <c r="AL340" s="3" t="n"/>
+      <c r="AM340" s="3" t="n"/>
+      <c r="AN340" s="3" t="n"/>
+      <c r="AO340" s="3" t="n"/>
     </row>
     <row r="341">
       <c r="A341" s="4" t="n"/>
@@ -12233,6 +15342,15 @@
       <c r="AD341" s="4" t="n"/>
       <c r="AE341" s="4" t="n"/>
       <c r="AF341" s="4" t="n"/>
+      <c r="AG341" s="4" t="n"/>
+      <c r="AH341" s="4" t="n"/>
+      <c r="AI341" s="4" t="n"/>
+      <c r="AJ341" s="4" t="n"/>
+      <c r="AK341" s="4" t="n"/>
+      <c r="AL341" s="4" t="n"/>
+      <c r="AM341" s="4" t="n"/>
+      <c r="AN341" s="4" t="n"/>
+      <c r="AO341" s="4" t="n"/>
     </row>
     <row r="342">
       <c r="A342" s="3" t="n"/>
@@ -12267,6 +15385,15 @@
       <c r="AD342" s="3" t="n"/>
       <c r="AE342" s="3" t="n"/>
       <c r="AF342" s="3" t="n"/>
+      <c r="AG342" s="3" t="n"/>
+      <c r="AH342" s="3" t="n"/>
+      <c r="AI342" s="3" t="n"/>
+      <c r="AJ342" s="3" t="n"/>
+      <c r="AK342" s="3" t="n"/>
+      <c r="AL342" s="3" t="n"/>
+      <c r="AM342" s="3" t="n"/>
+      <c r="AN342" s="3" t="n"/>
+      <c r="AO342" s="3" t="n"/>
     </row>
     <row r="343">
       <c r="A343" s="4" t="n"/>
@@ -12301,6 +15428,15 @@
       <c r="AD343" s="4" t="n"/>
       <c r="AE343" s="4" t="n"/>
       <c r="AF343" s="4" t="n"/>
+      <c r="AG343" s="4" t="n"/>
+      <c r="AH343" s="4" t="n"/>
+      <c r="AI343" s="4" t="n"/>
+      <c r="AJ343" s="4" t="n"/>
+      <c r="AK343" s="4" t="n"/>
+      <c r="AL343" s="4" t="n"/>
+      <c r="AM343" s="4" t="n"/>
+      <c r="AN343" s="4" t="n"/>
+      <c r="AO343" s="4" t="n"/>
     </row>
     <row r="344">
       <c r="A344" s="3" t="n"/>
@@ -12335,6 +15471,15 @@
       <c r="AD344" s="3" t="n"/>
       <c r="AE344" s="3" t="n"/>
       <c r="AF344" s="3" t="n"/>
+      <c r="AG344" s="3" t="n"/>
+      <c r="AH344" s="3" t="n"/>
+      <c r="AI344" s="3" t="n"/>
+      <c r="AJ344" s="3" t="n"/>
+      <c r="AK344" s="3" t="n"/>
+      <c r="AL344" s="3" t="n"/>
+      <c r="AM344" s="3" t="n"/>
+      <c r="AN344" s="3" t="n"/>
+      <c r="AO344" s="3" t="n"/>
     </row>
     <row r="345">
       <c r="A345" s="4" t="n"/>
@@ -12369,6 +15514,15 @@
       <c r="AD345" s="4" t="n"/>
       <c r="AE345" s="4" t="n"/>
       <c r="AF345" s="4" t="n"/>
+      <c r="AG345" s="4" t="n"/>
+      <c r="AH345" s="4" t="n"/>
+      <c r="AI345" s="4" t="n"/>
+      <c r="AJ345" s="4" t="n"/>
+      <c r="AK345" s="4" t="n"/>
+      <c r="AL345" s="4" t="n"/>
+      <c r="AM345" s="4" t="n"/>
+      <c r="AN345" s="4" t="n"/>
+      <c r="AO345" s="4" t="n"/>
     </row>
     <row r="346">
       <c r="A346" s="3" t="n"/>
@@ -12403,6 +15557,15 @@
       <c r="AD346" s="3" t="n"/>
       <c r="AE346" s="3" t="n"/>
       <c r="AF346" s="3" t="n"/>
+      <c r="AG346" s="3" t="n"/>
+      <c r="AH346" s="3" t="n"/>
+      <c r="AI346" s="3" t="n"/>
+      <c r="AJ346" s="3" t="n"/>
+      <c r="AK346" s="3" t="n"/>
+      <c r="AL346" s="3" t="n"/>
+      <c r="AM346" s="3" t="n"/>
+      <c r="AN346" s="3" t="n"/>
+      <c r="AO346" s="3" t="n"/>
     </row>
     <row r="347">
       <c r="A347" s="4" t="n"/>
@@ -12437,6 +15600,15 @@
       <c r="AD347" s="4" t="n"/>
       <c r="AE347" s="4" t="n"/>
       <c r="AF347" s="4" t="n"/>
+      <c r="AG347" s="4" t="n"/>
+      <c r="AH347" s="4" t="n"/>
+      <c r="AI347" s="4" t="n"/>
+      <c r="AJ347" s="4" t="n"/>
+      <c r="AK347" s="4" t="n"/>
+      <c r="AL347" s="4" t="n"/>
+      <c r="AM347" s="4" t="n"/>
+      <c r="AN347" s="4" t="n"/>
+      <c r="AO347" s="4" t="n"/>
     </row>
     <row r="348">
       <c r="A348" s="3" t="n"/>
@@ -12471,6 +15643,15 @@
       <c r="AD348" s="3" t="n"/>
       <c r="AE348" s="3" t="n"/>
       <c r="AF348" s="3" t="n"/>
+      <c r="AG348" s="3" t="n"/>
+      <c r="AH348" s="3" t="n"/>
+      <c r="AI348" s="3" t="n"/>
+      <c r="AJ348" s="3" t="n"/>
+      <c r="AK348" s="3" t="n"/>
+      <c r="AL348" s="3" t="n"/>
+      <c r="AM348" s="3" t="n"/>
+      <c r="AN348" s="3" t="n"/>
+      <c r="AO348" s="3" t="n"/>
     </row>
     <row r="349">
       <c r="A349" s="4" t="n"/>
@@ -12505,6 +15686,15 @@
       <c r="AD349" s="4" t="n"/>
       <c r="AE349" s="4" t="n"/>
       <c r="AF349" s="4" t="n"/>
+      <c r="AG349" s="4" t="n"/>
+      <c r="AH349" s="4" t="n"/>
+      <c r="AI349" s="4" t="n"/>
+      <c r="AJ349" s="4" t="n"/>
+      <c r="AK349" s="4" t="n"/>
+      <c r="AL349" s="4" t="n"/>
+      <c r="AM349" s="4" t="n"/>
+      <c r="AN349" s="4" t="n"/>
+      <c r="AO349" s="4" t="n"/>
     </row>
     <row r="350">
       <c r="A350" s="3" t="n"/>
@@ -12539,6 +15729,15 @@
       <c r="AD350" s="3" t="n"/>
       <c r="AE350" s="3" t="n"/>
       <c r="AF350" s="3" t="n"/>
+      <c r="AG350" s="3" t="n"/>
+      <c r="AH350" s="3" t="n"/>
+      <c r="AI350" s="3" t="n"/>
+      <c r="AJ350" s="3" t="n"/>
+      <c r="AK350" s="3" t="n"/>
+      <c r="AL350" s="3" t="n"/>
+      <c r="AM350" s="3" t="n"/>
+      <c r="AN350" s="3" t="n"/>
+      <c r="AO350" s="3" t="n"/>
     </row>
     <row r="351">
       <c r="A351" s="4" t="n"/>
@@ -12573,6 +15772,15 @@
       <c r="AD351" s="4" t="n"/>
       <c r="AE351" s="4" t="n"/>
       <c r="AF351" s="4" t="n"/>
+      <c r="AG351" s="4" t="n"/>
+      <c r="AH351" s="4" t="n"/>
+      <c r="AI351" s="4" t="n"/>
+      <c r="AJ351" s="4" t="n"/>
+      <c r="AK351" s="4" t="n"/>
+      <c r="AL351" s="4" t="n"/>
+      <c r="AM351" s="4" t="n"/>
+      <c r="AN351" s="4" t="n"/>
+      <c r="AO351" s="4" t="n"/>
     </row>
     <row r="352">
       <c r="A352" s="3" t="n"/>
@@ -12607,6 +15815,15 @@
       <c r="AD352" s="3" t="n"/>
       <c r="AE352" s="3" t="n"/>
       <c r="AF352" s="3" t="n"/>
+      <c r="AG352" s="3" t="n"/>
+      <c r="AH352" s="3" t="n"/>
+      <c r="AI352" s="3" t="n"/>
+      <c r="AJ352" s="3" t="n"/>
+      <c r="AK352" s="3" t="n"/>
+      <c r="AL352" s="3" t="n"/>
+      <c r="AM352" s="3" t="n"/>
+      <c r="AN352" s="3" t="n"/>
+      <c r="AO352" s="3" t="n"/>
     </row>
     <row r="353">
       <c r="A353" s="4" t="n"/>
@@ -12641,6 +15858,15 @@
       <c r="AD353" s="4" t="n"/>
       <c r="AE353" s="4" t="n"/>
       <c r="AF353" s="4" t="n"/>
+      <c r="AG353" s="4" t="n"/>
+      <c r="AH353" s="4" t="n"/>
+      <c r="AI353" s="4" t="n"/>
+      <c r="AJ353" s="4" t="n"/>
+      <c r="AK353" s="4" t="n"/>
+      <c r="AL353" s="4" t="n"/>
+      <c r="AM353" s="4" t="n"/>
+      <c r="AN353" s="4" t="n"/>
+      <c r="AO353" s="4" t="n"/>
     </row>
     <row r="354">
       <c r="A354" s="3" t="n"/>
@@ -12675,6 +15901,15 @@
       <c r="AD354" s="3" t="n"/>
       <c r="AE354" s="3" t="n"/>
       <c r="AF354" s="3" t="n"/>
+      <c r="AG354" s="3" t="n"/>
+      <c r="AH354" s="3" t="n"/>
+      <c r="AI354" s="3" t="n"/>
+      <c r="AJ354" s="3" t="n"/>
+      <c r="AK354" s="3" t="n"/>
+      <c r="AL354" s="3" t="n"/>
+      <c r="AM354" s="3" t="n"/>
+      <c r="AN354" s="3" t="n"/>
+      <c r="AO354" s="3" t="n"/>
     </row>
     <row r="355">
       <c r="A355" s="4" t="n"/>
@@ -12709,6 +15944,15 @@
       <c r="AD355" s="4" t="n"/>
       <c r="AE355" s="4" t="n"/>
       <c r="AF355" s="4" t="n"/>
+      <c r="AG355" s="4" t="n"/>
+      <c r="AH355" s="4" t="n"/>
+      <c r="AI355" s="4" t="n"/>
+      <c r="AJ355" s="4" t="n"/>
+      <c r="AK355" s="4" t="n"/>
+      <c r="AL355" s="4" t="n"/>
+      <c r="AM355" s="4" t="n"/>
+      <c r="AN355" s="4" t="n"/>
+      <c r="AO355" s="4" t="n"/>
     </row>
     <row r="356">
       <c r="A356" s="3" t="n"/>
@@ -12743,6 +15987,15 @@
       <c r="AD356" s="3" t="n"/>
       <c r="AE356" s="3" t="n"/>
       <c r="AF356" s="3" t="n"/>
+      <c r="AG356" s="3" t="n"/>
+      <c r="AH356" s="3" t="n"/>
+      <c r="AI356" s="3" t="n"/>
+      <c r="AJ356" s="3" t="n"/>
+      <c r="AK356" s="3" t="n"/>
+      <c r="AL356" s="3" t="n"/>
+      <c r="AM356" s="3" t="n"/>
+      <c r="AN356" s="3" t="n"/>
+      <c r="AO356" s="3" t="n"/>
     </row>
     <row r="357">
       <c r="A357" s="4" t="n"/>
@@ -12777,6 +16030,15 @@
       <c r="AD357" s="4" t="n"/>
       <c r="AE357" s="4" t="n"/>
       <c r="AF357" s="4" t="n"/>
+      <c r="AG357" s="4" t="n"/>
+      <c r="AH357" s="4" t="n"/>
+      <c r="AI357" s="4" t="n"/>
+      <c r="AJ357" s="4" t="n"/>
+      <c r="AK357" s="4" t="n"/>
+      <c r="AL357" s="4" t="n"/>
+      <c r="AM357" s="4" t="n"/>
+      <c r="AN357" s="4" t="n"/>
+      <c r="AO357" s="4" t="n"/>
     </row>
     <row r="358">
       <c r="A358" s="3" t="n"/>
@@ -12811,6 +16073,15 @@
       <c r="AD358" s="3" t="n"/>
       <c r="AE358" s="3" t="n"/>
       <c r="AF358" s="3" t="n"/>
+      <c r="AG358" s="3" t="n"/>
+      <c r="AH358" s="3" t="n"/>
+      <c r="AI358" s="3" t="n"/>
+      <c r="AJ358" s="3" t="n"/>
+      <c r="AK358" s="3" t="n"/>
+      <c r="AL358" s="3" t="n"/>
+      <c r="AM358" s="3" t="n"/>
+      <c r="AN358" s="3" t="n"/>
+      <c r="AO358" s="3" t="n"/>
     </row>
     <row r="359">
       <c r="A359" s="4" t="n"/>
@@ -12845,6 +16116,15 @@
       <c r="AD359" s="4" t="n"/>
       <c r="AE359" s="4" t="n"/>
       <c r="AF359" s="4" t="n"/>
+      <c r="AG359" s="4" t="n"/>
+      <c r="AH359" s="4" t="n"/>
+      <c r="AI359" s="4" t="n"/>
+      <c r="AJ359" s="4" t="n"/>
+      <c r="AK359" s="4" t="n"/>
+      <c r="AL359" s="4" t="n"/>
+      <c r="AM359" s="4" t="n"/>
+      <c r="AN359" s="4" t="n"/>
+      <c r="AO359" s="4" t="n"/>
     </row>
     <row r="360">
       <c r="A360" s="3" t="n"/>
@@ -12879,6 +16159,15 @@
       <c r="AD360" s="3" t="n"/>
       <c r="AE360" s="3" t="n"/>
       <c r="AF360" s="3" t="n"/>
+      <c r="AG360" s="3" t="n"/>
+      <c r="AH360" s="3" t="n"/>
+      <c r="AI360" s="3" t="n"/>
+      <c r="AJ360" s="3" t="n"/>
+      <c r="AK360" s="3" t="n"/>
+      <c r="AL360" s="3" t="n"/>
+      <c r="AM360" s="3" t="n"/>
+      <c r="AN360" s="3" t="n"/>
+      <c r="AO360" s="3" t="n"/>
     </row>
     <row r="361">
       <c r="A361" s="4" t="n"/>
@@ -12913,6 +16202,15 @@
       <c r="AD361" s="4" t="n"/>
       <c r="AE361" s="4" t="n"/>
       <c r="AF361" s="4" t="n"/>
+      <c r="AG361" s="4" t="n"/>
+      <c r="AH361" s="4" t="n"/>
+      <c r="AI361" s="4" t="n"/>
+      <c r="AJ361" s="4" t="n"/>
+      <c r="AK361" s="4" t="n"/>
+      <c r="AL361" s="4" t="n"/>
+      <c r="AM361" s="4" t="n"/>
+      <c r="AN361" s="4" t="n"/>
+      <c r="AO361" s="4" t="n"/>
     </row>
     <row r="362">
       <c r="A362" s="3" t="n"/>
@@ -12947,6 +16245,15 @@
       <c r="AD362" s="3" t="n"/>
       <c r="AE362" s="3" t="n"/>
       <c r="AF362" s="3" t="n"/>
+      <c r="AG362" s="3" t="n"/>
+      <c r="AH362" s="3" t="n"/>
+      <c r="AI362" s="3" t="n"/>
+      <c r="AJ362" s="3" t="n"/>
+      <c r="AK362" s="3" t="n"/>
+      <c r="AL362" s="3" t="n"/>
+      <c r="AM362" s="3" t="n"/>
+      <c r="AN362" s="3" t="n"/>
+      <c r="AO362" s="3" t="n"/>
     </row>
     <row r="363">
       <c r="A363" s="4" t="n"/>
@@ -12981,6 +16288,15 @@
       <c r="AD363" s="4" t="n"/>
       <c r="AE363" s="4" t="n"/>
       <c r="AF363" s="4" t="n"/>
+      <c r="AG363" s="4" t="n"/>
+      <c r="AH363" s="4" t="n"/>
+      <c r="AI363" s="4" t="n"/>
+      <c r="AJ363" s="4" t="n"/>
+      <c r="AK363" s="4" t="n"/>
+      <c r="AL363" s="4" t="n"/>
+      <c r="AM363" s="4" t="n"/>
+      <c r="AN363" s="4" t="n"/>
+      <c r="AO363" s="4" t="n"/>
     </row>
     <row r="364">
       <c r="A364" s="3" t="n"/>
@@ -13015,6 +16331,15 @@
       <c r="AD364" s="3" t="n"/>
       <c r="AE364" s="3" t="n"/>
       <c r="AF364" s="3" t="n"/>
+      <c r="AG364" s="3" t="n"/>
+      <c r="AH364" s="3" t="n"/>
+      <c r="AI364" s="3" t="n"/>
+      <c r="AJ364" s="3" t="n"/>
+      <c r="AK364" s="3" t="n"/>
+      <c r="AL364" s="3" t="n"/>
+      <c r="AM364" s="3" t="n"/>
+      <c r="AN364" s="3" t="n"/>
+      <c r="AO364" s="3" t="n"/>
     </row>
     <row r="365">
       <c r="A365" s="4" t="n"/>
@@ -13049,6 +16374,15 @@
       <c r="AD365" s="4" t="n"/>
       <c r="AE365" s="4" t="n"/>
       <c r="AF365" s="4" t="n"/>
+      <c r="AG365" s="4" t="n"/>
+      <c r="AH365" s="4" t="n"/>
+      <c r="AI365" s="4" t="n"/>
+      <c r="AJ365" s="4" t="n"/>
+      <c r="AK365" s="4" t="n"/>
+      <c r="AL365" s="4" t="n"/>
+      <c r="AM365" s="4" t="n"/>
+      <c r="AN365" s="4" t="n"/>
+      <c r="AO365" s="4" t="n"/>
     </row>
     <row r="366">
       <c r="A366" s="3" t="n"/>
@@ -13083,6 +16417,15 @@
       <c r="AD366" s="3" t="n"/>
       <c r="AE366" s="3" t="n"/>
       <c r="AF366" s="3" t="n"/>
+      <c r="AG366" s="3" t="n"/>
+      <c r="AH366" s="3" t="n"/>
+      <c r="AI366" s="3" t="n"/>
+      <c r="AJ366" s="3" t="n"/>
+      <c r="AK366" s="3" t="n"/>
+      <c r="AL366" s="3" t="n"/>
+      <c r="AM366" s="3" t="n"/>
+      <c r="AN366" s="3" t="n"/>
+      <c r="AO366" s="3" t="n"/>
     </row>
     <row r="367">
       <c r="A367" s="4" t="n"/>
@@ -13117,6 +16460,15 @@
       <c r="AD367" s="4" t="n"/>
       <c r="AE367" s="4" t="n"/>
       <c r="AF367" s="4" t="n"/>
+      <c r="AG367" s="4" t="n"/>
+      <c r="AH367" s="4" t="n"/>
+      <c r="AI367" s="4" t="n"/>
+      <c r="AJ367" s="4" t="n"/>
+      <c r="AK367" s="4" t="n"/>
+      <c r="AL367" s="4" t="n"/>
+      <c r="AM367" s="4" t="n"/>
+      <c r="AN367" s="4" t="n"/>
+      <c r="AO367" s="4" t="n"/>
     </row>
     <row r="368">
       <c r="A368" s="3" t="n"/>
@@ -13151,6 +16503,15 @@
       <c r="AD368" s="3" t="n"/>
       <c r="AE368" s="3" t="n"/>
       <c r="AF368" s="3" t="n"/>
+      <c r="AG368" s="3" t="n"/>
+      <c r="AH368" s="3" t="n"/>
+      <c r="AI368" s="3" t="n"/>
+      <c r="AJ368" s="3" t="n"/>
+      <c r="AK368" s="3" t="n"/>
+      <c r="AL368" s="3" t="n"/>
+      <c r="AM368" s="3" t="n"/>
+      <c r="AN368" s="3" t="n"/>
+      <c r="AO368" s="3" t="n"/>
     </row>
     <row r="369">
       <c r="A369" s="4" t="n"/>
@@ -13185,6 +16546,15 @@
       <c r="AD369" s="4" t="n"/>
       <c r="AE369" s="4" t="n"/>
       <c r="AF369" s="4" t="n"/>
+      <c r="AG369" s="4" t="n"/>
+      <c r="AH369" s="4" t="n"/>
+      <c r="AI369" s="4" t="n"/>
+      <c r="AJ369" s="4" t="n"/>
+      <c r="AK369" s="4" t="n"/>
+      <c r="AL369" s="4" t="n"/>
+      <c r="AM369" s="4" t="n"/>
+      <c r="AN369" s="4" t="n"/>
+      <c r="AO369" s="4" t="n"/>
     </row>
     <row r="370">
       <c r="A370" s="3" t="n"/>
@@ -13219,6 +16589,15 @@
       <c r="AD370" s="3" t="n"/>
       <c r="AE370" s="3" t="n"/>
       <c r="AF370" s="3" t="n"/>
+      <c r="AG370" s="3" t="n"/>
+      <c r="AH370" s="3" t="n"/>
+      <c r="AI370" s="3" t="n"/>
+      <c r="AJ370" s="3" t="n"/>
+      <c r="AK370" s="3" t="n"/>
+      <c r="AL370" s="3" t="n"/>
+      <c r="AM370" s="3" t="n"/>
+      <c r="AN370" s="3" t="n"/>
+      <c r="AO370" s="3" t="n"/>
     </row>
     <row r="371">
       <c r="A371" s="4" t="n"/>
@@ -13253,6 +16632,15 @@
       <c r="AD371" s="4" t="n"/>
       <c r="AE371" s="4" t="n"/>
       <c r="AF371" s="4" t="n"/>
+      <c r="AG371" s="4" t="n"/>
+      <c r="AH371" s="4" t="n"/>
+      <c r="AI371" s="4" t="n"/>
+      <c r="AJ371" s="4" t="n"/>
+      <c r="AK371" s="4" t="n"/>
+      <c r="AL371" s="4" t="n"/>
+      <c r="AM371" s="4" t="n"/>
+      <c r="AN371" s="4" t="n"/>
+      <c r="AO371" s="4" t="n"/>
     </row>
     <row r="372">
       <c r="A372" s="3" t="n"/>
@@ -13287,6 +16675,15 @@
       <c r="AD372" s="3" t="n"/>
       <c r="AE372" s="3" t="n"/>
       <c r="AF372" s="3" t="n"/>
+      <c r="AG372" s="3" t="n"/>
+      <c r="AH372" s="3" t="n"/>
+      <c r="AI372" s="3" t="n"/>
+      <c r="AJ372" s="3" t="n"/>
+      <c r="AK372" s="3" t="n"/>
+      <c r="AL372" s="3" t="n"/>
+      <c r="AM372" s="3" t="n"/>
+      <c r="AN372" s="3" t="n"/>
+      <c r="AO372" s="3" t="n"/>
     </row>
     <row r="373">
       <c r="A373" s="4" t="n"/>
@@ -13321,6 +16718,15 @@
       <c r="AD373" s="4" t="n"/>
       <c r="AE373" s="4" t="n"/>
       <c r="AF373" s="4" t="n"/>
+      <c r="AG373" s="4" t="n"/>
+      <c r="AH373" s="4" t="n"/>
+      <c r="AI373" s="4" t="n"/>
+      <c r="AJ373" s="4" t="n"/>
+      <c r="AK373" s="4" t="n"/>
+      <c r="AL373" s="4" t="n"/>
+      <c r="AM373" s="4" t="n"/>
+      <c r="AN373" s="4" t="n"/>
+      <c r="AO373" s="4" t="n"/>
     </row>
     <row r="374">
       <c r="A374" s="3" t="n"/>
@@ -13355,6 +16761,15 @@
       <c r="AD374" s="3" t="n"/>
       <c r="AE374" s="3" t="n"/>
       <c r="AF374" s="3" t="n"/>
+      <c r="AG374" s="3" t="n"/>
+      <c r="AH374" s="3" t="n"/>
+      <c r="AI374" s="3" t="n"/>
+      <c r="AJ374" s="3" t="n"/>
+      <c r="AK374" s="3" t="n"/>
+      <c r="AL374" s="3" t="n"/>
+      <c r="AM374" s="3" t="n"/>
+      <c r="AN374" s="3" t="n"/>
+      <c r="AO374" s="3" t="n"/>
     </row>
     <row r="375">
       <c r="A375" s="4" t="n"/>
@@ -13389,6 +16804,15 @@
       <c r="AD375" s="4" t="n"/>
       <c r="AE375" s="4" t="n"/>
       <c r="AF375" s="4" t="n"/>
+      <c r="AG375" s="4" t="n"/>
+      <c r="AH375" s="4" t="n"/>
+      <c r="AI375" s="4" t="n"/>
+      <c r="AJ375" s="4" t="n"/>
+      <c r="AK375" s="4" t="n"/>
+      <c r="AL375" s="4" t="n"/>
+      <c r="AM375" s="4" t="n"/>
+      <c r="AN375" s="4" t="n"/>
+      <c r="AO375" s="4" t="n"/>
     </row>
     <row r="376">
       <c r="A376" s="3" t="n"/>
@@ -13423,6 +16847,15 @@
       <c r="AD376" s="3" t="n"/>
       <c r="AE376" s="3" t="n"/>
       <c r="AF376" s="3" t="n"/>
+      <c r="AG376" s="3" t="n"/>
+      <c r="AH376" s="3" t="n"/>
+      <c r="AI376" s="3" t="n"/>
+      <c r="AJ376" s="3" t="n"/>
+      <c r="AK376" s="3" t="n"/>
+      <c r="AL376" s="3" t="n"/>
+      <c r="AM376" s="3" t="n"/>
+      <c r="AN376" s="3" t="n"/>
+      <c r="AO376" s="3" t="n"/>
     </row>
     <row r="377">
       <c r="A377" s="4" t="n"/>
@@ -13457,6 +16890,15 @@
       <c r="AD377" s="4" t="n"/>
       <c r="AE377" s="4" t="n"/>
       <c r="AF377" s="4" t="n"/>
+      <c r="AG377" s="4" t="n"/>
+      <c r="AH377" s="4" t="n"/>
+      <c r="AI377" s="4" t="n"/>
+      <c r="AJ377" s="4" t="n"/>
+      <c r="AK377" s="4" t="n"/>
+      <c r="AL377" s="4" t="n"/>
+      <c r="AM377" s="4" t="n"/>
+      <c r="AN377" s="4" t="n"/>
+      <c r="AO377" s="4" t="n"/>
     </row>
     <row r="378">
       <c r="A378" s="3" t="n"/>
@@ -13491,6 +16933,15 @@
       <c r="AD378" s="3" t="n"/>
       <c r="AE378" s="3" t="n"/>
       <c r="AF378" s="3" t="n"/>
+      <c r="AG378" s="3" t="n"/>
+      <c r="AH378" s="3" t="n"/>
+      <c r="AI378" s="3" t="n"/>
+      <c r="AJ378" s="3" t="n"/>
+      <c r="AK378" s="3" t="n"/>
+      <c r="AL378" s="3" t="n"/>
+      <c r="AM378" s="3" t="n"/>
+      <c r="AN378" s="3" t="n"/>
+      <c r="AO378" s="3" t="n"/>
     </row>
     <row r="379">
       <c r="A379" s="4" t="n"/>
@@ -13525,6 +16976,15 @@
       <c r="AD379" s="4" t="n"/>
       <c r="AE379" s="4" t="n"/>
       <c r="AF379" s="4" t="n"/>
+      <c r="AG379" s="4" t="n"/>
+      <c r="AH379" s="4" t="n"/>
+      <c r="AI379" s="4" t="n"/>
+      <c r="AJ379" s="4" t="n"/>
+      <c r="AK379" s="4" t="n"/>
+      <c r="AL379" s="4" t="n"/>
+      <c r="AM379" s="4" t="n"/>
+      <c r="AN379" s="4" t="n"/>
+      <c r="AO379" s="4" t="n"/>
     </row>
     <row r="380">
       <c r="A380" s="3" t="n"/>
@@ -13559,6 +17019,15 @@
       <c r="AD380" s="3" t="n"/>
       <c r="AE380" s="3" t="n"/>
       <c r="AF380" s="3" t="n"/>
+      <c r="AG380" s="3" t="n"/>
+      <c r="AH380" s="3" t="n"/>
+      <c r="AI380" s="3" t="n"/>
+      <c r="AJ380" s="3" t="n"/>
+      <c r="AK380" s="3" t="n"/>
+      <c r="AL380" s="3" t="n"/>
+      <c r="AM380" s="3" t="n"/>
+      <c r="AN380" s="3" t="n"/>
+      <c r="AO380" s="3" t="n"/>
     </row>
     <row r="381">
       <c r="A381" s="4" t="n"/>
@@ -13593,6 +17062,15 @@
       <c r="AD381" s="4" t="n"/>
       <c r="AE381" s="4" t="n"/>
       <c r="AF381" s="4" t="n"/>
+      <c r="AG381" s="4" t="n"/>
+      <c r="AH381" s="4" t="n"/>
+      <c r="AI381" s="4" t="n"/>
+      <c r="AJ381" s="4" t="n"/>
+      <c r="AK381" s="4" t="n"/>
+      <c r="AL381" s="4" t="n"/>
+      <c r="AM381" s="4" t="n"/>
+      <c r="AN381" s="4" t="n"/>
+      <c r="AO381" s="4" t="n"/>
     </row>
     <row r="382">
       <c r="A382" s="3" t="n"/>
@@ -13627,6 +17105,15 @@
       <c r="AD382" s="3" t="n"/>
       <c r="AE382" s="3" t="n"/>
       <c r="AF382" s="3" t="n"/>
+      <c r="AG382" s="3" t="n"/>
+      <c r="AH382" s="3" t="n"/>
+      <c r="AI382" s="3" t="n"/>
+      <c r="AJ382" s="3" t="n"/>
+      <c r="AK382" s="3" t="n"/>
+      <c r="AL382" s="3" t="n"/>
+      <c r="AM382" s="3" t="n"/>
+      <c r="AN382" s="3" t="n"/>
+      <c r="AO382" s="3" t="n"/>
     </row>
     <row r="383">
       <c r="A383" s="4" t="n"/>
@@ -13661,6 +17148,15 @@
       <c r="AD383" s="4" t="n"/>
       <c r="AE383" s="4" t="n"/>
       <c r="AF383" s="4" t="n"/>
+      <c r="AG383" s="4" t="n"/>
+      <c r="AH383" s="4" t="n"/>
+      <c r="AI383" s="4" t="n"/>
+      <c r="AJ383" s="4" t="n"/>
+      <c r="AK383" s="4" t="n"/>
+      <c r="AL383" s="4" t="n"/>
+      <c r="AM383" s="4" t="n"/>
+      <c r="AN383" s="4" t="n"/>
+      <c r="AO383" s="4" t="n"/>
     </row>
     <row r="384">
       <c r="A384" s="3" t="n"/>
@@ -13695,6 +17191,15 @@
       <c r="AD384" s="3" t="n"/>
       <c r="AE384" s="3" t="n"/>
       <c r="AF384" s="3" t="n"/>
+      <c r="AG384" s="3" t="n"/>
+      <c r="AH384" s="3" t="n"/>
+      <c r="AI384" s="3" t="n"/>
+      <c r="AJ384" s="3" t="n"/>
+      <c r="AK384" s="3" t="n"/>
+      <c r="AL384" s="3" t="n"/>
+      <c r="AM384" s="3" t="n"/>
+      <c r="AN384" s="3" t="n"/>
+      <c r="AO384" s="3" t="n"/>
     </row>
     <row r="385">
       <c r="A385" s="4" t="n"/>
@@ -13729,6 +17234,15 @@
       <c r="AD385" s="4" t="n"/>
       <c r="AE385" s="4" t="n"/>
       <c r="AF385" s="4" t="n"/>
+      <c r="AG385" s="4" t="n"/>
+      <c r="AH385" s="4" t="n"/>
+      <c r="AI385" s="4" t="n"/>
+      <c r="AJ385" s="4" t="n"/>
+      <c r="AK385" s="4" t="n"/>
+      <c r="AL385" s="4" t="n"/>
+      <c r="AM385" s="4" t="n"/>
+      <c r="AN385" s="4" t="n"/>
+      <c r="AO385" s="4" t="n"/>
     </row>
     <row r="386">
       <c r="A386" s="3" t="n"/>
@@ -13763,6 +17277,15 @@
       <c r="AD386" s="3" t="n"/>
       <c r="AE386" s="3" t="n"/>
       <c r="AF386" s="3" t="n"/>
+      <c r="AG386" s="3" t="n"/>
+      <c r="AH386" s="3" t="n"/>
+      <c r="AI386" s="3" t="n"/>
+      <c r="AJ386" s="3" t="n"/>
+      <c r="AK386" s="3" t="n"/>
+      <c r="AL386" s="3" t="n"/>
+      <c r="AM386" s="3" t="n"/>
+      <c r="AN386" s="3" t="n"/>
+      <c r="AO386" s="3" t="n"/>
     </row>
     <row r="387">
       <c r="A387" s="4" t="n"/>
@@ -13797,6 +17320,15 @@
       <c r="AD387" s="4" t="n"/>
       <c r="AE387" s="4" t="n"/>
       <c r="AF387" s="4" t="n"/>
+      <c r="AG387" s="4" t="n"/>
+      <c r="AH387" s="4" t="n"/>
+      <c r="AI387" s="4" t="n"/>
+      <c r="AJ387" s="4" t="n"/>
+      <c r="AK387" s="4" t="n"/>
+      <c r="AL387" s="4" t="n"/>
+      <c r="AM387" s="4" t="n"/>
+      <c r="AN387" s="4" t="n"/>
+      <c r="AO387" s="4" t="n"/>
     </row>
     <row r="388">
       <c r="A388" s="3" t="n"/>
@@ -13831,6 +17363,15 @@
       <c r="AD388" s="3" t="n"/>
       <c r="AE388" s="3" t="n"/>
       <c r="AF388" s="3" t="n"/>
+      <c r="AG388" s="3" t="n"/>
+      <c r="AH388" s="3" t="n"/>
+      <c r="AI388" s="3" t="n"/>
+      <c r="AJ388" s="3" t="n"/>
+      <c r="AK388" s="3" t="n"/>
+      <c r="AL388" s="3" t="n"/>
+      <c r="AM388" s="3" t="n"/>
+      <c r="AN388" s="3" t="n"/>
+      <c r="AO388" s="3" t="n"/>
     </row>
     <row r="389">
       <c r="A389" s="4" t="n"/>
@@ -13865,6 +17406,15 @@
       <c r="AD389" s="4" t="n"/>
       <c r="AE389" s="4" t="n"/>
       <c r="AF389" s="4" t="n"/>
+      <c r="AG389" s="4" t="n"/>
+      <c r="AH389" s="4" t="n"/>
+      <c r="AI389" s="4" t="n"/>
+      <c r="AJ389" s="4" t="n"/>
+      <c r="AK389" s="4" t="n"/>
+      <c r="AL389" s="4" t="n"/>
+      <c r="AM389" s="4" t="n"/>
+      <c r="AN389" s="4" t="n"/>
+      <c r="AO389" s="4" t="n"/>
     </row>
     <row r="390">
       <c r="A390" s="3" t="n"/>
@@ -13899,6 +17449,15 @@
       <c r="AD390" s="3" t="n"/>
       <c r="AE390" s="3" t="n"/>
       <c r="AF390" s="3" t="n"/>
+      <c r="AG390" s="3" t="n"/>
+      <c r="AH390" s="3" t="n"/>
+      <c r="AI390" s="3" t="n"/>
+      <c r="AJ390" s="3" t="n"/>
+      <c r="AK390" s="3" t="n"/>
+      <c r="AL390" s="3" t="n"/>
+      <c r="AM390" s="3" t="n"/>
+      <c r="AN390" s="3" t="n"/>
+      <c r="AO390" s="3" t="n"/>
     </row>
     <row r="391">
       <c r="A391" s="4" t="n"/>
@@ -13933,6 +17492,15 @@
       <c r="AD391" s="4" t="n"/>
       <c r="AE391" s="4" t="n"/>
       <c r="AF391" s="4" t="n"/>
+      <c r="AG391" s="4" t="n"/>
+      <c r="AH391" s="4" t="n"/>
+      <c r="AI391" s="4" t="n"/>
+      <c r="AJ391" s="4" t="n"/>
+      <c r="AK391" s="4" t="n"/>
+      <c r="AL391" s="4" t="n"/>
+      <c r="AM391" s="4" t="n"/>
+      <c r="AN391" s="4" t="n"/>
+      <c r="AO391" s="4" t="n"/>
     </row>
     <row r="392">
       <c r="A392" s="3" t="n"/>
@@ -13967,6 +17535,15 @@
       <c r="AD392" s="3" t="n"/>
       <c r="AE392" s="3" t="n"/>
       <c r="AF392" s="3" t="n"/>
+      <c r="AG392" s="3" t="n"/>
+      <c r="AH392" s="3" t="n"/>
+      <c r="AI392" s="3" t="n"/>
+      <c r="AJ392" s="3" t="n"/>
+      <c r="AK392" s="3" t="n"/>
+      <c r="AL392" s="3" t="n"/>
+      <c r="AM392" s="3" t="n"/>
+      <c r="AN392" s="3" t="n"/>
+      <c r="AO392" s="3" t="n"/>
     </row>
     <row r="393">
       <c r="A393" s="4" t="n"/>
@@ -14001,6 +17578,15 @@
       <c r="AD393" s="4" t="n"/>
       <c r="AE393" s="4" t="n"/>
       <c r="AF393" s="4" t="n"/>
+      <c r="AG393" s="4" t="n"/>
+      <c r="AH393" s="4" t="n"/>
+      <c r="AI393" s="4" t="n"/>
+      <c r="AJ393" s="4" t="n"/>
+      <c r="AK393" s="4" t="n"/>
+      <c r="AL393" s="4" t="n"/>
+      <c r="AM393" s="4" t="n"/>
+      <c r="AN393" s="4" t="n"/>
+      <c r="AO393" s="4" t="n"/>
     </row>
     <row r="394">
       <c r="A394" s="3" t="n"/>
@@ -14035,6 +17621,15 @@
       <c r="AD394" s="3" t="n"/>
       <c r="AE394" s="3" t="n"/>
       <c r="AF394" s="3" t="n"/>
+      <c r="AG394" s="3" t="n"/>
+      <c r="AH394" s="3" t="n"/>
+      <c r="AI394" s="3" t="n"/>
+      <c r="AJ394" s="3" t="n"/>
+      <c r="AK394" s="3" t="n"/>
+      <c r="AL394" s="3" t="n"/>
+      <c r="AM394" s="3" t="n"/>
+      <c r="AN394" s="3" t="n"/>
+      <c r="AO394" s="3" t="n"/>
     </row>
     <row r="395">
       <c r="A395" s="4" t="n"/>
@@ -14069,6 +17664,15 @@
       <c r="AD395" s="4" t="n"/>
       <c r="AE395" s="4" t="n"/>
       <c r="AF395" s="4" t="n"/>
+      <c r="AG395" s="4" t="n"/>
+      <c r="AH395" s="4" t="n"/>
+      <c r="AI395" s="4" t="n"/>
+      <c r="AJ395" s="4" t="n"/>
+      <c r="AK395" s="4" t="n"/>
+      <c r="AL395" s="4" t="n"/>
+      <c r="AM395" s="4" t="n"/>
+      <c r="AN395" s="4" t="n"/>
+      <c r="AO395" s="4" t="n"/>
     </row>
     <row r="396">
       <c r="A396" s="3" t="n"/>
@@ -14103,6 +17707,15 @@
       <c r="AD396" s="3" t="n"/>
       <c r="AE396" s="3" t="n"/>
       <c r="AF396" s="3" t="n"/>
+      <c r="AG396" s="3" t="n"/>
+      <c r="AH396" s="3" t="n"/>
+      <c r="AI396" s="3" t="n"/>
+      <c r="AJ396" s="3" t="n"/>
+      <c r="AK396" s="3" t="n"/>
+      <c r="AL396" s="3" t="n"/>
+      <c r="AM396" s="3" t="n"/>
+      <c r="AN396" s="3" t="n"/>
+      <c r="AO396" s="3" t="n"/>
     </row>
     <row r="397">
       <c r="A397" s="4" t="n"/>
@@ -14137,6 +17750,15 @@
       <c r="AD397" s="4" t="n"/>
       <c r="AE397" s="4" t="n"/>
       <c r="AF397" s="4" t="n"/>
+      <c r="AG397" s="4" t="n"/>
+      <c r="AH397" s="4" t="n"/>
+      <c r="AI397" s="4" t="n"/>
+      <c r="AJ397" s="4" t="n"/>
+      <c r="AK397" s="4" t="n"/>
+      <c r="AL397" s="4" t="n"/>
+      <c r="AM397" s="4" t="n"/>
+      <c r="AN397" s="4" t="n"/>
+      <c r="AO397" s="4" t="n"/>
     </row>
     <row r="398">
       <c r="A398" s="3" t="n"/>
@@ -14171,6 +17793,15 @@
       <c r="AD398" s="3" t="n"/>
       <c r="AE398" s="3" t="n"/>
       <c r="AF398" s="3" t="n"/>
+      <c r="AG398" s="3" t="n"/>
+      <c r="AH398" s="3" t="n"/>
+      <c r="AI398" s="3" t="n"/>
+      <c r="AJ398" s="3" t="n"/>
+      <c r="AK398" s="3" t="n"/>
+      <c r="AL398" s="3" t="n"/>
+      <c r="AM398" s="3" t="n"/>
+      <c r="AN398" s="3" t="n"/>
+      <c r="AO398" s="3" t="n"/>
     </row>
     <row r="399">
       <c r="A399" s="4" t="n"/>
@@ -14205,6 +17836,15 @@
       <c r="AD399" s="4" t="n"/>
       <c r="AE399" s="4" t="n"/>
       <c r="AF399" s="4" t="n"/>
+      <c r="AG399" s="4" t="n"/>
+      <c r="AH399" s="4" t="n"/>
+      <c r="AI399" s="4" t="n"/>
+      <c r="AJ399" s="4" t="n"/>
+      <c r="AK399" s="4" t="n"/>
+      <c r="AL399" s="4" t="n"/>
+      <c r="AM399" s="4" t="n"/>
+      <c r="AN399" s="4" t="n"/>
+      <c r="AO399" s="4" t="n"/>
     </row>
     <row r="400">
       <c r="A400" s="3" t="n"/>
@@ -14239,6 +17879,15 @@
       <c r="AD400" s="3" t="n"/>
       <c r="AE400" s="3" t="n"/>
       <c r="AF400" s="3" t="n"/>
+      <c r="AG400" s="3" t="n"/>
+      <c r="AH400" s="3" t="n"/>
+      <c r="AI400" s="3" t="n"/>
+      <c r="AJ400" s="3" t="n"/>
+      <c r="AK400" s="3" t="n"/>
+      <c r="AL400" s="3" t="n"/>
+      <c r="AM400" s="3" t="n"/>
+      <c r="AN400" s="3" t="n"/>
+      <c r="AO400" s="3" t="n"/>
     </row>
     <row r="401">
       <c r="A401" s="4" t="n"/>
@@ -14273,6 +17922,15 @@
       <c r="AD401" s="4" t="n"/>
       <c r="AE401" s="4" t="n"/>
       <c r="AF401" s="4" t="n"/>
+      <c r="AG401" s="4" t="n"/>
+      <c r="AH401" s="4" t="n"/>
+      <c r="AI401" s="4" t="n"/>
+      <c r="AJ401" s="4" t="n"/>
+      <c r="AK401" s="4" t="n"/>
+      <c r="AL401" s="4" t="n"/>
+      <c r="AM401" s="4" t="n"/>
+      <c r="AN401" s="4" t="n"/>
+      <c r="AO401" s="4" t="n"/>
     </row>
     <row r="402">
       <c r="A402" s="3" t="n"/>
@@ -14307,6 +17965,15 @@
       <c r="AD402" s="3" t="n"/>
       <c r="AE402" s="3" t="n"/>
       <c r="AF402" s="3" t="n"/>
+      <c r="AG402" s="3" t="n"/>
+      <c r="AH402" s="3" t="n"/>
+      <c r="AI402" s="3" t="n"/>
+      <c r="AJ402" s="3" t="n"/>
+      <c r="AK402" s="3" t="n"/>
+      <c r="AL402" s="3" t="n"/>
+      <c r="AM402" s="3" t="n"/>
+      <c r="AN402" s="3" t="n"/>
+      <c r="AO402" s="3" t="n"/>
     </row>
     <row r="403">
       <c r="A403" s="4" t="n"/>
@@ -14341,6 +18008,15 @@
       <c r="AD403" s="4" t="n"/>
       <c r="AE403" s="4" t="n"/>
       <c r="AF403" s="4" t="n"/>
+      <c r="AG403" s="4" t="n"/>
+      <c r="AH403" s="4" t="n"/>
+      <c r="AI403" s="4" t="n"/>
+      <c r="AJ403" s="4" t="n"/>
+      <c r="AK403" s="4" t="n"/>
+      <c r="AL403" s="4" t="n"/>
+      <c r="AM403" s="4" t="n"/>
+      <c r="AN403" s="4" t="n"/>
+      <c r="AO403" s="4" t="n"/>
     </row>
     <row r="404">
       <c r="A404" s="3" t="n"/>
@@ -14375,6 +18051,15 @@
       <c r="AD404" s="3" t="n"/>
       <c r="AE404" s="3" t="n"/>
       <c r="AF404" s="3" t="n"/>
+      <c r="AG404" s="3" t="n"/>
+      <c r="AH404" s="3" t="n"/>
+      <c r="AI404" s="3" t="n"/>
+      <c r="AJ404" s="3" t="n"/>
+      <c r="AK404" s="3" t="n"/>
+      <c r="AL404" s="3" t="n"/>
+      <c r="AM404" s="3" t="n"/>
+      <c r="AN404" s="3" t="n"/>
+      <c r="AO404" s="3" t="n"/>
     </row>
     <row r="405">
       <c r="A405" s="4" t="n"/>
@@ -14409,6 +18094,15 @@
       <c r="AD405" s="4" t="n"/>
       <c r="AE405" s="4" t="n"/>
       <c r="AF405" s="4" t="n"/>
+      <c r="AG405" s="4" t="n"/>
+      <c r="AH405" s="4" t="n"/>
+      <c r="AI405" s="4" t="n"/>
+      <c r="AJ405" s="4" t="n"/>
+      <c r="AK405" s="4" t="n"/>
+      <c r="AL405" s="4" t="n"/>
+      <c r="AM405" s="4" t="n"/>
+      <c r="AN405" s="4" t="n"/>
+      <c r="AO405" s="4" t="n"/>
     </row>
     <row r="406">
       <c r="A406" s="3" t="n"/>
@@ -14443,6 +18137,15 @@
       <c r="AD406" s="3" t="n"/>
       <c r="AE406" s="3" t="n"/>
       <c r="AF406" s="3" t="n"/>
+      <c r="AG406" s="3" t="n"/>
+      <c r="AH406" s="3" t="n"/>
+      <c r="AI406" s="3" t="n"/>
+      <c r="AJ406" s="3" t="n"/>
+      <c r="AK406" s="3" t="n"/>
+      <c r="AL406" s="3" t="n"/>
+      <c r="AM406" s="3" t="n"/>
+      <c r="AN406" s="3" t="n"/>
+      <c r="AO406" s="3" t="n"/>
     </row>
     <row r="407">
       <c r="A407" s="4" t="n"/>
@@ -14477,6 +18180,15 @@
       <c r="AD407" s="4" t="n"/>
       <c r="AE407" s="4" t="n"/>
       <c r="AF407" s="4" t="n"/>
+      <c r="AG407" s="4" t="n"/>
+      <c r="AH407" s="4" t="n"/>
+      <c r="AI407" s="4" t="n"/>
+      <c r="AJ407" s="4" t="n"/>
+      <c r="AK407" s="4" t="n"/>
+      <c r="AL407" s="4" t="n"/>
+      <c r="AM407" s="4" t="n"/>
+      <c r="AN407" s="4" t="n"/>
+      <c r="AO407" s="4" t="n"/>
     </row>
     <row r="408">
       <c r="A408" s="3" t="n"/>
@@ -14511,6 +18223,15 @@
       <c r="AD408" s="3" t="n"/>
       <c r="AE408" s="3" t="n"/>
       <c r="AF408" s="3" t="n"/>
+      <c r="AG408" s="3" t="n"/>
+      <c r="AH408" s="3" t="n"/>
+      <c r="AI408" s="3" t="n"/>
+      <c r="AJ408" s="3" t="n"/>
+      <c r="AK408" s="3" t="n"/>
+      <c r="AL408" s="3" t="n"/>
+      <c r="AM408" s="3" t="n"/>
+      <c r="AN408" s="3" t="n"/>
+      <c r="AO408" s="3" t="n"/>
     </row>
     <row r="409">
       <c r="A409" s="4" t="n"/>
@@ -14545,6 +18266,15 @@
       <c r="AD409" s="4" t="n"/>
       <c r="AE409" s="4" t="n"/>
       <c r="AF409" s="4" t="n"/>
+      <c r="AG409" s="4" t="n"/>
+      <c r="AH409" s="4" t="n"/>
+      <c r="AI409" s="4" t="n"/>
+      <c r="AJ409" s="4" t="n"/>
+      <c r="AK409" s="4" t="n"/>
+      <c r="AL409" s="4" t="n"/>
+      <c r="AM409" s="4" t="n"/>
+      <c r="AN409" s="4" t="n"/>
+      <c r="AO409" s="4" t="n"/>
     </row>
     <row r="410">
       <c r="A410" s="3" t="n"/>
@@ -14579,6 +18309,15 @@
       <c r="AD410" s="3" t="n"/>
       <c r="AE410" s="3" t="n"/>
       <c r="AF410" s="3" t="n"/>
+      <c r="AG410" s="3" t="n"/>
+      <c r="AH410" s="3" t="n"/>
+      <c r="AI410" s="3" t="n"/>
+      <c r="AJ410" s="3" t="n"/>
+      <c r="AK410" s="3" t="n"/>
+      <c r="AL410" s="3" t="n"/>
+      <c r="AM410" s="3" t="n"/>
+      <c r="AN410" s="3" t="n"/>
+      <c r="AO410" s="3" t="n"/>
     </row>
     <row r="411">
       <c r="A411" s="4" t="n"/>
@@ -14613,6 +18352,15 @@
       <c r="AD411" s="4" t="n"/>
       <c r="AE411" s="4" t="n"/>
       <c r="AF411" s="4" t="n"/>
+      <c r="AG411" s="4" t="n"/>
+      <c r="AH411" s="4" t="n"/>
+      <c r="AI411" s="4" t="n"/>
+      <c r="AJ411" s="4" t="n"/>
+      <c r="AK411" s="4" t="n"/>
+      <c r="AL411" s="4" t="n"/>
+      <c r="AM411" s="4" t="n"/>
+      <c r="AN411" s="4" t="n"/>
+      <c r="AO411" s="4" t="n"/>
     </row>
     <row r="412">
       <c r="A412" s="3" t="n"/>
@@ -14647,6 +18395,15 @@
       <c r="AD412" s="3" t="n"/>
       <c r="AE412" s="3" t="n"/>
       <c r="AF412" s="3" t="n"/>
+      <c r="AG412" s="3" t="n"/>
+      <c r="AH412" s="3" t="n"/>
+      <c r="AI412" s="3" t="n"/>
+      <c r="AJ412" s="3" t="n"/>
+      <c r="AK412" s="3" t="n"/>
+      <c r="AL412" s="3" t="n"/>
+      <c r="AM412" s="3" t="n"/>
+      <c r="AN412" s="3" t="n"/>
+      <c r="AO412" s="3" t="n"/>
     </row>
     <row r="413">
       <c r="A413" s="4" t="n"/>
@@ -14681,6 +18438,15 @@
       <c r="AD413" s="4" t="n"/>
       <c r="AE413" s="4" t="n"/>
       <c r="AF413" s="4" t="n"/>
+      <c r="AG413" s="4" t="n"/>
+      <c r="AH413" s="4" t="n"/>
+      <c r="AI413" s="4" t="n"/>
+      <c r="AJ413" s="4" t="n"/>
+      <c r="AK413" s="4" t="n"/>
+      <c r="AL413" s="4" t="n"/>
+      <c r="AM413" s="4" t="n"/>
+      <c r="AN413" s="4" t="n"/>
+      <c r="AO413" s="4" t="n"/>
     </row>
     <row r="414">
       <c r="A414" s="3" t="n"/>
@@ -14715,6 +18481,15 @@
       <c r="AD414" s="3" t="n"/>
       <c r="AE414" s="3" t="n"/>
       <c r="AF414" s="3" t="n"/>
+      <c r="AG414" s="3" t="n"/>
+      <c r="AH414" s="3" t="n"/>
+      <c r="AI414" s="3" t="n"/>
+      <c r="AJ414" s="3" t="n"/>
+      <c r="AK414" s="3" t="n"/>
+      <c r="AL414" s="3" t="n"/>
+      <c r="AM414" s="3" t="n"/>
+      <c r="AN414" s="3" t="n"/>
+      <c r="AO414" s="3" t="n"/>
     </row>
     <row r="415">
       <c r="A415" s="4" t="n"/>
@@ -14749,6 +18524,15 @@
       <c r="AD415" s="4" t="n"/>
       <c r="AE415" s="4" t="n"/>
       <c r="AF415" s="4" t="n"/>
+      <c r="AG415" s="4" t="n"/>
+      <c r="AH415" s="4" t="n"/>
+      <c r="AI415" s="4" t="n"/>
+      <c r="AJ415" s="4" t="n"/>
+      <c r="AK415" s="4" t="n"/>
+      <c r="AL415" s="4" t="n"/>
+      <c r="AM415" s="4" t="n"/>
+      <c r="AN415" s="4" t="n"/>
+      <c r="AO415" s="4" t="n"/>
     </row>
     <row r="416">
       <c r="A416" s="3" t="n"/>
@@ -14783,6 +18567,15 @@
       <c r="AD416" s="3" t="n"/>
       <c r="AE416" s="3" t="n"/>
       <c r="AF416" s="3" t="n"/>
+      <c r="AG416" s="3" t="n"/>
+      <c r="AH416" s="3" t="n"/>
+      <c r="AI416" s="3" t="n"/>
+      <c r="AJ416" s="3" t="n"/>
+      <c r="AK416" s="3" t="n"/>
+      <c r="AL416" s="3" t="n"/>
+      <c r="AM416" s="3" t="n"/>
+      <c r="AN416" s="3" t="n"/>
+      <c r="AO416" s="3" t="n"/>
     </row>
     <row r="417">
       <c r="A417" s="4" t="n"/>
@@ -14817,6 +18610,15 @@
       <c r="AD417" s="4" t="n"/>
       <c r="AE417" s="4" t="n"/>
       <c r="AF417" s="4" t="n"/>
+      <c r="AG417" s="4" t="n"/>
+      <c r="AH417" s="4" t="n"/>
+      <c r="AI417" s="4" t="n"/>
+      <c r="AJ417" s="4" t="n"/>
+      <c r="AK417" s="4" t="n"/>
+      <c r="AL417" s="4" t="n"/>
+      <c r="AM417" s="4" t="n"/>
+      <c r="AN417" s="4" t="n"/>
+      <c r="AO417" s="4" t="n"/>
     </row>
     <row r="418">
       <c r="A418" s="3" t="n"/>
@@ -14851,6 +18653,15 @@
       <c r="AD418" s="3" t="n"/>
       <c r="AE418" s="3" t="n"/>
       <c r="AF418" s="3" t="n"/>
+      <c r="AG418" s="3" t="n"/>
+      <c r="AH418" s="3" t="n"/>
+      <c r="AI418" s="3" t="n"/>
+      <c r="AJ418" s="3" t="n"/>
+      <c r="AK418" s="3" t="n"/>
+      <c r="AL418" s="3" t="n"/>
+      <c r="AM418" s="3" t="n"/>
+      <c r="AN418" s="3" t="n"/>
+      <c r="AO418" s="3" t="n"/>
     </row>
     <row r="419">
       <c r="A419" s="4" t="n"/>
@@ -14885,6 +18696,15 @@
       <c r="AD419" s="4" t="n"/>
       <c r="AE419" s="4" t="n"/>
       <c r="AF419" s="4" t="n"/>
+      <c r="AG419" s="4" t="n"/>
+      <c r="AH419" s="4" t="n"/>
+      <c r="AI419" s="4" t="n"/>
+      <c r="AJ419" s="4" t="n"/>
+      <c r="AK419" s="4" t="n"/>
+      <c r="AL419" s="4" t="n"/>
+      <c r="AM419" s="4" t="n"/>
+      <c r="AN419" s="4" t="n"/>
+      <c r="AO419" s="4" t="n"/>
     </row>
     <row r="420">
       <c r="A420" s="3" t="n"/>
@@ -14919,6 +18739,15 @@
       <c r="AD420" s="3" t="n"/>
       <c r="AE420" s="3" t="n"/>
       <c r="AF420" s="3" t="n"/>
+      <c r="AG420" s="3" t="n"/>
+      <c r="AH420" s="3" t="n"/>
+      <c r="AI420" s="3" t="n"/>
+      <c r="AJ420" s="3" t="n"/>
+      <c r="AK420" s="3" t="n"/>
+      <c r="AL420" s="3" t="n"/>
+      <c r="AM420" s="3" t="n"/>
+      <c r="AN420" s="3" t="n"/>
+      <c r="AO420" s="3" t="n"/>
     </row>
     <row r="421">
       <c r="A421" s="4" t="n"/>
@@ -14953,6 +18782,15 @@
       <c r="AD421" s="4" t="n"/>
       <c r="AE421" s="4" t="n"/>
       <c r="AF421" s="4" t="n"/>
+      <c r="AG421" s="4" t="n"/>
+      <c r="AH421" s="4" t="n"/>
+      <c r="AI421" s="4" t="n"/>
+      <c r="AJ421" s="4" t="n"/>
+      <c r="AK421" s="4" t="n"/>
+      <c r="AL421" s="4" t="n"/>
+      <c r="AM421" s="4" t="n"/>
+      <c r="AN421" s="4" t="n"/>
+      <c r="AO421" s="4" t="n"/>
     </row>
     <row r="422">
       <c r="A422" s="3" t="n"/>
@@ -14987,6 +18825,15 @@
       <c r="AD422" s="3" t="n"/>
       <c r="AE422" s="3" t="n"/>
       <c r="AF422" s="3" t="n"/>
+      <c r="AG422" s="3" t="n"/>
+      <c r="AH422" s="3" t="n"/>
+      <c r="AI422" s="3" t="n"/>
+      <c r="AJ422" s="3" t="n"/>
+      <c r="AK422" s="3" t="n"/>
+      <c r="AL422" s="3" t="n"/>
+      <c r="AM422" s="3" t="n"/>
+      <c r="AN422" s="3" t="n"/>
+      <c r="AO422" s="3" t="n"/>
     </row>
     <row r="423">
       <c r="A423" s="4" t="n"/>
@@ -15021,6 +18868,15 @@
       <c r="AD423" s="4" t="n"/>
       <c r="AE423" s="4" t="n"/>
       <c r="AF423" s="4" t="n"/>
+      <c r="AG423" s="4" t="n"/>
+      <c r="AH423" s="4" t="n"/>
+      <c r="AI423" s="4" t="n"/>
+      <c r="AJ423" s="4" t="n"/>
+      <c r="AK423" s="4" t="n"/>
+      <c r="AL423" s="4" t="n"/>
+      <c r="AM423" s="4" t="n"/>
+      <c r="AN423" s="4" t="n"/>
+      <c r="AO423" s="4" t="n"/>
     </row>
     <row r="424">
       <c r="A424" s="3" t="n"/>
@@ -15055,6 +18911,15 @@
       <c r="AD424" s="3" t="n"/>
       <c r="AE424" s="3" t="n"/>
       <c r="AF424" s="3" t="n"/>
+      <c r="AG424" s="3" t="n"/>
+      <c r="AH424" s="3" t="n"/>
+      <c r="AI424" s="3" t="n"/>
+      <c r="AJ424" s="3" t="n"/>
+      <c r="AK424" s="3" t="n"/>
+      <c r="AL424" s="3" t="n"/>
+      <c r="AM424" s="3" t="n"/>
+      <c r="AN424" s="3" t="n"/>
+      <c r="AO424" s="3" t="n"/>
     </row>
     <row r="425">
       <c r="A425" s="4" t="n"/>
@@ -15089,6 +18954,15 @@
       <c r="AD425" s="4" t="n"/>
       <c r="AE425" s="4" t="n"/>
       <c r="AF425" s="4" t="n"/>
+      <c r="AG425" s="4" t="n"/>
+      <c r="AH425" s="4" t="n"/>
+      <c r="AI425" s="4" t="n"/>
+      <c r="AJ425" s="4" t="n"/>
+      <c r="AK425" s="4" t="n"/>
+      <c r="AL425" s="4" t="n"/>
+      <c r="AM425" s="4" t="n"/>
+      <c r="AN425" s="4" t="n"/>
+      <c r="AO425" s="4" t="n"/>
     </row>
     <row r="426">
       <c r="A426" s="3" t="n"/>
@@ -15123,6 +18997,15 @@
       <c r="AD426" s="3" t="n"/>
       <c r="AE426" s="3" t="n"/>
       <c r="AF426" s="3" t="n"/>
+      <c r="AG426" s="3" t="n"/>
+      <c r="AH426" s="3" t="n"/>
+      <c r="AI426" s="3" t="n"/>
+      <c r="AJ426" s="3" t="n"/>
+      <c r="AK426" s="3" t="n"/>
+      <c r="AL426" s="3" t="n"/>
+      <c r="AM426" s="3" t="n"/>
+      <c r="AN426" s="3" t="n"/>
+      <c r="AO426" s="3" t="n"/>
     </row>
     <row r="427">
       <c r="A427" s="4" t="n"/>
@@ -15157,6 +19040,15 @@
       <c r="AD427" s="4" t="n"/>
       <c r="AE427" s="4" t="n"/>
       <c r="AF427" s="4" t="n"/>
+      <c r="AG427" s="4" t="n"/>
+      <c r="AH427" s="4" t="n"/>
+      <c r="AI427" s="4" t="n"/>
+      <c r="AJ427" s="4" t="n"/>
+      <c r="AK427" s="4" t="n"/>
+      <c r="AL427" s="4" t="n"/>
+      <c r="AM427" s="4" t="n"/>
+      <c r="AN427" s="4" t="n"/>
+      <c r="AO427" s="4" t="n"/>
     </row>
     <row r="428">
       <c r="A428" s="3" t="n"/>
@@ -15191,6 +19083,15 @@
       <c r="AD428" s="3" t="n"/>
       <c r="AE428" s="3" t="n"/>
       <c r="AF428" s="3" t="n"/>
+      <c r="AG428" s="3" t="n"/>
+      <c r="AH428" s="3" t="n"/>
+      <c r="AI428" s="3" t="n"/>
+      <c r="AJ428" s="3" t="n"/>
+      <c r="AK428" s="3" t="n"/>
+      <c r="AL428" s="3" t="n"/>
+      <c r="AM428" s="3" t="n"/>
+      <c r="AN428" s="3" t="n"/>
+      <c r="AO428" s="3" t="n"/>
     </row>
     <row r="429">
       <c r="A429" s="4" t="n"/>
@@ -15225,6 +19126,15 @@
       <c r="AD429" s="4" t="n"/>
       <c r="AE429" s="4" t="n"/>
       <c r="AF429" s="4" t="n"/>
+      <c r="AG429" s="4" t="n"/>
+      <c r="AH429" s="4" t="n"/>
+      <c r="AI429" s="4" t="n"/>
+      <c r="AJ429" s="4" t="n"/>
+      <c r="AK429" s="4" t="n"/>
+      <c r="AL429" s="4" t="n"/>
+      <c r="AM429" s="4" t="n"/>
+      <c r="AN429" s="4" t="n"/>
+      <c r="AO429" s="4" t="n"/>
     </row>
     <row r="430">
       <c r="A430" s="3" t="n"/>
@@ -15259,6 +19169,15 @@
       <c r="AD430" s="3" t="n"/>
       <c r="AE430" s="3" t="n"/>
       <c r="AF430" s="3" t="n"/>
+      <c r="AG430" s="3" t="n"/>
+      <c r="AH430" s="3" t="n"/>
+      <c r="AI430" s="3" t="n"/>
+      <c r="AJ430" s="3" t="n"/>
+      <c r="AK430" s="3" t="n"/>
+      <c r="AL430" s="3" t="n"/>
+      <c r="AM430" s="3" t="n"/>
+      <c r="AN430" s="3" t="n"/>
+      <c r="AO430" s="3" t="n"/>
     </row>
     <row r="431">
       <c r="A431" s="4" t="n"/>
@@ -15293,6 +19212,15 @@
       <c r="AD431" s="4" t="n"/>
       <c r="AE431" s="4" t="n"/>
       <c r="AF431" s="4" t="n"/>
+      <c r="AG431" s="4" t="n"/>
+      <c r="AH431" s="4" t="n"/>
+      <c r="AI431" s="4" t="n"/>
+      <c r="AJ431" s="4" t="n"/>
+      <c r="AK431" s="4" t="n"/>
+      <c r="AL431" s="4" t="n"/>
+      <c r="AM431" s="4" t="n"/>
+      <c r="AN431" s="4" t="n"/>
+      <c r="AO431" s="4" t="n"/>
     </row>
     <row r="432">
       <c r="A432" s="3" t="n"/>
@@ -15327,6 +19255,15 @@
       <c r="AD432" s="3" t="n"/>
       <c r="AE432" s="3" t="n"/>
       <c r="AF432" s="3" t="n"/>
+      <c r="AG432" s="3" t="n"/>
+      <c r="AH432" s="3" t="n"/>
+      <c r="AI432" s="3" t="n"/>
+      <c r="AJ432" s="3" t="n"/>
+      <c r="AK432" s="3" t="n"/>
+      <c r="AL432" s="3" t="n"/>
+      <c r="AM432" s="3" t="n"/>
+      <c r="AN432" s="3" t="n"/>
+      <c r="AO432" s="3" t="n"/>
     </row>
     <row r="433">
       <c r="A433" s="4" t="n"/>
@@ -15361,6 +19298,15 @@
       <c r="AD433" s="4" t="n"/>
       <c r="AE433" s="4" t="n"/>
       <c r="AF433" s="4" t="n"/>
+      <c r="AG433" s="4" t="n"/>
+      <c r="AH433" s="4" t="n"/>
+      <c r="AI433" s="4" t="n"/>
+      <c r="AJ433" s="4" t="n"/>
+      <c r="AK433" s="4" t="n"/>
+      <c r="AL433" s="4" t="n"/>
+      <c r="AM433" s="4" t="n"/>
+      <c r="AN433" s="4" t="n"/>
+      <c r="AO433" s="4" t="n"/>
     </row>
     <row r="434">
       <c r="A434" s="3" t="n"/>
@@ -15395,6 +19341,15 @@
       <c r="AD434" s="3" t="n"/>
       <c r="AE434" s="3" t="n"/>
       <c r="AF434" s="3" t="n"/>
+      <c r="AG434" s="3" t="n"/>
+      <c r="AH434" s="3" t="n"/>
+      <c r="AI434" s="3" t="n"/>
+      <c r="AJ434" s="3" t="n"/>
+      <c r="AK434" s="3" t="n"/>
+      <c r="AL434" s="3" t="n"/>
+      <c r="AM434" s="3" t="n"/>
+      <c r="AN434" s="3" t="n"/>
+      <c r="AO434" s="3" t="n"/>
     </row>
     <row r="435">
       <c r="A435" s="4" t="n"/>
@@ -15429,6 +19384,15 @@
       <c r="AD435" s="4" t="n"/>
       <c r="AE435" s="4" t="n"/>
       <c r="AF435" s="4" t="n"/>
+      <c r="AG435" s="4" t="n"/>
+      <c r="AH435" s="4" t="n"/>
+      <c r="AI435" s="4" t="n"/>
+      <c r="AJ435" s="4" t="n"/>
+      <c r="AK435" s="4" t="n"/>
+      <c r="AL435" s="4" t="n"/>
+      <c r="AM435" s="4" t="n"/>
+      <c r="AN435" s="4" t="n"/>
+      <c r="AO435" s="4" t="n"/>
     </row>
     <row r="436">
       <c r="A436" s="3" t="n"/>
@@ -15463,6 +19427,15 @@
       <c r="AD436" s="3" t="n"/>
       <c r="AE436" s="3" t="n"/>
       <c r="AF436" s="3" t="n"/>
+      <c r="AG436" s="3" t="n"/>
+      <c r="AH436" s="3" t="n"/>
+      <c r="AI436" s="3" t="n"/>
+      <c r="AJ436" s="3" t="n"/>
+      <c r="AK436" s="3" t="n"/>
+      <c r="AL436" s="3" t="n"/>
+      <c r="AM436" s="3" t="n"/>
+      <c r="AN436" s="3" t="n"/>
+      <c r="AO436" s="3" t="n"/>
     </row>
     <row r="437">
       <c r="A437" s="4" t="n"/>
@@ -15497,6 +19470,15 @@
       <c r="AD437" s="4" t="n"/>
       <c r="AE437" s="4" t="n"/>
       <c r="AF437" s="4" t="n"/>
+      <c r="AG437" s="4" t="n"/>
+      <c r="AH437" s="4" t="n"/>
+      <c r="AI437" s="4" t="n"/>
+      <c r="AJ437" s="4" t="n"/>
+      <c r="AK437" s="4" t="n"/>
+      <c r="AL437" s="4" t="n"/>
+      <c r="AM437" s="4" t="n"/>
+      <c r="AN437" s="4" t="n"/>
+      <c r="AO437" s="4" t="n"/>
     </row>
     <row r="438">
       <c r="A438" s="3" t="n"/>
@@ -15531,6 +19513,15 @@
       <c r="AD438" s="3" t="n"/>
       <c r="AE438" s="3" t="n"/>
       <c r="AF438" s="3" t="n"/>
+      <c r="AG438" s="3" t="n"/>
+      <c r="AH438" s="3" t="n"/>
+      <c r="AI438" s="3" t="n"/>
+      <c r="AJ438" s="3" t="n"/>
+      <c r="AK438" s="3" t="n"/>
+      <c r="AL438" s="3" t="n"/>
+      <c r="AM438" s="3" t="n"/>
+      <c r="AN438" s="3" t="n"/>
+      <c r="AO438" s="3" t="n"/>
     </row>
     <row r="439">
       <c r="A439" s="4" t="n"/>
@@ -15565,6 +19556,15 @@
       <c r="AD439" s="4" t="n"/>
       <c r="AE439" s="4" t="n"/>
       <c r="AF439" s="4" t="n"/>
+      <c r="AG439" s="4" t="n"/>
+      <c r="AH439" s="4" t="n"/>
+      <c r="AI439" s="4" t="n"/>
+      <c r="AJ439" s="4" t="n"/>
+      <c r="AK439" s="4" t="n"/>
+      <c r="AL439" s="4" t="n"/>
+      <c r="AM439" s="4" t="n"/>
+      <c r="AN439" s="4" t="n"/>
+      <c r="AO439" s="4" t="n"/>
     </row>
     <row r="440">
       <c r="A440" s="3" t="n"/>
@@ -15599,6 +19599,15 @@
       <c r="AD440" s="3" t="n"/>
       <c r="AE440" s="3" t="n"/>
       <c r="AF440" s="3" t="n"/>
+      <c r="AG440" s="3" t="n"/>
+      <c r="AH440" s="3" t="n"/>
+      <c r="AI440" s="3" t="n"/>
+      <c r="AJ440" s="3" t="n"/>
+      <c r="AK440" s="3" t="n"/>
+      <c r="AL440" s="3" t="n"/>
+      <c r="AM440" s="3" t="n"/>
+      <c r="AN440" s="3" t="n"/>
+      <c r="AO440" s="3" t="n"/>
     </row>
     <row r="441">
       <c r="A441" s="4" t="n"/>
@@ -15633,6 +19642,15 @@
       <c r="AD441" s="4" t="n"/>
       <c r="AE441" s="4" t="n"/>
       <c r="AF441" s="4" t="n"/>
+      <c r="AG441" s="4" t="n"/>
+      <c r="AH441" s="4" t="n"/>
+      <c r="AI441" s="4" t="n"/>
+      <c r="AJ441" s="4" t="n"/>
+      <c r="AK441" s="4" t="n"/>
+      <c r="AL441" s="4" t="n"/>
+      <c r="AM441" s="4" t="n"/>
+      <c r="AN441" s="4" t="n"/>
+      <c r="AO441" s="4" t="n"/>
     </row>
     <row r="442">
       <c r="A442" s="3" t="n"/>
@@ -15667,6 +19685,15 @@
       <c r="AD442" s="3" t="n"/>
       <c r="AE442" s="3" t="n"/>
       <c r="AF442" s="3" t="n"/>
+      <c r="AG442" s="3" t="n"/>
+      <c r="AH442" s="3" t="n"/>
+      <c r="AI442" s="3" t="n"/>
+      <c r="AJ442" s="3" t="n"/>
+      <c r="AK442" s="3" t="n"/>
+      <c r="AL442" s="3" t="n"/>
+      <c r="AM442" s="3" t="n"/>
+      <c r="AN442" s="3" t="n"/>
+      <c r="AO442" s="3" t="n"/>
     </row>
     <row r="443">
       <c r="A443" s="4" t="n"/>
@@ -15701,6 +19728,15 @@
       <c r="AD443" s="4" t="n"/>
       <c r="AE443" s="4" t="n"/>
       <c r="AF443" s="4" t="n"/>
+      <c r="AG443" s="4" t="n"/>
+      <c r="AH443" s="4" t="n"/>
+      <c r="AI443" s="4" t="n"/>
+      <c r="AJ443" s="4" t="n"/>
+      <c r="AK443" s="4" t="n"/>
+      <c r="AL443" s="4" t="n"/>
+      <c r="AM443" s="4" t="n"/>
+      <c r="AN443" s="4" t="n"/>
+      <c r="AO443" s="4" t="n"/>
     </row>
     <row r="444">
       <c r="A444" s="3" t="n"/>
@@ -15735,6 +19771,15 @@
       <c r="AD444" s="3" t="n"/>
       <c r="AE444" s="3" t="n"/>
       <c r="AF444" s="3" t="n"/>
+      <c r="AG444" s="3" t="n"/>
+      <c r="AH444" s="3" t="n"/>
+      <c r="AI444" s="3" t="n"/>
+      <c r="AJ444" s="3" t="n"/>
+      <c r="AK444" s="3" t="n"/>
+      <c r="AL444" s="3" t="n"/>
+      <c r="AM444" s="3" t="n"/>
+      <c r="AN444" s="3" t="n"/>
+      <c r="AO444" s="3" t="n"/>
     </row>
     <row r="445">
       <c r="A445" s="4" t="n"/>
@@ -15769,6 +19814,15 @@
       <c r="AD445" s="4" t="n"/>
       <c r="AE445" s="4" t="n"/>
       <c r="AF445" s="4" t="n"/>
+      <c r="AG445" s="4" t="n"/>
+      <c r="AH445" s="4" t="n"/>
+      <c r="AI445" s="4" t="n"/>
+      <c r="AJ445" s="4" t="n"/>
+      <c r="AK445" s="4" t="n"/>
+      <c r="AL445" s="4" t="n"/>
+      <c r="AM445" s="4" t="n"/>
+      <c r="AN445" s="4" t="n"/>
+      <c r="AO445" s="4" t="n"/>
     </row>
     <row r="446">
       <c r="A446" s="3" t="n"/>
@@ -15803,6 +19857,15 @@
       <c r="AD446" s="3" t="n"/>
       <c r="AE446" s="3" t="n"/>
       <c r="AF446" s="3" t="n"/>
+      <c r="AG446" s="3" t="n"/>
+      <c r="AH446" s="3" t="n"/>
+      <c r="AI446" s="3" t="n"/>
+      <c r="AJ446" s="3" t="n"/>
+      <c r="AK446" s="3" t="n"/>
+      <c r="AL446" s="3" t="n"/>
+      <c r="AM446" s="3" t="n"/>
+      <c r="AN446" s="3" t="n"/>
+      <c r="AO446" s="3" t="n"/>
     </row>
     <row r="447">
       <c r="A447" s="4" t="n"/>
@@ -15837,6 +19900,15 @@
       <c r="AD447" s="4" t="n"/>
       <c r="AE447" s="4" t="n"/>
       <c r="AF447" s="4" t="n"/>
+      <c r="AG447" s="4" t="n"/>
+      <c r="AH447" s="4" t="n"/>
+      <c r="AI447" s="4" t="n"/>
+      <c r="AJ447" s="4" t="n"/>
+      <c r="AK447" s="4" t="n"/>
+      <c r="AL447" s="4" t="n"/>
+      <c r="AM447" s="4" t="n"/>
+      <c r="AN447" s="4" t="n"/>
+      <c r="AO447" s="4" t="n"/>
     </row>
     <row r="448">
       <c r="A448" s="3" t="n"/>
@@ -15871,6 +19943,15 @@
       <c r="AD448" s="3" t="n"/>
       <c r="AE448" s="3" t="n"/>
       <c r="AF448" s="3" t="n"/>
+      <c r="AG448" s="3" t="n"/>
+      <c r="AH448" s="3" t="n"/>
+      <c r="AI448" s="3" t="n"/>
+      <c r="AJ448" s="3" t="n"/>
+      <c r="AK448" s="3" t="n"/>
+      <c r="AL448" s="3" t="n"/>
+      <c r="AM448" s="3" t="n"/>
+      <c r="AN448" s="3" t="n"/>
+      <c r="AO448" s="3" t="n"/>
     </row>
     <row r="449">
       <c r="A449" s="4" t="n"/>
@@ -15905,6 +19986,15 @@
       <c r="AD449" s="4" t="n"/>
       <c r="AE449" s="4" t="n"/>
       <c r="AF449" s="4" t="n"/>
+      <c r="AG449" s="4" t="n"/>
+      <c r="AH449" s="4" t="n"/>
+      <c r="AI449" s="4" t="n"/>
+      <c r="AJ449" s="4" t="n"/>
+      <c r="AK449" s="4" t="n"/>
+      <c r="AL449" s="4" t="n"/>
+      <c r="AM449" s="4" t="n"/>
+      <c r="AN449" s="4" t="n"/>
+      <c r="AO449" s="4" t="n"/>
     </row>
     <row r="450">
       <c r="A450" s="3" t="n"/>
@@ -15939,6 +20029,15 @@
       <c r="AD450" s="3" t="n"/>
       <c r="AE450" s="3" t="n"/>
       <c r="AF450" s="3" t="n"/>
+      <c r="AG450" s="3" t="n"/>
+      <c r="AH450" s="3" t="n"/>
+      <c r="AI450" s="3" t="n"/>
+      <c r="AJ450" s="3" t="n"/>
+      <c r="AK450" s="3" t="n"/>
+      <c r="AL450" s="3" t="n"/>
+      <c r="AM450" s="3" t="n"/>
+      <c r="AN450" s="3" t="n"/>
+      <c r="AO450" s="3" t="n"/>
     </row>
     <row r="451">
       <c r="A451" s="4" t="n"/>
@@ -15973,6 +20072,15 @@
       <c r="AD451" s="4" t="n"/>
       <c r="AE451" s="4" t="n"/>
       <c r="AF451" s="4" t="n"/>
+      <c r="AG451" s="4" t="n"/>
+      <c r="AH451" s="4" t="n"/>
+      <c r="AI451" s="4" t="n"/>
+      <c r="AJ451" s="4" t="n"/>
+      <c r="AK451" s="4" t="n"/>
+      <c r="AL451" s="4" t="n"/>
+      <c r="AM451" s="4" t="n"/>
+      <c r="AN451" s="4" t="n"/>
+      <c r="AO451" s="4" t="n"/>
     </row>
     <row r="452">
       <c r="A452" s="3" t="n"/>
@@ -16007,6 +20115,15 @@
       <c r="AD452" s="3" t="n"/>
       <c r="AE452" s="3" t="n"/>
       <c r="AF452" s="3" t="n"/>
+      <c r="AG452" s="3" t="n"/>
+      <c r="AH452" s="3" t="n"/>
+      <c r="AI452" s="3" t="n"/>
+      <c r="AJ452" s="3" t="n"/>
+      <c r="AK452" s="3" t="n"/>
+      <c r="AL452" s="3" t="n"/>
+      <c r="AM452" s="3" t="n"/>
+      <c r="AN452" s="3" t="n"/>
+      <c r="AO452" s="3" t="n"/>
     </row>
     <row r="453">
       <c r="A453" s="4" t="n"/>
@@ -16041,6 +20158,15 @@
       <c r="AD453" s="4" t="n"/>
       <c r="AE453" s="4" t="n"/>
       <c r="AF453" s="4" t="n"/>
+      <c r="AG453" s="4" t="n"/>
+      <c r="AH453" s="4" t="n"/>
+      <c r="AI453" s="4" t="n"/>
+      <c r="AJ453" s="4" t="n"/>
+      <c r="AK453" s="4" t="n"/>
+      <c r="AL453" s="4" t="n"/>
+      <c r="AM453" s="4" t="n"/>
+      <c r="AN453" s="4" t="n"/>
+      <c r="AO453" s="4" t="n"/>
     </row>
     <row r="454">
       <c r="A454" s="3" t="n"/>
@@ -16075,6 +20201,15 @@
       <c r="AD454" s="3" t="n"/>
       <c r="AE454" s="3" t="n"/>
       <c r="AF454" s="3" t="n"/>
+      <c r="AG454" s="3" t="n"/>
+      <c r="AH454" s="3" t="n"/>
+      <c r="AI454" s="3" t="n"/>
+      <c r="AJ454" s="3" t="n"/>
+      <c r="AK454" s="3" t="n"/>
+      <c r="AL454" s="3" t="n"/>
+      <c r="AM454" s="3" t="n"/>
+      <c r="AN454" s="3" t="n"/>
+      <c r="AO454" s="3" t="n"/>
     </row>
     <row r="455">
       <c r="A455" s="4" t="n"/>
@@ -16109,6 +20244,15 @@
       <c r="AD455" s="4" t="n"/>
       <c r="AE455" s="4" t="n"/>
       <c r="AF455" s="4" t="n"/>
+      <c r="AG455" s="4" t="n"/>
+      <c r="AH455" s="4" t="n"/>
+      <c r="AI455" s="4" t="n"/>
+      <c r="AJ455" s="4" t="n"/>
+      <c r="AK455" s="4" t="n"/>
+      <c r="AL455" s="4" t="n"/>
+      <c r="AM455" s="4" t="n"/>
+      <c r="AN455" s="4" t="n"/>
+      <c r="AO455" s="4" t="n"/>
     </row>
     <row r="456">
       <c r="A456" s="3" t="n"/>
@@ -16143,6 +20287,15 @@
       <c r="AD456" s="3" t="n"/>
       <c r="AE456" s="3" t="n"/>
       <c r="AF456" s="3" t="n"/>
+      <c r="AG456" s="3" t="n"/>
+      <c r="AH456" s="3" t="n"/>
+      <c r="AI456" s="3" t="n"/>
+      <c r="AJ456" s="3" t="n"/>
+      <c r="AK456" s="3" t="n"/>
+      <c r="AL456" s="3" t="n"/>
+      <c r="AM456" s="3" t="n"/>
+      <c r="AN456" s="3" t="n"/>
+      <c r="AO456" s="3" t="n"/>
     </row>
     <row r="457">
       <c r="A457" s="4" t="n"/>
@@ -16177,6 +20330,15 @@
       <c r="AD457" s="4" t="n"/>
       <c r="AE457" s="4" t="n"/>
       <c r="AF457" s="4" t="n"/>
+      <c r="AG457" s="4" t="n"/>
+      <c r="AH457" s="4" t="n"/>
+      <c r="AI457" s="4" t="n"/>
+      <c r="AJ457" s="4" t="n"/>
+      <c r="AK457" s="4" t="n"/>
+      <c r="AL457" s="4" t="n"/>
+      <c r="AM457" s="4" t="n"/>
+      <c r="AN457" s="4" t="n"/>
+      <c r="AO457" s="4" t="n"/>
     </row>
     <row r="458">
       <c r="A458" s="3" t="n"/>
@@ -16211,6 +20373,15 @@
       <c r="AD458" s="3" t="n"/>
       <c r="AE458" s="3" t="n"/>
       <c r="AF458" s="3" t="n"/>
+      <c r="AG458" s="3" t="n"/>
+      <c r="AH458" s="3" t="n"/>
+      <c r="AI458" s="3" t="n"/>
+      <c r="AJ458" s="3" t="n"/>
+      <c r="AK458" s="3" t="n"/>
+      <c r="AL458" s="3" t="n"/>
+      <c r="AM458" s="3" t="n"/>
+      <c r="AN458" s="3" t="n"/>
+      <c r="AO458" s="3" t="n"/>
     </row>
     <row r="459">
       <c r="A459" s="4" t="n"/>
@@ -16245,6 +20416,15 @@
       <c r="AD459" s="4" t="n"/>
       <c r="AE459" s="4" t="n"/>
       <c r="AF459" s="4" t="n"/>
+      <c r="AG459" s="4" t="n"/>
+      <c r="AH459" s="4" t="n"/>
+      <c r="AI459" s="4" t="n"/>
+      <c r="AJ459" s="4" t="n"/>
+      <c r="AK459" s="4" t="n"/>
+      <c r="AL459" s="4" t="n"/>
+      <c r="AM459" s="4" t="n"/>
+      <c r="AN459" s="4" t="n"/>
+      <c r="AO459" s="4" t="n"/>
     </row>
     <row r="460">
       <c r="A460" s="3" t="n"/>
@@ -16279,6 +20459,15 @@
       <c r="AD460" s="3" t="n"/>
       <c r="AE460" s="3" t="n"/>
       <c r="AF460" s="3" t="n"/>
+      <c r="AG460" s="3" t="n"/>
+      <c r="AH460" s="3" t="n"/>
+      <c r="AI460" s="3" t="n"/>
+      <c r="AJ460" s="3" t="n"/>
+      <c r="AK460" s="3" t="n"/>
+      <c r="AL460" s="3" t="n"/>
+      <c r="AM460" s="3" t="n"/>
+      <c r="AN460" s="3" t="n"/>
+      <c r="AO460" s="3" t="n"/>
     </row>
     <row r="461">
       <c r="A461" s="4" t="n"/>
@@ -16313,6 +20502,15 @@
       <c r="AD461" s="4" t="n"/>
       <c r="AE461" s="4" t="n"/>
       <c r="AF461" s="4" t="n"/>
+      <c r="AG461" s="4" t="n"/>
+      <c r="AH461" s="4" t="n"/>
+      <c r="AI461" s="4" t="n"/>
+      <c r="AJ461" s="4" t="n"/>
+      <c r="AK461" s="4" t="n"/>
+      <c r="AL461" s="4" t="n"/>
+      <c r="AM461" s="4" t="n"/>
+      <c r="AN461" s="4" t="n"/>
+      <c r="AO461" s="4" t="n"/>
     </row>
     <row r="462">
       <c r="A462" s="3" t="n"/>
@@ -16347,6 +20545,15 @@
       <c r="AD462" s="3" t="n"/>
       <c r="AE462" s="3" t="n"/>
       <c r="AF462" s="3" t="n"/>
+      <c r="AG462" s="3" t="n"/>
+      <c r="AH462" s="3" t="n"/>
+      <c r="AI462" s="3" t="n"/>
+      <c r="AJ462" s="3" t="n"/>
+      <c r="AK462" s="3" t="n"/>
+      <c r="AL462" s="3" t="n"/>
+      <c r="AM462" s="3" t="n"/>
+      <c r="AN462" s="3" t="n"/>
+      <c r="AO462" s="3" t="n"/>
     </row>
     <row r="463">
       <c r="A463" s="4" t="n"/>
@@ -16381,6 +20588,15 @@
       <c r="AD463" s="4" t="n"/>
       <c r="AE463" s="4" t="n"/>
       <c r="AF463" s="4" t="n"/>
+      <c r="AG463" s="4" t="n"/>
+      <c r="AH463" s="4" t="n"/>
+      <c r="AI463" s="4" t="n"/>
+      <c r="AJ463" s="4" t="n"/>
+      <c r="AK463" s="4" t="n"/>
+      <c r="AL463" s="4" t="n"/>
+      <c r="AM463" s="4" t="n"/>
+      <c r="AN463" s="4" t="n"/>
+      <c r="AO463" s="4" t="n"/>
     </row>
     <row r="464">
       <c r="A464" s="3" t="n"/>
@@ -16415,6 +20631,15 @@
       <c r="AD464" s="3" t="n"/>
       <c r="AE464" s="3" t="n"/>
       <c r="AF464" s="3" t="n"/>
+      <c r="AG464" s="3" t="n"/>
+      <c r="AH464" s="3" t="n"/>
+      <c r="AI464" s="3" t="n"/>
+      <c r="AJ464" s="3" t="n"/>
+      <c r="AK464" s="3" t="n"/>
+      <c r="AL464" s="3" t="n"/>
+      <c r="AM464" s="3" t="n"/>
+      <c r="AN464" s="3" t="n"/>
+      <c r="AO464" s="3" t="n"/>
     </row>
     <row r="465">
       <c r="A465" s="4" t="n"/>
@@ -16449,6 +20674,15 @@
       <c r="AD465" s="4" t="n"/>
       <c r="AE465" s="4" t="n"/>
       <c r="AF465" s="4" t="n"/>
+      <c r="AG465" s="4" t="n"/>
+      <c r="AH465" s="4" t="n"/>
+      <c r="AI465" s="4" t="n"/>
+      <c r="AJ465" s="4" t="n"/>
+      <c r="AK465" s="4" t="n"/>
+      <c r="AL465" s="4" t="n"/>
+      <c r="AM465" s="4" t="n"/>
+      <c r="AN465" s="4" t="n"/>
+      <c r="AO465" s="4" t="n"/>
     </row>
     <row r="466">
       <c r="A466" s="3" t="n"/>
@@ -16483,6 +20717,15 @@
       <c r="AD466" s="3" t="n"/>
       <c r="AE466" s="3" t="n"/>
       <c r="AF466" s="3" t="n"/>
+      <c r="AG466" s="3" t="n"/>
+      <c r="AH466" s="3" t="n"/>
+      <c r="AI466" s="3" t="n"/>
+      <c r="AJ466" s="3" t="n"/>
+      <c r="AK466" s="3" t="n"/>
+      <c r="AL466" s="3" t="n"/>
+      <c r="AM466" s="3" t="n"/>
+      <c r="AN466" s="3" t="n"/>
+      <c r="AO466" s="3" t="n"/>
     </row>
     <row r="467">
       <c r="A467" s="4" t="n"/>
@@ -16517,6 +20760,15 @@
       <c r="AD467" s="4" t="n"/>
       <c r="AE467" s="4" t="n"/>
       <c r="AF467" s="4" t="n"/>
+      <c r="AG467" s="4" t="n"/>
+      <c r="AH467" s="4" t="n"/>
+      <c r="AI467" s="4" t="n"/>
+      <c r="AJ467" s="4" t="n"/>
+      <c r="AK467" s="4" t="n"/>
+      <c r="AL467" s="4" t="n"/>
+      <c r="AM467" s="4" t="n"/>
+      <c r="AN467" s="4" t="n"/>
+      <c r="AO467" s="4" t="n"/>
     </row>
     <row r="468">
       <c r="A468" s="3" t="n"/>
@@ -16551,6 +20803,15 @@
       <c r="AD468" s="3" t="n"/>
       <c r="AE468" s="3" t="n"/>
       <c r="AF468" s="3" t="n"/>
+      <c r="AG468" s="3" t="n"/>
+      <c r="AH468" s="3" t="n"/>
+      <c r="AI468" s="3" t="n"/>
+      <c r="AJ468" s="3" t="n"/>
+      <c r="AK468" s="3" t="n"/>
+      <c r="AL468" s="3" t="n"/>
+      <c r="AM468" s="3" t="n"/>
+      <c r="AN468" s="3" t="n"/>
+      <c r="AO468" s="3" t="n"/>
     </row>
     <row r="469">
       <c r="A469" s="4" t="n"/>
@@ -16585,6 +20846,15 @@
       <c r="AD469" s="4" t="n"/>
       <c r="AE469" s="4" t="n"/>
       <c r="AF469" s="4" t="n"/>
+      <c r="AG469" s="4" t="n"/>
+      <c r="AH469" s="4" t="n"/>
+      <c r="AI469" s="4" t="n"/>
+      <c r="AJ469" s="4" t="n"/>
+      <c r="AK469" s="4" t="n"/>
+      <c r="AL469" s="4" t="n"/>
+      <c r="AM469" s="4" t="n"/>
+      <c r="AN469" s="4" t="n"/>
+      <c r="AO469" s="4" t="n"/>
     </row>
     <row r="470">
       <c r="A470" s="3" t="n"/>
@@ -16619,6 +20889,15 @@
       <c r="AD470" s="3" t="n"/>
       <c r="AE470" s="3" t="n"/>
       <c r="AF470" s="3" t="n"/>
+      <c r="AG470" s="3" t="n"/>
+      <c r="AH470" s="3" t="n"/>
+      <c r="AI470" s="3" t="n"/>
+      <c r="AJ470" s="3" t="n"/>
+      <c r="AK470" s="3" t="n"/>
+      <c r="AL470" s="3" t="n"/>
+      <c r="AM470" s="3" t="n"/>
+      <c r="AN470" s="3" t="n"/>
+      <c r="AO470" s="3" t="n"/>
     </row>
     <row r="471">
       <c r="A471" s="4" t="n"/>
@@ -16653,6 +20932,15 @@
       <c r="AD471" s="4" t="n"/>
       <c r="AE471" s="4" t="n"/>
       <c r="AF471" s="4" t="n"/>
+      <c r="AG471" s="4" t="n"/>
+      <c r="AH471" s="4" t="n"/>
+      <c r="AI471" s="4" t="n"/>
+      <c r="AJ471" s="4" t="n"/>
+      <c r="AK471" s="4" t="n"/>
+      <c r="AL471" s="4" t="n"/>
+      <c r="AM471" s="4" t="n"/>
+      <c r="AN471" s="4" t="n"/>
+      <c r="AO471" s="4" t="n"/>
     </row>
     <row r="472">
       <c r="A472" s="3" t="n"/>
@@ -16687,6 +20975,15 @@
       <c r="AD472" s="3" t="n"/>
       <c r="AE472" s="3" t="n"/>
       <c r="AF472" s="3" t="n"/>
+      <c r="AG472" s="3" t="n"/>
+      <c r="AH472" s="3" t="n"/>
+      <c r="AI472" s="3" t="n"/>
+      <c r="AJ472" s="3" t="n"/>
+      <c r="AK472" s="3" t="n"/>
+      <c r="AL472" s="3" t="n"/>
+      <c r="AM472" s="3" t="n"/>
+      <c r="AN472" s="3" t="n"/>
+      <c r="AO472" s="3" t="n"/>
     </row>
     <row r="473">
       <c r="A473" s="4" t="n"/>
@@ -16721,6 +21018,15 @@
       <c r="AD473" s="4" t="n"/>
       <c r="AE473" s="4" t="n"/>
       <c r="AF473" s="4" t="n"/>
+      <c r="AG473" s="4" t="n"/>
+      <c r="AH473" s="4" t="n"/>
+      <c r="AI473" s="4" t="n"/>
+      <c r="AJ473" s="4" t="n"/>
+      <c r="AK473" s="4" t="n"/>
+      <c r="AL473" s="4" t="n"/>
+      <c r="AM473" s="4" t="n"/>
+      <c r="AN473" s="4" t="n"/>
+      <c r="AO473" s="4" t="n"/>
     </row>
     <row r="474">
       <c r="A474" s="3" t="n"/>
@@ -16755,6 +21061,15 @@
       <c r="AD474" s="3" t="n"/>
       <c r="AE474" s="3" t="n"/>
       <c r="AF474" s="3" t="n"/>
+      <c r="AG474" s="3" t="n"/>
+      <c r="AH474" s="3" t="n"/>
+      <c r="AI474" s="3" t="n"/>
+      <c r="AJ474" s="3" t="n"/>
+      <c r="AK474" s="3" t="n"/>
+      <c r="AL474" s="3" t="n"/>
+      <c r="AM474" s="3" t="n"/>
+      <c r="AN474" s="3" t="n"/>
+      <c r="AO474" s="3" t="n"/>
     </row>
     <row r="475">
       <c r="A475" s="4" t="n"/>
@@ -16789,6 +21104,15 @@
       <c r="AD475" s="4" t="n"/>
       <c r="AE475" s="4" t="n"/>
       <c r="AF475" s="4" t="n"/>
+      <c r="AG475" s="4" t="n"/>
+      <c r="AH475" s="4" t="n"/>
+      <c r="AI475" s="4" t="n"/>
+      <c r="AJ475" s="4" t="n"/>
+      <c r="AK475" s="4" t="n"/>
+      <c r="AL475" s="4" t="n"/>
+      <c r="AM475" s="4" t="n"/>
+      <c r="AN475" s="4" t="n"/>
+      <c r="AO475" s="4" t="n"/>
     </row>
     <row r="476">
       <c r="A476" s="3" t="n"/>
@@ -16823,6 +21147,15 @@
       <c r="AD476" s="3" t="n"/>
       <c r="AE476" s="3" t="n"/>
       <c r="AF476" s="3" t="n"/>
+      <c r="AG476" s="3" t="n"/>
+      <c r="AH476" s="3" t="n"/>
+      <c r="AI476" s="3" t="n"/>
+      <c r="AJ476" s="3" t="n"/>
+      <c r="AK476" s="3" t="n"/>
+      <c r="AL476" s="3" t="n"/>
+      <c r="AM476" s="3" t="n"/>
+      <c r="AN476" s="3" t="n"/>
+      <c r="AO476" s="3" t="n"/>
     </row>
     <row r="477">
       <c r="A477" s="4" t="n"/>
@@ -16857,6 +21190,15 @@
       <c r="AD477" s="4" t="n"/>
       <c r="AE477" s="4" t="n"/>
       <c r="AF477" s="4" t="n"/>
+      <c r="AG477" s="4" t="n"/>
+      <c r="AH477" s="4" t="n"/>
+      <c r="AI477" s="4" t="n"/>
+      <c r="AJ477" s="4" t="n"/>
+      <c r="AK477" s="4" t="n"/>
+      <c r="AL477" s="4" t="n"/>
+      <c r="AM477" s="4" t="n"/>
+      <c r="AN477" s="4" t="n"/>
+      <c r="AO477" s="4" t="n"/>
     </row>
     <row r="478">
       <c r="A478" s="3" t="n"/>
@@ -16891,6 +21233,15 @@
       <c r="AD478" s="3" t="n"/>
       <c r="AE478" s="3" t="n"/>
       <c r="AF478" s="3" t="n"/>
+      <c r="AG478" s="3" t="n"/>
+      <c r="AH478" s="3" t="n"/>
+      <c r="AI478" s="3" t="n"/>
+      <c r="AJ478" s="3" t="n"/>
+      <c r="AK478" s="3" t="n"/>
+      <c r="AL478" s="3" t="n"/>
+      <c r="AM478" s="3" t="n"/>
+      <c r="AN478" s="3" t="n"/>
+      <c r="AO478" s="3" t="n"/>
     </row>
     <row r="479">
       <c r="A479" s="4" t="n"/>
@@ -16925,6 +21276,15 @@
       <c r="AD479" s="4" t="n"/>
       <c r="AE479" s="4" t="n"/>
       <c r="AF479" s="4" t="n"/>
+      <c r="AG479" s="4" t="n"/>
+      <c r="AH479" s="4" t="n"/>
+      <c r="AI479" s="4" t="n"/>
+      <c r="AJ479" s="4" t="n"/>
+      <c r="AK479" s="4" t="n"/>
+      <c r="AL479" s="4" t="n"/>
+      <c r="AM479" s="4" t="n"/>
+      <c r="AN479" s="4" t="n"/>
+      <c r="AO479" s="4" t="n"/>
     </row>
     <row r="480">
       <c r="A480" s="3" t="n"/>
@@ -16959,6 +21319,15 @@
       <c r="AD480" s="3" t="n"/>
       <c r="AE480" s="3" t="n"/>
       <c r="AF480" s="3" t="n"/>
+      <c r="AG480" s="3" t="n"/>
+      <c r="AH480" s="3" t="n"/>
+      <c r="AI480" s="3" t="n"/>
+      <c r="AJ480" s="3" t="n"/>
+      <c r="AK480" s="3" t="n"/>
+      <c r="AL480" s="3" t="n"/>
+      <c r="AM480" s="3" t="n"/>
+      <c r="AN480" s="3" t="n"/>
+      <c r="AO480" s="3" t="n"/>
     </row>
     <row r="481">
       <c r="A481" s="4" t="n"/>
@@ -16993,6 +21362,15 @@
       <c r="AD481" s="4" t="n"/>
       <c r="AE481" s="4" t="n"/>
       <c r="AF481" s="4" t="n"/>
+      <c r="AG481" s="4" t="n"/>
+      <c r="AH481" s="4" t="n"/>
+      <c r="AI481" s="4" t="n"/>
+      <c r="AJ481" s="4" t="n"/>
+      <c r="AK481" s="4" t="n"/>
+      <c r="AL481" s="4" t="n"/>
+      <c r="AM481" s="4" t="n"/>
+      <c r="AN481" s="4" t="n"/>
+      <c r="AO481" s="4" t="n"/>
     </row>
     <row r="482">
       <c r="A482" s="3" t="n"/>
@@ -17027,6 +21405,15 @@
       <c r="AD482" s="3" t="n"/>
       <c r="AE482" s="3" t="n"/>
       <c r="AF482" s="3" t="n"/>
+      <c r="AG482" s="3" t="n"/>
+      <c r="AH482" s="3" t="n"/>
+      <c r="AI482" s="3" t="n"/>
+      <c r="AJ482" s="3" t="n"/>
+      <c r="AK482" s="3" t="n"/>
+      <c r="AL482" s="3" t="n"/>
+      <c r="AM482" s="3" t="n"/>
+      <c r="AN482" s="3" t="n"/>
+      <c r="AO482" s="3" t="n"/>
     </row>
     <row r="483">
       <c r="A483" s="4" t="n"/>
@@ -17061,6 +21448,15 @@
       <c r="AD483" s="4" t="n"/>
       <c r="AE483" s="4" t="n"/>
       <c r="AF483" s="4" t="n"/>
+      <c r="AG483" s="4" t="n"/>
+      <c r="AH483" s="4" t="n"/>
+      <c r="AI483" s="4" t="n"/>
+      <c r="AJ483" s="4" t="n"/>
+      <c r="AK483" s="4" t="n"/>
+      <c r="AL483" s="4" t="n"/>
+      <c r="AM483" s="4" t="n"/>
+      <c r="AN483" s="4" t="n"/>
+      <c r="AO483" s="4" t="n"/>
     </row>
     <row r="484">
       <c r="A484" s="3" t="n"/>
@@ -17095,6 +21491,15 @@
       <c r="AD484" s="3" t="n"/>
       <c r="AE484" s="3" t="n"/>
       <c r="AF484" s="3" t="n"/>
+      <c r="AG484" s="3" t="n"/>
+      <c r="AH484" s="3" t="n"/>
+      <c r="AI484" s="3" t="n"/>
+      <c r="AJ484" s="3" t="n"/>
+      <c r="AK484" s="3" t="n"/>
+      <c r="AL484" s="3" t="n"/>
+      <c r="AM484" s="3" t="n"/>
+      <c r="AN484" s="3" t="n"/>
+      <c r="AO484" s="3" t="n"/>
     </row>
     <row r="485">
       <c r="A485" s="4" t="n"/>
@@ -17129,6 +21534,15 @@
       <c r="AD485" s="4" t="n"/>
       <c r="AE485" s="4" t="n"/>
       <c r="AF485" s="4" t="n"/>
+      <c r="AG485" s="4" t="n"/>
+      <c r="AH485" s="4" t="n"/>
+      <c r="AI485" s="4" t="n"/>
+      <c r="AJ485" s="4" t="n"/>
+      <c r="AK485" s="4" t="n"/>
+      <c r="AL485" s="4" t="n"/>
+      <c r="AM485" s="4" t="n"/>
+      <c r="AN485" s="4" t="n"/>
+      <c r="AO485" s="4" t="n"/>
     </row>
     <row r="486">
       <c r="A486" s="3" t="n"/>
@@ -17163,6 +21577,15 @@
       <c r="AD486" s="3" t="n"/>
       <c r="AE486" s="3" t="n"/>
       <c r="AF486" s="3" t="n"/>
+      <c r="AG486" s="3" t="n"/>
+      <c r="AH486" s="3" t="n"/>
+      <c r="AI486" s="3" t="n"/>
+      <c r="AJ486" s="3" t="n"/>
+      <c r="AK486" s="3" t="n"/>
+      <c r="AL486" s="3" t="n"/>
+      <c r="AM486" s="3" t="n"/>
+      <c r="AN486" s="3" t="n"/>
+      <c r="AO486" s="3" t="n"/>
     </row>
     <row r="487">
       <c r="A487" s="4" t="n"/>
@@ -17197,6 +21620,15 @@
       <c r="AD487" s="4" t="n"/>
       <c r="AE487" s="4" t="n"/>
       <c r="AF487" s="4" t="n"/>
+      <c r="AG487" s="4" t="n"/>
+      <c r="AH487" s="4" t="n"/>
+      <c r="AI487" s="4" t="n"/>
+      <c r="AJ487" s="4" t="n"/>
+      <c r="AK487" s="4" t="n"/>
+      <c r="AL487" s="4" t="n"/>
+      <c r="AM487" s="4" t="n"/>
+      <c r="AN487" s="4" t="n"/>
+      <c r="AO487" s="4" t="n"/>
     </row>
     <row r="488">
       <c r="A488" s="3" t="n"/>
@@ -17231,6 +21663,15 @@
       <c r="AD488" s="3" t="n"/>
       <c r="AE488" s="3" t="n"/>
       <c r="AF488" s="3" t="n"/>
+      <c r="AG488" s="3" t="n"/>
+      <c r="AH488" s="3" t="n"/>
+      <c r="AI488" s="3" t="n"/>
+      <c r="AJ488" s="3" t="n"/>
+      <c r="AK488" s="3" t="n"/>
+      <c r="AL488" s="3" t="n"/>
+      <c r="AM488" s="3" t="n"/>
+      <c r="AN488" s="3" t="n"/>
+      <c r="AO488" s="3" t="n"/>
     </row>
     <row r="489">
       <c r="A489" s="4" t="n"/>
@@ -17265,6 +21706,15 @@
       <c r="AD489" s="4" t="n"/>
       <c r="AE489" s="4" t="n"/>
       <c r="AF489" s="4" t="n"/>
+      <c r="AG489" s="4" t="n"/>
+      <c r="AH489" s="4" t="n"/>
+      <c r="AI489" s="4" t="n"/>
+      <c r="AJ489" s="4" t="n"/>
+      <c r="AK489" s="4" t="n"/>
+      <c r="AL489" s="4" t="n"/>
+      <c r="AM489" s="4" t="n"/>
+      <c r="AN489" s="4" t="n"/>
+      <c r="AO489" s="4" t="n"/>
     </row>
     <row r="490">
       <c r="A490" s="3" t="n"/>
@@ -17299,6 +21749,15 @@
       <c r="AD490" s="3" t="n"/>
       <c r="AE490" s="3" t="n"/>
       <c r="AF490" s="3" t="n"/>
+      <c r="AG490" s="3" t="n"/>
+      <c r="AH490" s="3" t="n"/>
+      <c r="AI490" s="3" t="n"/>
+      <c r="AJ490" s="3" t="n"/>
+      <c r="AK490" s="3" t="n"/>
+      <c r="AL490" s="3" t="n"/>
+      <c r="AM490" s="3" t="n"/>
+      <c r="AN490" s="3" t="n"/>
+      <c r="AO490" s="3" t="n"/>
     </row>
     <row r="491">
       <c r="A491" s="4" t="n"/>
@@ -17333,6 +21792,15 @@
       <c r="AD491" s="4" t="n"/>
       <c r="AE491" s="4" t="n"/>
       <c r="AF491" s="4" t="n"/>
+      <c r="AG491" s="4" t="n"/>
+      <c r="AH491" s="4" t="n"/>
+      <c r="AI491" s="4" t="n"/>
+      <c r="AJ491" s="4" t="n"/>
+      <c r="AK491" s="4" t="n"/>
+      <c r="AL491" s="4" t="n"/>
+      <c r="AM491" s="4" t="n"/>
+      <c r="AN491" s="4" t="n"/>
+      <c r="AO491" s="4" t="n"/>
     </row>
     <row r="492">
       <c r="A492" s="3" t="n"/>
@@ -17367,6 +21835,15 @@
       <c r="AD492" s="3" t="n"/>
       <c r="AE492" s="3" t="n"/>
       <c r="AF492" s="3" t="n"/>
+      <c r="AG492" s="3" t="n"/>
+      <c r="AH492" s="3" t="n"/>
+      <c r="AI492" s="3" t="n"/>
+      <c r="AJ492" s="3" t="n"/>
+      <c r="AK492" s="3" t="n"/>
+      <c r="AL492" s="3" t="n"/>
+      <c r="AM492" s="3" t="n"/>
+      <c r="AN492" s="3" t="n"/>
+      <c r="AO492" s="3" t="n"/>
     </row>
     <row r="493">
       <c r="A493" s="4" t="n"/>
@@ -17401,6 +21878,15 @@
       <c r="AD493" s="4" t="n"/>
       <c r="AE493" s="4" t="n"/>
       <c r="AF493" s="4" t="n"/>
+      <c r="AG493" s="4" t="n"/>
+      <c r="AH493" s="4" t="n"/>
+      <c r="AI493" s="4" t="n"/>
+      <c r="AJ493" s="4" t="n"/>
+      <c r="AK493" s="4" t="n"/>
+      <c r="AL493" s="4" t="n"/>
+      <c r="AM493" s="4" t="n"/>
+      <c r="AN493" s="4" t="n"/>
+      <c r="AO493" s="4" t="n"/>
     </row>
     <row r="494">
       <c r="A494" s="3" t="n"/>
@@ -17435,6 +21921,15 @@
       <c r="AD494" s="3" t="n"/>
       <c r="AE494" s="3" t="n"/>
       <c r="AF494" s="3" t="n"/>
+      <c r="AG494" s="3" t="n"/>
+      <c r="AH494" s="3" t="n"/>
+      <c r="AI494" s="3" t="n"/>
+      <c r="AJ494" s="3" t="n"/>
+      <c r="AK494" s="3" t="n"/>
+      <c r="AL494" s="3" t="n"/>
+      <c r="AM494" s="3" t="n"/>
+      <c r="AN494" s="3" t="n"/>
+      <c r="AO494" s="3" t="n"/>
     </row>
     <row r="495">
       <c r="A495" s="4" t="n"/>
@@ -17469,6 +21964,15 @@
       <c r="AD495" s="4" t="n"/>
       <c r="AE495" s="4" t="n"/>
       <c r="AF495" s="4" t="n"/>
+      <c r="AG495" s="4" t="n"/>
+      <c r="AH495" s="4" t="n"/>
+      <c r="AI495" s="4" t="n"/>
+      <c r="AJ495" s="4" t="n"/>
+      <c r="AK495" s="4" t="n"/>
+      <c r="AL495" s="4" t="n"/>
+      <c r="AM495" s="4" t="n"/>
+      <c r="AN495" s="4" t="n"/>
+      <c r="AO495" s="4" t="n"/>
     </row>
     <row r="496">
       <c r="A496" s="3" t="n"/>
@@ -17503,6 +22007,15 @@
       <c r="AD496" s="3" t="n"/>
       <c r="AE496" s="3" t="n"/>
       <c r="AF496" s="3" t="n"/>
+      <c r="AG496" s="3" t="n"/>
+      <c r="AH496" s="3" t="n"/>
+      <c r="AI496" s="3" t="n"/>
+      <c r="AJ496" s="3" t="n"/>
+      <c r="AK496" s="3" t="n"/>
+      <c r="AL496" s="3" t="n"/>
+      <c r="AM496" s="3" t="n"/>
+      <c r="AN496" s="3" t="n"/>
+      <c r="AO496" s="3" t="n"/>
     </row>
     <row r="497">
       <c r="A497" s="4" t="n"/>
@@ -17537,6 +22050,15 @@
       <c r="AD497" s="4" t="n"/>
       <c r="AE497" s="4" t="n"/>
       <c r="AF497" s="4" t="n"/>
+      <c r="AG497" s="4" t="n"/>
+      <c r="AH497" s="4" t="n"/>
+      <c r="AI497" s="4" t="n"/>
+      <c r="AJ497" s="4" t="n"/>
+      <c r="AK497" s="4" t="n"/>
+      <c r="AL497" s="4" t="n"/>
+      <c r="AM497" s="4" t="n"/>
+      <c r="AN497" s="4" t="n"/>
+      <c r="AO497" s="4" t="n"/>
     </row>
     <row r="498">
       <c r="A498" s="3" t="n"/>
@@ -17571,6 +22093,15 @@
       <c r="AD498" s="3" t="n"/>
       <c r="AE498" s="3" t="n"/>
       <c r="AF498" s="3" t="n"/>
+      <c r="AG498" s="3" t="n"/>
+      <c r="AH498" s="3" t="n"/>
+      <c r="AI498" s="3" t="n"/>
+      <c r="AJ498" s="3" t="n"/>
+      <c r="AK498" s="3" t="n"/>
+      <c r="AL498" s="3" t="n"/>
+      <c r="AM498" s="3" t="n"/>
+      <c r="AN498" s="3" t="n"/>
+      <c r="AO498" s="3" t="n"/>
     </row>
     <row r="499">
       <c r="A499" s="4" t="n"/>
@@ -17605,6 +22136,15 @@
       <c r="AD499" s="4" t="n"/>
       <c r="AE499" s="4" t="n"/>
       <c r="AF499" s="4" t="n"/>
+      <c r="AG499" s="4" t="n"/>
+      <c r="AH499" s="4" t="n"/>
+      <c r="AI499" s="4" t="n"/>
+      <c r="AJ499" s="4" t="n"/>
+      <c r="AK499" s="4" t="n"/>
+      <c r="AL499" s="4" t="n"/>
+      <c r="AM499" s="4" t="n"/>
+      <c r="AN499" s="4" t="n"/>
+      <c r="AO499" s="4" t="n"/>
     </row>
     <row r="500">
       <c r="A500" s="3" t="n"/>
@@ -17639,6 +22179,15 @@
       <c r="AD500" s="3" t="n"/>
       <c r="AE500" s="3" t="n"/>
       <c r="AF500" s="3" t="n"/>
+      <c r="AG500" s="3" t="n"/>
+      <c r="AH500" s="3" t="n"/>
+      <c r="AI500" s="3" t="n"/>
+      <c r="AJ500" s="3" t="n"/>
+      <c r="AK500" s="3" t="n"/>
+      <c r="AL500" s="3" t="n"/>
+      <c r="AM500" s="3" t="n"/>
+      <c r="AN500" s="3" t="n"/>
+      <c r="AO500" s="3" t="n"/>
     </row>
     <row r="501">
       <c r="A501" s="4" t="n"/>
@@ -17673,18 +22222,31 @@
       <c r="AD501" s="4" t="n"/>
       <c r="AE501" s="4" t="n"/>
       <c r="AF501" s="4" t="n"/>
+      <c r="AG501" s="4" t="n"/>
+      <c r="AH501" s="4" t="n"/>
+      <c r="AI501" s="4" t="n"/>
+      <c r="AJ501" s="4" t="n"/>
+      <c r="AK501" s="4" t="n"/>
+      <c r="AL501" s="4" t="n"/>
+      <c r="AM501" s="4" t="n"/>
+      <c r="AN501" s="4" t="n"/>
+      <c r="AO501" s="4" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AF501"/>
-  <dataValidations count="3">
+  <autoFilter ref="A1:AO501"/>
+  <dataValidations count="4">
     <dataValidation sqref="C2:C501" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="请选择下拉选项" error="该字段请使用模板中的下拉选项。" promptTitle="IP类型" prompt="请选择指定的IP类型。" type="list" errorStyle="stop">
       <formula1>"游戏,动画,影视,综艺,体育,潮牌,潮玩,品牌,文化艺术,线下活动,其他"</formula1>
     </dataValidation>
     <dataValidation sqref="D2:D501 E2:E501 F2:F501 G2:G501 H2:H501 I2:I501 J2:J501 K2:K501 L2:L501" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="覆盖市场" prompt="每列选择一个市场；可使用多列。" type="list">
       <formula1>"中国,东南亚,南亚,欧洲,中东,非洲,拉美,北美,全球"</formula1>
     </dataValidation>
-    <dataValidation sqref="Q2:Q501" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="请选择下拉选项" error="该字段请使用模板中的下拉选项。" promptTitle="合作状态" prompt="请选择合作状态；留空默认为待评估。" type="list" errorStyle="stop">
+    <dataValidation sqref="Z2:Z501" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="请选择下拉选项" error="该字段请使用模板中的下拉选项。" promptTitle="合作状态" prompt="请选择合作状态；留空默认为待评估。" type="list" errorStyle="stop">
       <formula1>"可合作,洽谈中,待评估,暂不可合作"</formula1>
+    </dataValidation>
+    <dataValidation sqref="M2:U501" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="渗透率格式错误" error="请填写0至100的数字，例如25表示25%。" promptTitle="覆盖市场渗透率" prompt="逐列对应覆盖市场1至9；填0至100，可留空。" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>100</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -17737,7 +22299,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>覆盖市场1为必填；覆盖市场2至9可选，每列从下拉选择一个市场。若需自定义市场可直接输入；重复市场会去重。</t>
+          <t>覆盖市场1必填，覆盖市场2至9可选；渗透率1至9逐列对应市场1至9，填0至100的数字（例如25表示25%），可留空。自定义市场可直接输入；重复市场会报错。</t>
         </is>
       </c>
     </row>

--- a/vue-pure-admin/public/IP导入模板.xlsx
+++ b/vue-pure-admin/public/IP导入模板.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IP导入模板" sheetId="1" r:id="Rfba138fbca764dcc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填写说明" sheetId="2" r:id="R3931af3715794002"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IP导入模板" sheetId="1" r:id="R8ad127a35d9b4421"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填写说明" sheetId="2" r:id="R0189a531553d4ae8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -23240,7 +23240,7 @@
       <x:c r="AQ501" s="11"/>
     </x:row>
   </x:sheetData>
-  <x:dataValidations count="4">
+  <x:dataValidations count="5">
     <x:dataValidation type="list" errorStyle="stop" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="请选择下拉选项" error="该字段请使用模板中的下拉选项。" promptTitle="IP类型" prompt="请选择指定的IP类型。" sqref="C2:C501">
       <x:formula1>"游戏,动画,影视,综艺,体育,潮牌,潮玩,品牌,文化艺术,线下活动,其他"</x:formula1>
     </x:dataValidation>
@@ -23254,9 +23254,12 @@
       <x:formula1>0</x:formula1>
       <x:formula2>100</x:formula2>
     </x:dataValidation>
+    <x:dataValidation type="list" allowBlank="1" showDropDown="0" showErrorMessage="0" sqref="AP2:AP501">
+      <x:formula1>"产品定制,功能联动,联名周边礼盒,线上营销,线下物料及互动"</x:formula1>
+    </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0a8143eb9bde4704"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R093563d1dce6427a"/>
 </x:worksheet>
 </file>
 
@@ -23369,7 +23372,7 @@
         <x:v>可合作形式</x:v>
       </x:c>
       <x:c r="B9" s="10" t="str">
-        <x:v>选填，多选用 / 或 ; 分隔。可选：产品定制、功能联动、联名周边礼盒、线上营销、线下物料及互动。例如：产品定制 / 线上营销。</x:v>
+        <x:v>选填。可从下拉框选择一个选项；多个形式请用 / 或 ; 分隔后输入或粘贴。再次下拉选择会替换单元格原值。可选：产品定制、功能联动、联名周边礼盒、线上营销、线下物料及互动。</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="64" customHeight="1">
